--- a/examples/example_classifier_results.xlsx
+++ b/examples/example_classifier_results.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
     <sheet name="Statistical Tests" sheetId="2" r:id="rId2"/>
-    <sheet name="Estimates" sheetId="3" r:id="rId3"/>
-    <sheet name="Sample" sheetId="4" r:id="rId4"/>
+    <sheet name="Model Performance" sheetId="3" r:id="rId3"/>
+    <sheet name="Estimates" sheetId="4" r:id="rId4"/>
+    <sheet name="Sample" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="110">
   <si>
     <t>Group</t>
   </si>
@@ -202,15 +203,60 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>rho_delta: intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
+    <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
+    <t>model</t>
+  </si>
+  <si>
     <t>metric</t>
   </si>
   <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>ci_low</t>
+  </si>
+  <si>
+    <t>ci_high</t>
+  </si>
+  <si>
+    <t>n_eyes</t>
+  </si>
+  <si>
+    <t>n_patients</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>auc</t>
+  </si>
+  <si>
+    <t>brier</t>
+  </si>
+  <si>
+    <t>logloss</t>
+  </si>
+  <si>
+    <t>sensitivity</t>
+  </si>
+  <si>
+    <t>specificity</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>patient bootstrap, percentile</t>
+  </si>
+  <si>
+    <t>bootstrap, percentile</t>
+  </si>
+  <si>
     <t>model_a</t>
   </si>
   <si>
@@ -226,12 +272,6 @@
     <t>diff</t>
   </si>
   <si>
-    <t>ci_low</t>
-  </si>
-  <si>
-    <t>ci_high</t>
-  </si>
-  <si>
     <t>p</t>
   </si>
   <si>
@@ -247,24 +287,6 @@
     <t>p_adj</t>
   </si>
   <si>
-    <t>auc</t>
-  </si>
-  <si>
-    <t>brier</t>
-  </si>
-  <si>
-    <t>logloss</t>
-  </si>
-  <si>
-    <t>sensitivity</t>
-  </si>
-  <si>
-    <t>specificity</t>
-  </si>
-  <si>
-    <t>accuracy</t>
-  </si>
-  <si>
     <t>DeLong (1988)</t>
   </si>
   <si>
@@ -281,12 +303,6 @@
   </si>
   <si>
     <t>truth</t>
-  </si>
-  <si>
-    <t>n_eyes</t>
-  </si>
-  <si>
-    <t>n_patients</t>
   </si>
   <si>
     <t>n_bilateral</t>
@@ -1867,6 +1883,1614 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2">
+        <v>0.9497450348899624</v>
+      </c>
+      <c r="E2">
+        <v>0.9320893216905599</v>
+      </c>
+      <c r="F2">
+        <v>0.9658422111533366</v>
+      </c>
+      <c r="G2">
+        <v>516</v>
+      </c>
+      <c r="H2">
+        <v>300</v>
+      </c>
+      <c r="I2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3">
+        <v>0.9360670194003528</v>
+      </c>
+      <c r="E3">
+        <v>0.9132995820124723</v>
+      </c>
+      <c r="F3">
+        <v>0.9561922327746769</v>
+      </c>
+      <c r="G3">
+        <v>516</v>
+      </c>
+      <c r="H3">
+        <v>300</v>
+      </c>
+      <c r="I3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="E4">
+        <v>0.8573046968123558</v>
+      </c>
+      <c r="F4">
+        <v>0.9177145234366175</v>
+      </c>
+      <c r="G4">
+        <v>516</v>
+      </c>
+      <c r="H4">
+        <v>300</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5">
+        <v>0.09039919269379845</v>
+      </c>
+      <c r="E5">
+        <v>0.07832652244405816</v>
+      </c>
+      <c r="F5">
+        <v>0.1022662245047647</v>
+      </c>
+      <c r="G5">
+        <v>516</v>
+      </c>
+      <c r="H5">
+        <v>300</v>
+      </c>
+      <c r="I5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6">
+        <v>0.09607086470930232</v>
+      </c>
+      <c r="E6">
+        <v>0.08251477675096154</v>
+      </c>
+      <c r="F6">
+        <v>0.1101717326762754</v>
+      </c>
+      <c r="G6">
+        <v>516</v>
+      </c>
+      <c r="H6">
+        <v>300</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7">
+        <v>0.1235763627906977</v>
+      </c>
+      <c r="E7">
+        <v>0.1064186137780775</v>
+      </c>
+      <c r="F7">
+        <v>0.1410180048162069</v>
+      </c>
+      <c r="G7">
+        <v>516</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+      <c r="I7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8">
+        <v>0.3017094343669053</v>
+      </c>
+      <c r="E8">
+        <v>0.2707681375493131</v>
+      </c>
+      <c r="F8">
+        <v>0.3317168115905306</v>
+      </c>
+      <c r="G8">
+        <v>516</v>
+      </c>
+      <c r="H8">
+        <v>300</v>
+      </c>
+      <c r="I8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9">
+        <v>0.3154288386745746</v>
+      </c>
+      <c r="E9">
+        <v>0.2813931137035998</v>
+      </c>
+      <c r="F9">
+        <v>0.3510561699111525</v>
+      </c>
+      <c r="G9">
+        <v>516</v>
+      </c>
+      <c r="H9">
+        <v>300</v>
+      </c>
+      <c r="I9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10">
+        <v>0.3822401917568288</v>
+      </c>
+      <c r="E10">
+        <v>0.3387446684060572</v>
+      </c>
+      <c r="F10">
+        <v>0.4265781353425924</v>
+      </c>
+      <c r="G10">
+        <v>516</v>
+      </c>
+      <c r="H10">
+        <v>300</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E11">
+        <v>0.7656013257575758</v>
+      </c>
+      <c r="F11">
+        <v>0.8960148148148149</v>
+      </c>
+      <c r="G11">
+        <v>516</v>
+      </c>
+      <c r="H11">
+        <v>300</v>
+      </c>
+      <c r="I11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="E12">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="F12">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="G12">
+        <v>516</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="E13">
+        <v>0.6846128033040785</v>
+      </c>
+      <c r="F13">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G13">
+        <v>516</v>
+      </c>
+      <c r="H13">
+        <v>300</v>
+      </c>
+      <c r="I13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14">
+        <v>0.8862433862433863</v>
+      </c>
+      <c r="E14">
+        <v>0.852937169418176</v>
+      </c>
+      <c r="F14">
+        <v>0.9182058047493403</v>
+      </c>
+      <c r="G14">
+        <v>516</v>
+      </c>
+      <c r="H14">
+        <v>300</v>
+      </c>
+      <c r="I14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15">
+        <v>0.8994708994708994</v>
+      </c>
+      <c r="E15">
+        <v>0.8660881121774977</v>
+      </c>
+      <c r="F15">
+        <v>0.9300518134715026</v>
+      </c>
+      <c r="G15">
+        <v>516</v>
+      </c>
+      <c r="H15">
+        <v>300</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="E16">
+        <v>0.8077940861367046</v>
+      </c>
+      <c r="F16">
+        <v>0.8837240729101195</v>
+      </c>
+      <c r="G16">
+        <v>516</v>
+      </c>
+      <c r="H16">
+        <v>300</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17">
+        <v>0.8720930232558139</v>
+      </c>
+      <c r="E17">
+        <v>0.8428290766208252</v>
+      </c>
+      <c r="F17">
+        <v>0.9011928958756779</v>
+      </c>
+      <c r="G17">
+        <v>516</v>
+      </c>
+      <c r="H17">
+        <v>300</v>
+      </c>
+      <c r="I17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18">
+        <v>0.874031007751938</v>
+      </c>
+      <c r="E18">
+        <v>0.8448275862068966</v>
+      </c>
+      <c r="F18">
+        <v>0.9020735511528966</v>
+      </c>
+      <c r="G18">
+        <v>516</v>
+      </c>
+      <c r="H18">
+        <v>300</v>
+      </c>
+      <c r="I18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19">
+        <v>0.8236434108527132</v>
+      </c>
+      <c r="E19">
+        <v>0.7895702093070514</v>
+      </c>
+      <c r="F19">
+        <v>0.8568627450980392</v>
+      </c>
+      <c r="G19">
+        <v>516</v>
+      </c>
+      <c r="H19">
+        <v>300</v>
+      </c>
+      <c r="I19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20">
+        <v>0.9572425828970333</v>
+      </c>
+      <c r="E20">
+        <v>0.9314174085184896</v>
+      </c>
+      <c r="F20">
+        <v>0.9779403804253587</v>
+      </c>
+      <c r="G20">
+        <v>263</v>
+      </c>
+      <c r="H20">
+        <v>263</v>
+      </c>
+      <c r="I20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21">
+        <v>0.954261198371146</v>
+      </c>
+      <c r="E21">
+        <v>0.9278557781439901</v>
+      </c>
+      <c r="F21">
+        <v>0.9757148084114029</v>
+      </c>
+      <c r="G21">
+        <v>263</v>
+      </c>
+      <c r="H21">
+        <v>263</v>
+      </c>
+      <c r="I21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22">
+        <v>0.9070680628272252</v>
+      </c>
+      <c r="E22">
+        <v>0.8680864992881939</v>
+      </c>
+      <c r="F22">
+        <v>0.9400875480541542</v>
+      </c>
+      <c r="G22">
+        <v>263</v>
+      </c>
+      <c r="H22">
+        <v>263</v>
+      </c>
+      <c r="I22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23">
+        <v>0.08409677600760457</v>
+      </c>
+      <c r="E23">
+        <v>0.06911136540874524</v>
+      </c>
+      <c r="F23">
+        <v>0.1009847289695818</v>
+      </c>
+      <c r="G23">
+        <v>263</v>
+      </c>
+      <c r="H23">
+        <v>263</v>
+      </c>
+      <c r="I23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24">
+        <v>0.08091932330798481</v>
+      </c>
+      <c r="E24">
+        <v>0.06420706836501901</v>
+      </c>
+      <c r="F24">
+        <v>0.09966024858365012</v>
+      </c>
+      <c r="G24">
+        <v>263</v>
+      </c>
+      <c r="H24">
+        <v>263</v>
+      </c>
+      <c r="I24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25">
+        <v>0.1173666533840304</v>
+      </c>
+      <c r="E25">
+        <v>0.0959141370114068</v>
+      </c>
+      <c r="F25">
+        <v>0.1397679711159696</v>
+      </c>
+      <c r="G25">
+        <v>263</v>
+      </c>
+      <c r="H25">
+        <v>263</v>
+      </c>
+      <c r="I25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26">
+        <v>0.2869453687617093</v>
+      </c>
+      <c r="E26">
+        <v>0.2491849800219261</v>
+      </c>
+      <c r="F26">
+        <v>0.3292138341683321</v>
+      </c>
+      <c r="G26">
+        <v>263</v>
+      </c>
+      <c r="H26">
+        <v>263</v>
+      </c>
+      <c r="I26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27">
+        <v>0.2760765501167315</v>
+      </c>
+      <c r="E27">
+        <v>0.2337866905120009</v>
+      </c>
+      <c r="F27">
+        <v>0.3225826966370221</v>
+      </c>
+      <c r="G27">
+        <v>263</v>
+      </c>
+      <c r="H27">
+        <v>263</v>
+      </c>
+      <c r="I27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28">
+        <v>0.3615170226541689</v>
+      </c>
+      <c r="E28">
+        <v>0.3096911889090577</v>
+      </c>
+      <c r="F28">
+        <v>0.4159065315200386</v>
+      </c>
+      <c r="G28">
+        <v>263</v>
+      </c>
+      <c r="H28">
+        <v>263</v>
+      </c>
+      <c r="I28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29">
+        <v>0.8194444444444444</v>
+      </c>
+      <c r="E29">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="F29">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="G29">
+        <v>263</v>
+      </c>
+      <c r="H29">
+        <v>263</v>
+      </c>
+      <c r="I29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30">
+        <v>0.8055555555555556</v>
+      </c>
+      <c r="E30">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="F30">
+        <v>0.8889649923896501</v>
+      </c>
+      <c r="G30">
+        <v>263</v>
+      </c>
+      <c r="H30">
+        <v>263</v>
+      </c>
+      <c r="I30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="E31">
+        <v>0.676056338028169</v>
+      </c>
+      <c r="F31">
+        <v>0.8676470588235294</v>
+      </c>
+      <c r="G31">
+        <v>263</v>
+      </c>
+      <c r="H31">
+        <v>263</v>
+      </c>
+      <c r="I31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32">
+        <v>0.9057591623036649</v>
+      </c>
+      <c r="E32">
+        <v>0.8628515406162466</v>
+      </c>
+      <c r="F32">
+        <v>0.945273631840796</v>
+      </c>
+      <c r="G32">
+        <v>263</v>
+      </c>
+      <c r="H32">
+        <v>263</v>
+      </c>
+      <c r="I32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33">
+        <v>0.9162303664921466</v>
+      </c>
+      <c r="E33">
+        <v>0.8743455497382199</v>
+      </c>
+      <c r="F33">
+        <v>0.953223949337939</v>
+      </c>
+      <c r="G33">
+        <v>263</v>
+      </c>
+      <c r="H33">
+        <v>263</v>
+      </c>
+      <c r="I33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34">
+        <v>0.837696335078534</v>
+      </c>
+      <c r="E34">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="F34">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G34">
+        <v>263</v>
+      </c>
+      <c r="H34">
+        <v>263</v>
+      </c>
+      <c r="I34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35">
+        <v>0.8821292775665399</v>
+      </c>
+      <c r="E35">
+        <v>0.8403041825095057</v>
+      </c>
+      <c r="F35">
+        <v>0.9201520912547528</v>
+      </c>
+      <c r="G35">
+        <v>263</v>
+      </c>
+      <c r="H35">
+        <v>263</v>
+      </c>
+      <c r="I35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36">
+        <v>0.8859315589353612</v>
+      </c>
+      <c r="E36">
+        <v>0.844106463878327</v>
+      </c>
+      <c r="F36">
+        <v>0.9201520912547528</v>
+      </c>
+      <c r="G36">
+        <v>263</v>
+      </c>
+      <c r="H36">
+        <v>263</v>
+      </c>
+      <c r="I36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37">
+        <v>0.8212927756653993</v>
+      </c>
+      <c r="E37">
+        <v>0.7756653992395437</v>
+      </c>
+      <c r="F37">
+        <v>0.8669201520912547</v>
+      </c>
+      <c r="G37">
+        <v>263</v>
+      </c>
+      <c r="H37">
+        <v>263</v>
+      </c>
+      <c r="I37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38">
+        <v>0.9407308377896613</v>
+      </c>
+      <c r="E38">
+        <v>0.911409306760217</v>
+      </c>
+      <c r="F38">
+        <v>0.9649602719005704</v>
+      </c>
+      <c r="G38">
+        <v>253</v>
+      </c>
+      <c r="H38">
+        <v>253</v>
+      </c>
+      <c r="I38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39">
+        <v>0.9163830821584832</v>
+      </c>
+      <c r="E39">
+        <v>0.8794413082083586</v>
+      </c>
+      <c r="F39">
+        <v>0.9491267011035582</v>
+      </c>
+      <c r="G39">
+        <v>253</v>
+      </c>
+      <c r="H39">
+        <v>253</v>
+      </c>
+      <c r="I39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40">
+        <v>0.8704423918327662</v>
+      </c>
+      <c r="E40">
+        <v>0.8206890454828421</v>
+      </c>
+      <c r="F40">
+        <v>0.9151523253929671</v>
+      </c>
+      <c r="G40">
+        <v>253</v>
+      </c>
+      <c r="H40">
+        <v>253</v>
+      </c>
+      <c r="I40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41">
+        <v>0.09695071675889329</v>
+      </c>
+      <c r="E41">
+        <v>0.08017872622529643</v>
+      </c>
+      <c r="F41">
+        <v>0.1154392034308301</v>
+      </c>
+      <c r="G41">
+        <v>253</v>
+      </c>
+      <c r="H41">
+        <v>253</v>
+      </c>
+      <c r="I41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42">
+        <v>0.1118212812648221</v>
+      </c>
+      <c r="E42">
+        <v>0.0916886461521739</v>
+      </c>
+      <c r="F42">
+        <v>0.1326395123577075</v>
+      </c>
+      <c r="G42">
+        <v>253</v>
+      </c>
+      <c r="H42">
+        <v>253</v>
+      </c>
+      <c r="I42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43">
+        <v>0.130031515256917</v>
+      </c>
+      <c r="E43">
+        <v>0.1057446896225297</v>
+      </c>
+      <c r="F43">
+        <v>0.1559957030592885</v>
+      </c>
+      <c r="G43">
+        <v>253</v>
+      </c>
+      <c r="H43">
+        <v>253</v>
+      </c>
+      <c r="I43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44">
+        <v>0.317057059877445</v>
+      </c>
+      <c r="E44">
+        <v>0.2758562403397774</v>
+      </c>
+      <c r="F44">
+        <v>0.3622894928340787</v>
+      </c>
+      <c r="G44">
+        <v>253</v>
+      </c>
+      <c r="H44">
+        <v>253</v>
+      </c>
+      <c r="I44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45">
+        <v>0.3563365536576291</v>
+      </c>
+      <c r="E45">
+        <v>0.3056173165279735</v>
+      </c>
+      <c r="F45">
+        <v>0.4092161441083348</v>
+      </c>
+      <c r="G45">
+        <v>253</v>
+      </c>
+      <c r="H45">
+        <v>253</v>
+      </c>
+      <c r="I45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46">
+        <v>0.4037824584524792</v>
+      </c>
+      <c r="E46">
+        <v>0.3398855733723783</v>
+      </c>
+      <c r="F46">
+        <v>0.4722873582532369</v>
+      </c>
+      <c r="G46">
+        <v>253</v>
+      </c>
+      <c r="H46">
+        <v>253</v>
+      </c>
+      <c r="I46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="E47">
+        <v>0.7534246575342466</v>
+      </c>
+      <c r="F47">
+        <v>0.9305555555555556</v>
+      </c>
+      <c r="G47">
+        <v>253</v>
+      </c>
+      <c r="H47">
+        <v>253</v>
+      </c>
+      <c r="I47" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48">
+        <v>0.803030303030303</v>
+      </c>
+      <c r="E48">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="F48">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G48">
+        <v>253</v>
+      </c>
+      <c r="H48">
+        <v>253</v>
+      </c>
+      <c r="I48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49">
+        <v>0.7424242424242424</v>
+      </c>
+      <c r="E49">
+        <v>0.6323529411764706</v>
+      </c>
+      <c r="F49">
+        <v>0.8450704225352113</v>
+      </c>
+      <c r="G49">
+        <v>253</v>
+      </c>
+      <c r="H49">
+        <v>253</v>
+      </c>
+      <c r="I49" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50">
+        <v>0.8663101604278075</v>
+      </c>
+      <c r="E50">
+        <v>0.8148044111527257</v>
+      </c>
+      <c r="F50">
+        <v>0.9135135135135135</v>
+      </c>
+      <c r="G50">
+        <v>253</v>
+      </c>
+      <c r="H50">
+        <v>253</v>
+      </c>
+      <c r="I50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="E51">
+        <v>0.835046541887699</v>
+      </c>
+      <c r="F51">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="G51">
+        <v>253</v>
+      </c>
+      <c r="H51">
+        <v>253</v>
+      </c>
+      <c r="I51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52">
+        <v>0.8556149732620321</v>
+      </c>
+      <c r="E52">
+        <v>0.8011363636363636</v>
+      </c>
+      <c r="F52">
+        <v>0.9039590823489129</v>
+      </c>
+      <c r="G52">
+        <v>253</v>
+      </c>
+      <c r="H52">
+        <v>253</v>
+      </c>
+      <c r="I52" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53">
+        <v>0.8616600790513834</v>
+      </c>
+      <c r="E53">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="F53">
+        <v>0.9011857707509882</v>
+      </c>
+      <c r="G53">
+        <v>253</v>
+      </c>
+      <c r="H53">
+        <v>253</v>
+      </c>
+      <c r="I53" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54">
+        <v>0.8616600790513834</v>
+      </c>
+      <c r="E54">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="F54">
+        <v>0.9011857707509882</v>
+      </c>
+      <c r="G54">
+        <v>253</v>
+      </c>
+      <c r="H54">
+        <v>253</v>
+      </c>
+      <c r="I54" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="E55">
+        <v>0.7786561264822134</v>
+      </c>
+      <c r="F55">
+        <v>0.8735177865612648</v>
+      </c>
+      <c r="G55">
+        <v>253</v>
+      </c>
+      <c r="H55">
+        <v>253</v>
+      </c>
+      <c r="I55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1878,43 +3502,43 @@
         <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" t="s">
-        <v>70</v>
-      </c>
       <c r="J1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="L1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="M1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1922,7 +3546,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>38</v>
@@ -1960,7 +3584,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
@@ -2004,7 +3628,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
@@ -2048,7 +3672,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -2092,7 +3716,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
         <v>38</v>
@@ -2136,7 +3760,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
@@ -2180,7 +3804,7 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -2218,7 +3842,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -2262,7 +3886,7 @@
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
@@ -2306,7 +3930,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
@@ -2350,7 +3974,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -2394,7 +4018,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
@@ -2438,7 +4062,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -2476,7 +4100,7 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -2520,7 +4144,7 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -2564,7 +4188,7 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
@@ -2608,7 +4232,7 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
@@ -2652,7 +4276,7 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
@@ -2696,7 +4320,7 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
         <v>38</v>
@@ -2723,7 +4347,7 @@
         <v>0.7589783551323271</v>
       </c>
       <c r="M20" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N20">
         <v>0.7589783551323271</v>
@@ -2734,7 +4358,7 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
         <v>38</v>
@@ -2772,7 +4396,7 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
@@ -2810,7 +4434,7 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
@@ -2837,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N23">
         <v>1</v>
@@ -2848,7 +4472,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -2875,7 +4499,7 @@
         <v>0.8311704095417624</v>
       </c>
       <c r="M24" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N24">
         <v>0.8311704095417624</v>
@@ -2886,7 +4510,7 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
@@ -2913,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -2924,7 +4548,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
         <v>38</v>
@@ -2951,7 +4575,7 @@
         <v>0.003869222643548615</v>
       </c>
       <c r="M26" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N26">
         <v>0.01160766793064584</v>
@@ -2962,7 +4586,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
         <v>38</v>
@@ -3000,7 +4624,7 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
         <v>38</v>
@@ -3038,7 +4662,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
         <v>38</v>
@@ -3065,7 +4689,7 @@
         <v>0.6055766163353462</v>
       </c>
       <c r="M29" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -3076,7 +4700,7 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
         <v>38</v>
@@ -3103,7 +4727,7 @@
         <v>0.02585758046344289</v>
       </c>
       <c r="M30" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N30">
         <v>0.05171516092688578</v>
@@ -3114,7 +4738,7 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>38</v>
@@ -3141,7 +4765,7 @@
         <v>0.02373851525005458</v>
       </c>
       <c r="M31" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N31">
         <v>0.04747703050010915</v>
@@ -3152,7 +4776,7 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
@@ -3179,7 +4803,7 @@
         <v>0.009812492570670151</v>
       </c>
       <c r="M32" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N32">
         <v>0.0196249851413403</v>
@@ -3190,7 +4814,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
@@ -3228,7 +4852,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
         <v>39</v>
@@ -3266,7 +4890,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
         <v>39</v>
@@ -3293,7 +4917,7 @@
         <v>0.8025873486341526</v>
       </c>
       <c r="M35" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -3304,7 +4928,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
         <v>39</v>
@@ -3331,7 +4955,7 @@
         <v>0.01480610912734845</v>
       </c>
       <c r="M36" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N36">
         <v>0.03878637069516434</v>
@@ -3342,7 +4966,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
         <v>39</v>
@@ -3369,7 +4993,7 @@
         <v>0.02227097895923274</v>
       </c>
       <c r="M37" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N37">
         <v>0.04454195791846547</v>
@@ -3380,7 +5004,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
@@ -3407,7 +5031,7 @@
         <v>0.1467487068347569</v>
       </c>
       <c r="M38" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N38">
         <v>0.1467487068347569</v>
@@ -3418,7 +5042,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>38</v>
@@ -3456,7 +5080,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
         <v>38</v>
@@ -3494,7 +5118,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
@@ -3521,7 +5145,7 @@
         <v>0.6463551955394902</v>
       </c>
       <c r="M41" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N41">
         <v>0.6463551955394902</v>
@@ -3532,7 +5156,7 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
@@ -3559,7 +5183,7 @@
         <v>0.6276258050283593</v>
       </c>
       <c r="M42" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N42">
         <v>0.8501067391385259</v>
@@ -3570,7 +5194,7 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
         <v>38</v>
@@ -3597,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -3608,7 +5232,7 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
         <v>38</v>
@@ -3635,7 +5259,7 @@
         <v>0.003403025345125086</v>
       </c>
       <c r="M44" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N44">
         <v>0.01020907603537526</v>
@@ -3646,7 +5270,7 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
         <v>38</v>
@@ -3684,7 +5308,7 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
         <v>38</v>
@@ -3722,7 +5346,7 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C47" t="s">
         <v>38</v>
@@ -3749,7 +5373,7 @@
         <v>0.2109029260566068</v>
       </c>
       <c r="M47" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N47">
         <v>0.6327087781698203</v>
@@ -3760,7 +5384,7 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C48" t="s">
         <v>38</v>
@@ -3787,7 +5411,7 @@
         <v>0.8501067391385259</v>
       </c>
       <c r="M48" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N48">
         <v>0.8501067391385259</v>
@@ -3798,7 +5422,7 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
         <v>38</v>
@@ -3825,7 +5449,7 @@
         <v>0.2626182904425174</v>
       </c>
       <c r="M49" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N49">
         <v>0.5252365808850348</v>
@@ -3836,7 +5460,7 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C50" t="s">
         <v>39</v>
@@ -3863,7 +5487,7 @@
         <v>0.04866005335540764</v>
       </c>
       <c r="M50" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="N50">
         <v>0.09732010671081527</v>
@@ -3874,7 +5498,7 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
         <v>39</v>
@@ -3912,7 +5536,7 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
         <v>39</v>
@@ -3950,7 +5574,7 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
         <v>39</v>
@@ -3977,7 +5601,7 @@
         <v>0.4795001221869534</v>
       </c>
       <c r="M53" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N53">
         <v>0.6463551955394902</v>
@@ -3988,7 +5612,7 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
         <v>39</v>
@@ -4015,7 +5639,7 @@
         <v>0.4576140668763148</v>
       </c>
       <c r="M54" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N54">
         <v>0.8501067391385259</v>
@@ -4026,7 +5650,7 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
         <v>39</v>
@@ -4053,7 +5677,7 @@
         <v>0.2432427057426535</v>
       </c>
       <c r="M55" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N55">
         <v>0.486485411485307</v>
@@ -4064,7 +5688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4074,49 +5698,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="P1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -4124,16 +5748,16 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F2">
         <v>516</v>
@@ -4157,16 +5781,16 @@
         <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -4174,16 +5798,16 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F3">
         <v>263</v>
@@ -4207,16 +5831,16 @@
         <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -4224,16 +5848,16 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F4">
         <v>253</v>
@@ -4257,16 +5881,16 @@
         <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_classifier_results.xlsx
+++ b/examples/example_classifier_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="142">
   <si>
     <t>Group</t>
   </si>
@@ -44,6 +44,12 @@
     <t>AUC Diff 95% CI high</t>
   </si>
   <si>
+    <t>AUC Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>AUC Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Obuchowski (AUC) p</t>
   </si>
   <si>
@@ -59,6 +65,12 @@
     <t>Brier Diff 95% CI high</t>
   </si>
   <si>
+    <t>Brier Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>Brier Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (Brier) p</t>
   </si>
   <si>
@@ -74,6 +86,12 @@
     <t>LogLoss Diff 95% CI high</t>
   </si>
   <si>
+    <t>LogLoss Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>LogLoss Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (LogLoss) p</t>
   </si>
   <si>
@@ -89,6 +107,12 @@
     <t>Sensitivity Diff 95% CI high</t>
   </si>
   <si>
+    <t>Sensitivity Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>Sensitivity Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Sensitivity p</t>
   </si>
   <si>
@@ -104,6 +128,12 @@
     <t>Specificity Diff 95% CI high</t>
   </si>
   <si>
+    <t>Specificity Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>Specificity Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Specificity p</t>
   </si>
   <si>
@@ -119,6 +149,12 @@
     <t>Accuracy Diff 95% CI high</t>
   </si>
   <si>
+    <t>Accuracy Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>Accuracy Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Accuracy p</t>
   </si>
   <si>
@@ -179,9 +215,18 @@
     <t>FWER Correction</t>
   </si>
   <si>
+    <t>Adjusted p-values (p_adj)</t>
+  </si>
+  <si>
+    <t>Adjusted Confidence Intervals</t>
+  </si>
+  <si>
     <t>Fellow-Eye Correlation</t>
   </si>
   <si>
+    <t>Subgroups</t>
+  </si>
+  <si>
     <t>Patient as the unit (cluster bootstrap / cluster-robust tests)</t>
   </si>
   <si>
@@ -203,9 +248,18 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Hommel: AUC, Sensitivity, Specificity, Accuracy; Romano-Wolf step-down: Brier Score, Log-Loss</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Bonferroni (normal theory, Obuchowski SE): AUC; Romano-Wolf simultaneous (max-|t|): Brier Score, Log-Loss; Bonferroni (percentile bootstrap): Sensitivity, Specificity, Accuracy. Brier score and log-loss: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). AUC: difference ± z × SE, z the normal quantile for coverage 1 - 0.05/m (Bonferroni). Sensitivity, specificity and accuracy: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+  </si>
+  <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
+    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings; p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
+  </si>
+  <si>
     <t>group</t>
   </si>
   <si>
@@ -287,12 +341,45 @@
     <t>p_adj</t>
   </si>
   <si>
+    <t>p_adj_method</t>
+  </si>
+  <si>
+    <t>ci_adj_low</t>
+  </si>
+  <si>
+    <t>ci_adj_high</t>
+  </si>
+  <si>
+    <t>ci_adj_method</t>
+  </si>
+  <si>
     <t>DeLong (1988)</t>
   </si>
   <si>
     <t>McNemar</t>
   </si>
   <si>
+    <t>Hommel</t>
+  </si>
+  <si>
+    <t>Romano-Wolf step-down</t>
+  </si>
+  <si>
+    <t>Bonferroni (normal theory, Obuchowski SE)</t>
+  </si>
+  <si>
+    <t>Romano-Wolf simultaneous (max-|t|)</t>
+  </si>
+  <si>
+    <t>Bonferroni (percentile bootstrap)</t>
+  </si>
+  <si>
+    <t>Bonferroni (normal theory, DeLong SE)</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
     <t>task</t>
   </si>
   <si>
@@ -330,6 +417,15 @@
   </si>
   <si>
     <t>fwer_method</t>
+  </si>
+  <si>
+    <t>All eyes: 516 eyes, 300 patients</t>
+  </si>
+  <si>
+    <t>eye = L: 263 eyes, 263 patients</t>
+  </si>
+  <si>
+    <t>eye = R: 253 eyes, 253 patients</t>
   </si>
   <si>
     <t>binary</t>
@@ -679,24 +775,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="22.7109375" customWidth="1"/>
-    <col min="9" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="13" width="22.7109375" customWidth="1"/>
-    <col min="14" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="18" width="22.7109375" customWidth="1"/>
-    <col min="19" max="20" width="15.7109375" customWidth="1"/>
-    <col min="21" max="23" width="22.7109375" customWidth="1"/>
-    <col min="24" max="25" width="15.7109375" customWidth="1"/>
-    <col min="26" max="28" width="22.7109375" customWidth="1"/>
-    <col min="29" max="30" width="15.7109375" customWidth="1"/>
-    <col min="31" max="33" width="22.7109375" customWidth="1"/>
-    <col min="34" max="35" width="15.7109375" customWidth="1"/>
+    <col min="1" max="10" width="22.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="17" width="22.7109375" customWidth="1"/>
+    <col min="18" max="19" width="15.7109375" customWidth="1"/>
+    <col min="20" max="24" width="22.7109375" customWidth="1"/>
+    <col min="25" max="26" width="15.7109375" customWidth="1"/>
+    <col min="27" max="31" width="22.7109375" customWidth="1"/>
+    <col min="32" max="33" width="15.7109375" customWidth="1"/>
+    <col min="34" max="38" width="22.7109375" customWidth="1"/>
+    <col min="39" max="40" width="15.7109375" customWidth="1"/>
+    <col min="41" max="45" width="22.7109375" customWidth="1"/>
+    <col min="46" max="47" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:47">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -802,16 +898,52 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:35">
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>516</v>
@@ -829,96 +961,132 @@
         <v>0.03269284363071832</v>
       </c>
       <c r="I2">
+        <v>-0.009547469685576918</v>
+      </c>
+      <c r="J2">
+        <v>0.03690350066479627</v>
+      </c>
+      <c r="K2">
         <v>0.1585783521869673</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>0.1585783521869673</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>-0.005671672015503809</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>-0.01696010224074354</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>0.006063415874129986</v>
       </c>
-      <c r="N2">
+      <c r="P2">
+        <v>-0.01950821088880687</v>
+      </c>
+      <c r="Q2">
+        <v>0.008164866857799255</v>
+      </c>
+      <c r="R2">
         <v>0.349</v>
       </c>
-      <c r="O2">
+      <c r="S2">
         <v>0.349</v>
       </c>
-      <c r="P2">
+      <c r="T2">
         <v>-0.01371940430766994</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>-0.04096857231250371</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <v>0.01379438013133473</v>
       </c>
-      <c r="S2">
+      <c r="W2">
+        <v>-0.04655890094471718</v>
+      </c>
+      <c r="X2">
+        <v>0.01912009232937731</v>
+      </c>
+      <c r="Y2">
         <v>0.3366</v>
       </c>
-      <c r="T2">
+      <c r="Z2">
         <v>0.3366</v>
       </c>
-      <c r="U2">
+      <c r="AA2">
         <v>0.02898550724637683</v>
       </c>
-      <c r="V2">
+      <c r="AB2">
         <v>-0.05263157894736842</v>
       </c>
-      <c r="W2">
+      <c r="AC2">
         <v>0.1134832366215345</v>
       </c>
-      <c r="X2">
+      <c r="AD2">
+        <v>-0.07142857142857142</v>
+      </c>
+      <c r="AE2">
+        <v>0.130241215008934</v>
+      </c>
+      <c r="AF2">
         <v>0.4938941871029767</v>
       </c>
-      <c r="Y2">
+      <c r="AG2">
         <v>0.4938941871029767</v>
       </c>
-      <c r="Z2">
+      <c r="AH2">
         <v>-0.01322751322751314</v>
       </c>
-      <c r="AA2">
+      <c r="AI2">
         <v>-0.04639490333476167</v>
       </c>
-      <c r="AB2">
+      <c r="AJ2">
         <v>0.02026352423192726</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
+        <v>-0.05426356589147287</v>
+      </c>
+      <c r="AL2">
+        <v>0.02761214074670986</v>
+      </c>
+      <c r="AM2">
         <v>0.4462239688329609</v>
       </c>
-      <c r="AD2">
+      <c r="AN2">
         <v>0.4462239688329609</v>
       </c>
-      <c r="AE2">
+      <c r="AO2">
         <v>-0.001937984496124034</v>
       </c>
-      <c r="AF2">
+      <c r="AP2">
         <v>-0.03475239539069325</v>
       </c>
-      <c r="AG2">
+      <c r="AQ2">
         <v>0.03125</v>
       </c>
-      <c r="AH2">
+      <c r="AR2">
+        <v>-0.04177596020833175</v>
+      </c>
+      <c r="AS2">
+        <v>0.03788432607331588</v>
+      </c>
+      <c r="AT2">
         <v>0.9094173748556938</v>
       </c>
-      <c r="AI2">
+      <c r="AU2">
         <v>0.9094173748556938</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:47">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>516</v>
@@ -936,96 +1104,132 @@
         <v>0.08836234224812071</v>
       </c>
       <c r="I3">
+        <v>0.02725895814217121</v>
+      </c>
+      <c r="J3">
+        <v>0.09445333385997573</v>
+      </c>
+      <c r="K3">
         <v>1.448835277480167E-05</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>4.346505832440501E-05</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>-0.03317717009689918</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>-0.0483943797631313</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>-0.01828621828652867</v>
       </c>
-      <c r="N3">
+      <c r="P3">
+        <v>-0.05126736698243801</v>
+      </c>
+      <c r="Q3">
+        <v>-0.01508697321136034</v>
+      </c>
+      <c r="R3">
         <v>0.0004</v>
-      </c>
-      <c r="O3">
-        <v>0.0004</v>
-      </c>
-      <c r="P3">
-        <v>-0.08053075738992366</v>
-      </c>
-      <c r="Q3">
-        <v>-0.1192318182347926</v>
-      </c>
-      <c r="R3">
-        <v>-0.04360054027952263</v>
       </c>
       <c r="S3">
         <v>0.0004</v>
       </c>
       <c r="T3">
+        <v>-0.08053075738992366</v>
+      </c>
+      <c r="U3">
+        <v>-0.1192318182347926</v>
+      </c>
+      <c r="V3">
+        <v>-0.04360054027952263</v>
+      </c>
+      <c r="W3">
+        <v>-0.1256862042172851</v>
+      </c>
+      <c r="X3">
+        <v>-0.03537531056256221</v>
+      </c>
+      <c r="Y3">
         <v>0.0004</v>
       </c>
-      <c r="U3">
+      <c r="Z3">
+        <v>0.0004</v>
+      </c>
+      <c r="AA3">
         <v>0.07246376811594202</v>
       </c>
-      <c r="V3">
+      <c r="AB3">
         <v>-0.01563115157480314</v>
       </c>
-      <c r="W3">
+      <c r="AC3">
         <v>0.1677441004546439</v>
       </c>
-      <c r="X3">
+      <c r="AD3">
+        <v>-0.03651368760064402</v>
+      </c>
+      <c r="AE3">
+        <v>0.1830387554082666</v>
+      </c>
+      <c r="AF3">
         <v>0.1144834666737794</v>
       </c>
-      <c r="Y3">
+      <c r="AG3">
         <v>0.3434504000213381</v>
       </c>
-      <c r="Z3">
+      <c r="AH3">
         <v>0.03968253968253976</v>
       </c>
-      <c r="AA3">
+      <c r="AI3">
         <v>0</v>
       </c>
-      <c r="AB3">
+      <c r="AJ3">
         <v>0.07859078590785908</v>
       </c>
-      <c r="AC3">
+      <c r="AK3">
+        <v>-0.005588512241054602</v>
+      </c>
+      <c r="AL3">
+        <v>0.08740359897172237</v>
+      </c>
+      <c r="AM3">
         <v>0.04645567201881207</v>
       </c>
-      <c r="AD3">
+      <c r="AN3">
         <v>0.09291134403762413</v>
       </c>
-      <c r="AE3">
+      <c r="AO3">
         <v>0.04844961240310075</v>
       </c>
-      <c r="AF3">
+      <c r="AP3">
         <v>0.01167201843526879</v>
       </c>
-      <c r="AG3">
+      <c r="AQ3">
         <v>0.08577835648148151</v>
       </c>
-      <c r="AH3">
+      <c r="AR3">
+        <v>0.003838771593090211</v>
+      </c>
+      <c r="AS3">
+        <v>0.09452543094275381</v>
+      </c>
+      <c r="AT3">
         <v>0.01094842344892238</v>
       </c>
-      <c r="AI3">
+      <c r="AU3">
         <v>0.02189684689784475</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:47">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>516</v>
@@ -1043,96 +1247,132 @@
         <v>0.07495351316857367</v>
       </c>
       <c r="I4">
+        <v>0.0132521474128741</v>
+      </c>
+      <c r="J4">
+        <v>0.0811041136100535</v>
+      </c>
+      <c r="K4">
         <v>0.0008712249487968415</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>0.001742449897593683</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>-0.02750549808139537</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>-0.04313435688609747</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>-0.01196780749470757</v>
       </c>
-      <c r="N4">
+      <c r="P4">
+        <v>-0.04617217904084742</v>
+      </c>
+      <c r="Q4">
+        <v>-0.008838817121943308</v>
+      </c>
+      <c r="R4">
         <v>0.0014</v>
       </c>
-      <c r="O4">
+      <c r="S4">
         <v>0.0018</v>
       </c>
-      <c r="P4">
+      <c r="T4">
         <v>-0.06681135308225372</v>
       </c>
-      <c r="Q4">
+      <c r="U4">
         <v>-0.1061917788999018</v>
       </c>
-      <c r="R4">
+      <c r="V4">
         <v>-0.02801716367843521</v>
       </c>
-      <c r="S4">
+      <c r="W4">
+        <v>-0.1131438348997234</v>
+      </c>
+      <c r="X4">
+        <v>-0.0204788712647841</v>
+      </c>
+      <c r="Y4">
         <v>0.0016</v>
       </c>
-      <c r="T4">
+      <c r="Z4">
         <v>0.0022</v>
       </c>
-      <c r="U4">
+      <c r="AA4">
         <v>0.04347826086956519</v>
       </c>
-      <c r="V4">
+      <c r="AB4">
         <v>-0.03821656050955414</v>
       </c>
-      <c r="W4">
+      <c r="AC4">
         <v>0.1268715944089079</v>
       </c>
-      <c r="X4">
+      <c r="AD4">
+        <v>-0.05569153069153064</v>
+      </c>
+      <c r="AE4">
+        <v>0.1481537875904076</v>
+      </c>
+      <c r="AF4">
         <v>0.3060346718543977</v>
       </c>
-      <c r="Y4">
+      <c r="AG4">
         <v>0.4938941871029767</v>
       </c>
-      <c r="Z4">
+      <c r="AH4">
         <v>0.05291005291005291</v>
       </c>
-      <c r="AA4">
+      <c r="AI4">
         <v>0.01312335958005249</v>
       </c>
-      <c r="AB4">
+      <c r="AJ4">
         <v>0.09230972194032881</v>
       </c>
-      <c r="AC4">
+      <c r="AK4">
+        <v>0.002741720565337171</v>
+      </c>
+      <c r="AL4">
+        <v>0.1029690177624242</v>
+      </c>
+      <c r="AM4">
         <v>0.01191397884158072</v>
       </c>
-      <c r="AD4">
+      <c r="AN4">
         <v>0.03574193652474216</v>
       </c>
-      <c r="AE4">
+      <c r="AO4">
         <v>0.05038759689922478</v>
       </c>
-      <c r="AF4">
+      <c r="AP4">
         <v>0.013670542458577</v>
       </c>
-      <c r="AG4">
+      <c r="AQ4">
         <v>0.08663281190468416</v>
       </c>
-      <c r="AH4">
+      <c r="AR4">
+        <v>0.005802707930367505</v>
+      </c>
+      <c r="AS4">
+        <v>0.09554657303978027</v>
+      </c>
+      <c r="AT4">
         <v>0.007770714070688979</v>
       </c>
-      <c r="AI4">
+      <c r="AU4">
         <v>0.01642263517338357</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:47">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>263</v>
@@ -1150,96 +1390,132 @@
         <v>0.022026282275109</v>
       </c>
       <c r="I5">
+        <v>-0.02028082889276633</v>
+      </c>
+      <c r="J5">
+        <v>0.02624359794454106</v>
+      </c>
+      <c r="K5">
         <v>0.7589783551323271</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>0.7589783551323271</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>0.003177452699619873</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-0.01107254006932483</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>0.01767353194661654</v>
       </c>
-      <c r="N5">
+      <c r="P5">
+        <v>-0.0142294328360232</v>
+      </c>
+      <c r="Q5">
+        <v>0.02058433823526295</v>
+      </c>
+      <c r="R5">
         <v>0.6637999999999999</v>
       </c>
-      <c r="O5">
+      <c r="S5">
         <v>0.6637999999999999</v>
       </c>
-      <c r="P5">
+      <c r="T5">
         <v>0.01086881864497791</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
         <v>-0.02212520523906435</v>
       </c>
-      <c r="R5">
+      <c r="V5">
         <v>0.04443815211367416</v>
       </c>
-      <c r="S5">
+      <c r="W5">
+        <v>-0.02924065294566617</v>
+      </c>
+      <c r="X5">
+        <v>0.05097829023562198</v>
+      </c>
+      <c r="Y5">
         <v>0.516</v>
       </c>
-      <c r="T5">
+      <c r="Z5">
         <v>0.516</v>
       </c>
-      <c r="U5">
+      <c r="AA5">
         <v>0.01388888888888884</v>
       </c>
-      <c r="V5">
+      <c r="AB5">
         <v>-0.08571428571428572</v>
       </c>
-      <c r="W5">
+      <c r="AC5">
         <v>0.1143091334894614</v>
       </c>
-      <c r="X5">
+      <c r="AD5">
+        <v>-0.1084520884520883</v>
+      </c>
+      <c r="AE5">
+        <v>0.1354452054794529</v>
+      </c>
+      <c r="AF5">
         <v>1</v>
       </c>
-      <c r="Y5">
+      <c r="AG5">
         <v>1</v>
       </c>
-      <c r="Z5">
+      <c r="AH5">
         <v>-0.01047120418848169</v>
       </c>
-      <c r="AA5">
+      <c r="AI5">
         <v>-0.05913978494623656</v>
       </c>
-      <c r="AB5">
+      <c r="AJ5">
         <v>0.03685185185185189</v>
       </c>
-      <c r="AC5">
+      <c r="AK5">
+        <v>-0.06964953136679887</v>
+      </c>
+      <c r="AL5">
+        <v>0.04973337731233337</v>
+      </c>
+      <c r="AM5">
         <v>0.8311704095417624</v>
       </c>
-      <c r="AD5">
+      <c r="AN5">
         <v>0.8311704095417624</v>
       </c>
-      <c r="AE5">
+      <c r="AO5">
         <v>-0.003802281368821325</v>
       </c>
-      <c r="AF5">
+      <c r="AP5">
         <v>-0.04562737642585551</v>
       </c>
-      <c r="AG5">
+      <c r="AQ5">
         <v>0.04182509505703422</v>
       </c>
-      <c r="AH5">
+      <c r="AR5">
+        <v>-0.05703422053231939</v>
+      </c>
+      <c r="AS5">
+        <v>0.04942965779467681</v>
+      </c>
+      <c r="AT5">
         <v>1</v>
       </c>
-      <c r="AI5">
+      <c r="AU5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:47">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>263</v>
@@ -1257,96 +1533,132 @@
         <v>0.08421841033082253</v>
       </c>
       <c r="I6">
+        <v>0.00859192659616724</v>
+      </c>
+      <c r="J6">
+        <v>0.09175711354344908</v>
+      </c>
+      <c r="K6">
         <v>0.003869222643548615</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>0.01160766793064584</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>-0.03326987737642581</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>-0.05333303837337318</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>-0.01403268008184253</v>
       </c>
-      <c r="N6">
+      <c r="P6">
+        <v>-0.05724448040629365</v>
+      </c>
+      <c r="Q6">
+        <v>-0.009295274346557969</v>
+      </c>
+      <c r="R6">
         <v>0.0032</v>
       </c>
-      <c r="O6">
+      <c r="S6">
         <v>0.006</v>
       </c>
-      <c r="P6">
+      <c r="T6">
         <v>-0.07457165389245912</v>
       </c>
-      <c r="Q6">
+      <c r="U6">
         <v>-0.1233238778955756</v>
       </c>
-      <c r="R6">
+      <c r="V6">
         <v>-0.02701278723372434</v>
       </c>
-      <c r="S6">
+      <c r="W6">
+        <v>-0.1321164458071846</v>
+      </c>
+      <c r="X6">
+        <v>-0.01702686197773369</v>
+      </c>
+      <c r="Y6">
         <v>0.0056</v>
       </c>
-      <c r="T6">
+      <c r="Z6">
         <v>0.0108</v>
       </c>
-      <c r="U6">
+      <c r="AA6">
         <v>0.04166666666666663</v>
       </c>
-      <c r="V6">
+      <c r="AB6">
         <v>-0.06451612903225806</v>
       </c>
-      <c r="W6">
+      <c r="AC6">
         <v>0.1470588235294118</v>
       </c>
-      <c r="X6">
+      <c r="AD6">
+        <v>-0.08893822029095019</v>
+      </c>
+      <c r="AE6">
+        <v>0.171875</v>
+      </c>
+      <c r="AF6">
         <v>0.6055766163353462</v>
       </c>
-      <c r="Y6">
+      <c r="AG6">
         <v>1</v>
       </c>
-      <c r="Z6">
+      <c r="AH6">
         <v>0.06806282722513091</v>
       </c>
-      <c r="AA6">
+      <c r="AI6">
         <v>0.0154639175257732</v>
       </c>
-      <c r="AB6">
+      <c r="AJ6">
         <v>0.1237113402061856</v>
       </c>
-      <c r="AC6">
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0.1371632174931668</v>
+      </c>
+      <c r="AM6">
         <v>0.02585758046344289</v>
       </c>
-      <c r="AD6">
+      <c r="AN6">
         <v>0.05171516092688578</v>
       </c>
-      <c r="AE6">
+      <c r="AO6">
         <v>0.06083650190114065</v>
       </c>
-      <c r="AF6">
+      <c r="AP6">
         <v>0.01140684410646388</v>
       </c>
-      <c r="AG6">
+      <c r="AQ6">
         <v>0.1102661596958175</v>
       </c>
-      <c r="AH6">
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0.1216730038022814</v>
+      </c>
+      <c r="AT6">
         <v>0.02373851525005458</v>
       </c>
-      <c r="AI6">
+      <c r="AU6">
         <v>0.04747703050010915</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:47">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>263</v>
@@ -1364,96 +1676,132 @@
         <v>0.08301175254021582</v>
       </c>
       <c r="I7">
+        <v>0.003442818587617621</v>
+      </c>
+      <c r="J7">
+        <v>0.09094345250022397</v>
+      </c>
+      <c r="K7">
         <v>0.009812492570670151</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>0.0196249851413403</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>-0.03644733007604568</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>-0.05932266260572364</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>-0.01460453971831455</v>
       </c>
-      <c r="N7">
+      <c r="P7">
+        <v>-0.063099354823316</v>
+      </c>
+      <c r="Q7">
+        <v>-0.009795305328775369</v>
+      </c>
+      <c r="R7">
         <v>0.0016</v>
       </c>
-      <c r="O7">
+      <c r="S7">
         <v>0.006</v>
       </c>
-      <c r="P7">
+      <c r="T7">
         <v>-0.08544047253743703</v>
       </c>
-      <c r="Q7">
+      <c r="U7">
         <v>-0.1406807097413394</v>
       </c>
-      <c r="R7">
+      <c r="V7">
         <v>-0.03111577025431145</v>
       </c>
-      <c r="S7">
+      <c r="W7">
+        <v>-0.1494866851663962</v>
+      </c>
+      <c r="X7">
+        <v>-0.02139425990847783</v>
+      </c>
+      <c r="Y7">
         <v>0.002</v>
       </c>
-      <c r="T7">
+      <c r="Z7">
         <v>0.008399999999999999</v>
       </c>
-      <c r="U7">
+      <c r="AA7">
         <v>0.02777777777777779</v>
       </c>
-      <c r="V7">
+      <c r="AB7">
         <v>-0.07692307692307693</v>
       </c>
-      <c r="W7">
+      <c r="AC7">
         <v>0.1375</v>
       </c>
-      <c r="X7">
+      <c r="AD7">
+        <v>-0.1036050156739811</v>
+      </c>
+      <c r="AE7">
+        <v>0.1643835616438356</v>
+      </c>
+      <c r="AF7">
         <v>0.8025873486341526</v>
       </c>
-      <c r="Y7">
+      <c r="AG7">
         <v>1</v>
       </c>
-      <c r="Z7">
+      <c r="AH7">
         <v>0.07853403141361259</v>
       </c>
-      <c r="AA7">
+      <c r="AI7">
         <v>0.02093695462478186</v>
       </c>
-      <c r="AB7">
+      <c r="AJ7">
         <v>0.1358722034613761</v>
       </c>
-      <c r="AC7">
+      <c r="AK7">
+        <v>0.01025641025641026</v>
+      </c>
+      <c r="AL7">
+        <v>0.1530566801619438</v>
+      </c>
+      <c r="AM7">
         <v>0.01480610912734845</v>
       </c>
-      <c r="AD7">
+      <c r="AN7">
         <v>0.03878637069516434</v>
       </c>
-      <c r="AE7">
+      <c r="AO7">
         <v>0.06463878326996197</v>
       </c>
-      <c r="AF7">
+      <c r="AP7">
         <v>0.01140684410646388</v>
       </c>
-      <c r="AG7">
+      <c r="AQ7">
         <v>0.1178707224334601</v>
       </c>
-      <c r="AH7">
+      <c r="AR7">
+        <v>0.003802281368821293</v>
+      </c>
+      <c r="AS7">
+        <v>0.1254752851711027</v>
+      </c>
+      <c r="AT7">
         <v>0.02227097895923274</v>
       </c>
-      <c r="AI7">
+      <c r="AU7">
         <v>0.04454195791846547</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:47">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>253</v>
@@ -1471,96 +1819,132 @@
         <v>0.0572333825399616</v>
       </c>
       <c r="I8">
+        <v>-0.01582008783175719</v>
+      </c>
+      <c r="J8">
+        <v>0.06451559909411336</v>
+      </c>
+      <c r="K8">
         <v>0.1467487068347569</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>0.1467487068347569</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>-0.01487056450592883</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>-0.03288227345609322</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>0.003186446569978699</v>
       </c>
-      <c r="N8">
+      <c r="P8">
+        <v>-0.03571830630142864</v>
+      </c>
+      <c r="Q8">
+        <v>0.005977177289570985</v>
+      </c>
+      <c r="R8">
         <v>0.1052</v>
       </c>
-      <c r="O8">
+      <c r="S8">
         <v>0.1868</v>
       </c>
-      <c r="P8">
+      <c r="T8">
         <v>-0.03927949378018425</v>
       </c>
-      <c r="Q8">
+      <c r="U8">
         <v>-0.08396634944318943</v>
       </c>
-      <c r="R8">
+      <c r="V8">
         <v>0.003910375492078746</v>
       </c>
-      <c r="S8">
+      <c r="W8">
+        <v>-0.08982206866643555</v>
+      </c>
+      <c r="X8">
+        <v>0.01126308110606705</v>
+      </c>
+      <c r="Y8">
         <v>0.07779999999999999</v>
       </c>
-      <c r="T8">
+      <c r="Z8">
         <v>0.1416</v>
       </c>
-      <c r="U8">
+      <c r="AA8">
         <v>0.04545454545454553</v>
       </c>
-      <c r="V8">
+      <c r="AB8">
         <v>-0.0847457627118644</v>
       </c>
-      <c r="W8">
+      <c r="AC8">
         <v>0.1739130434782609</v>
       </c>
-      <c r="X8">
+      <c r="AD8">
+        <v>-0.1131249999999998</v>
+      </c>
+      <c r="AE8">
+        <v>0.2034996861268049</v>
+      </c>
+      <c r="AF8">
         <v>0.6463551955394902</v>
       </c>
-      <c r="Y8">
+      <c r="AG8">
         <v>0.6463551955394902</v>
       </c>
-      <c r="Z8">
+      <c r="AH8">
         <v>-0.01604278074866305</v>
       </c>
-      <c r="AA8">
+      <c r="AI8">
         <v>-0.05945945945945946</v>
       </c>
-      <c r="AB8">
+      <c r="AJ8">
         <v>0.02660285584253046</v>
       </c>
-      <c r="AC8">
+      <c r="AK8">
+        <v>-0.07119289340101519</v>
+      </c>
+      <c r="AL8">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AM8">
         <v>0.6276258050283593</v>
       </c>
-      <c r="AD8">
+      <c r="AN8">
         <v>0.8501067391385259</v>
       </c>
-      <c r="AE8">
+      <c r="AO8">
         <v>0</v>
       </c>
-      <c r="AF8">
+      <c r="AP8">
         <v>-0.04743083003952569</v>
       </c>
-      <c r="AG8">
+      <c r="AQ8">
         <v>0.04743083003952569</v>
       </c>
-      <c r="AH8">
+      <c r="AR8">
+        <v>-0.05533596837944664</v>
+      </c>
+      <c r="AS8">
+        <v>0.05533596837944664</v>
+      </c>
+      <c r="AT8">
         <v>1</v>
       </c>
-      <c r="AI8">
+      <c r="AU8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:47">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>253</v>
@@ -1578,96 +1962,132 @@
         <v>0.11732616761233</v>
       </c>
       <c r="I9">
+        <v>0.01283465784607815</v>
+      </c>
+      <c r="J9">
+        <v>0.127742234067712</v>
+      </c>
+      <c r="K9">
         <v>0.003403025345125086</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>0.01020907603537526</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-0.03308079849802376</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-0.05855212414881788</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>-0.01034818093491874</v>
       </c>
-      <c r="N9">
+      <c r="P9">
+        <v>-0.06143081418824267</v>
+      </c>
+      <c r="Q9">
+        <v>-0.004730782807804843</v>
+      </c>
+      <c r="R9">
         <v>0.007</v>
       </c>
-      <c r="O9">
+      <c r="S9">
         <v>0.0166</v>
       </c>
-      <c r="P9">
+      <c r="T9">
         <v>-0.08672539857503453</v>
       </c>
-      <c r="Q9">
+      <c r="U9">
         <v>-0.1531605520737868</v>
       </c>
-      <c r="R9">
+      <c r="V9">
         <v>-0.03011349316215359</v>
       </c>
-      <c r="S9">
+      <c r="W9">
+        <v>-0.1592997954158392</v>
+      </c>
+      <c r="X9">
+        <v>-0.01415100173422988</v>
+      </c>
+      <c r="Y9">
         <v>0.007</v>
       </c>
-      <c r="T9">
+      <c r="Z9">
         <v>0.0138</v>
       </c>
-      <c r="U9">
+      <c r="AA9">
         <v>0.1060606060606061</v>
       </c>
-      <c r="V9">
+      <c r="AB9">
         <v>-0.03947368421052631</v>
       </c>
-      <c r="W9">
+      <c r="AC9">
         <v>0.2424242424242424</v>
       </c>
-      <c r="X9">
+      <c r="AD9">
+        <v>-0.07352941176470588</v>
+      </c>
+      <c r="AE9">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="AF9">
         <v>0.2109029260566068</v>
       </c>
-      <c r="Y9">
+      <c r="AG9">
         <v>0.6327087781698203</v>
       </c>
-      <c r="Z9">
+      <c r="AH9">
         <v>0.01069518716577544</v>
       </c>
-      <c r="AA9">
+      <c r="AI9">
         <v>-0.04591836734693878</v>
       </c>
-      <c r="AB9">
+      <c r="AJ9">
         <v>0.06595227976443453</v>
       </c>
-      <c r="AC9">
+      <c r="AK9">
+        <v>-0.05615820998675333</v>
+      </c>
+      <c r="AL9">
+        <v>0.07951283350219536</v>
+      </c>
+      <c r="AM9">
         <v>0.8501067391385259</v>
       </c>
-      <c r="AD9">
+      <c r="AN9">
         <v>0.8501067391385259</v>
       </c>
-      <c r="AE9">
+      <c r="AO9">
         <v>0.03557312252964429</v>
       </c>
-      <c r="AF9">
+      <c r="AP9">
         <v>-0.01976284584980237</v>
       </c>
-      <c r="AG9">
+      <c r="AQ9">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AH9">
+      <c r="AR9">
+        <v>-0.03162055335968379</v>
+      </c>
+      <c r="AS9">
+        <v>0.1001976284584995</v>
+      </c>
+      <c r="AT9">
         <v>0.2626182904425174</v>
       </c>
-      <c r="AI9">
+      <c r="AU9">
         <v>0.5252365808850348</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:47">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>253</v>
@@ -1685,84 +2105,120 @@
         <v>0.09161121359083908</v>
       </c>
       <c r="I10">
+        <v>-0.009843146013245659</v>
+      </c>
+      <c r="J10">
+        <v>0.1017245266646797</v>
+      </c>
+      <c r="K10">
         <v>0.04866005335540764</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.09732010671081527</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-0.01821023399209493</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-0.04208292671189801</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>0.00481220577491211</v>
       </c>
-      <c r="N10">
+      <c r="P10">
+        <v>-0.0459950736638484</v>
+      </c>
+      <c r="Q10">
+        <v>0.009574605679658545</v>
+      </c>
+      <c r="R10">
         <v>0.1366</v>
       </c>
-      <c r="O10">
+      <c r="S10">
         <v>0.1868</v>
       </c>
-      <c r="P10">
+      <c r="T10">
         <v>-0.04744590479485028</v>
       </c>
-      <c r="Q10">
+      <c r="U10">
         <v>-0.1062323134937177</v>
       </c>
-      <c r="R10">
+      <c r="V10">
         <v>0.01013852501960102</v>
       </c>
-      <c r="S10">
+      <c r="W10">
+        <v>-0.1179283647360767</v>
+      </c>
+      <c r="X10">
+        <v>0.02303655514637615</v>
+      </c>
+      <c r="Y10">
         <v>0.1234</v>
       </c>
-      <c r="T10">
+      <c r="Z10">
         <v>0.1416</v>
       </c>
-      <c r="U10">
+      <c r="AA10">
         <v>0.06060606060606055</v>
       </c>
-      <c r="V10">
+      <c r="AB10">
         <v>-0.0625</v>
       </c>
-      <c r="W10">
+      <c r="AC10">
         <v>0.1864406779661017</v>
       </c>
-      <c r="X10">
+      <c r="AD10">
+        <v>-0.09015151515151501</v>
+      </c>
+      <c r="AE10">
+        <v>0.213666666666667</v>
+      </c>
+      <c r="AF10">
         <v>0.4795001221869534</v>
       </c>
-      <c r="Y10">
+      <c r="AG10">
         <v>0.6463551955394902</v>
       </c>
-      <c r="Z10">
+      <c r="AH10">
         <v>0.0267379679144385</v>
       </c>
-      <c r="AA10">
+      <c r="AI10">
         <v>-0.02748011656851434</v>
       </c>
-      <c r="AB10">
+      <c r="AJ10">
         <v>0.0855763517528224</v>
       </c>
-      <c r="AC10">
+      <c r="AK10">
+        <v>-0.04218323586744636</v>
+      </c>
+      <c r="AL10">
+        <v>0.09913967059336842</v>
+      </c>
+      <c r="AM10">
         <v>0.4576140668763148</v>
       </c>
-      <c r="AD10">
+      <c r="AN10">
         <v>0.8501067391385259</v>
       </c>
-      <c r="AE10">
+      <c r="AO10">
         <v>0.03557312252964429</v>
       </c>
-      <c r="AF10">
+      <c r="AP10">
         <v>-0.0158102766798419</v>
       </c>
-      <c r="AG10">
+      <c r="AQ10">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AH10">
+      <c r="AR10">
+        <v>-0.02766798418972332</v>
+      </c>
+      <c r="AS10">
+        <v>0.1001976284584995</v>
+      </c>
+      <c r="AT10">
         <v>0.2432427057426535</v>
       </c>
-      <c r="AI10">
+      <c r="AU10">
         <v>0.486485411485307</v>
       </c>
     </row>
@@ -1773,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1782,98 +2238,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1891,42 +2371,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D2">
         <v>0.9497450348899624</v>
@@ -1944,18 +2424,18 @@
         <v>300</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D3">
         <v>0.9360670194003528</v>
@@ -1973,18 +2453,18 @@
         <v>300</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>0.888888888888889</v>
@@ -2002,18 +2482,18 @@
         <v>300</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>0.09039919269379845</v>
@@ -2031,18 +2511,18 @@
         <v>300</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>0.09607086470930232</v>
@@ -2060,18 +2540,18 @@
         <v>300</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D7">
         <v>0.1235763627906977</v>
@@ -2089,18 +2569,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D8">
         <v>0.3017094343669053</v>
@@ -2118,18 +2598,18 @@
         <v>300</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D9">
         <v>0.3154288386745746</v>
@@ -2147,18 +2627,18 @@
         <v>300</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D10">
         <v>0.3822401917568288</v>
@@ -2176,18 +2656,18 @@
         <v>300</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D11">
         <v>0.8333333333333334</v>
@@ -2205,18 +2685,18 @@
         <v>300</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D12">
         <v>0.8043478260869565</v>
@@ -2234,18 +2714,18 @@
         <v>300</v>
       </c>
       <c r="I12" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D13">
         <v>0.7608695652173914</v>
@@ -2263,18 +2743,18 @@
         <v>300</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D14">
         <v>0.8862433862433863</v>
@@ -2292,18 +2772,18 @@
         <v>300</v>
       </c>
       <c r="I14" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D15">
         <v>0.8994708994708994</v>
@@ -2321,18 +2801,18 @@
         <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D16">
         <v>0.8465608465608465</v>
@@ -2350,18 +2830,18 @@
         <v>300</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D17">
         <v>0.8720930232558139</v>
@@ -2379,18 +2859,18 @@
         <v>300</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D18">
         <v>0.874031007751938</v>
@@ -2408,18 +2888,18 @@
         <v>300</v>
       </c>
       <c r="I18" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D19">
         <v>0.8236434108527132</v>
@@ -2437,18 +2917,18 @@
         <v>300</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D20">
         <v>0.9572425828970333</v>
@@ -2466,18 +2946,18 @@
         <v>263</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D21">
         <v>0.954261198371146</v>
@@ -2495,18 +2975,18 @@
         <v>263</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D22">
         <v>0.9070680628272252</v>
@@ -2524,18 +3004,18 @@
         <v>263</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D23">
         <v>0.08409677600760457</v>
@@ -2553,18 +3033,18 @@
         <v>263</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>0.08091932330798481</v>
@@ -2582,18 +3062,18 @@
         <v>263</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D25">
         <v>0.1173666533840304</v>
@@ -2611,18 +3091,18 @@
         <v>263</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D26">
         <v>0.2869453687617093</v>
@@ -2640,18 +3120,18 @@
         <v>263</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D27">
         <v>0.2760765501167315</v>
@@ -2669,18 +3149,18 @@
         <v>263</v>
       </c>
       <c r="I27" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D28">
         <v>0.3615170226541689</v>
@@ -2698,18 +3178,18 @@
         <v>263</v>
       </c>
       <c r="I28" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D29">
         <v>0.8194444444444444</v>
@@ -2727,18 +3207,18 @@
         <v>263</v>
       </c>
       <c r="I29" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D30">
         <v>0.8055555555555556</v>
@@ -2756,18 +3236,18 @@
         <v>263</v>
       </c>
       <c r="I30" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D31">
         <v>0.7777777777777778</v>
@@ -2785,18 +3265,18 @@
         <v>263</v>
       </c>
       <c r="I31" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D32">
         <v>0.9057591623036649</v>
@@ -2814,18 +3294,18 @@
         <v>263</v>
       </c>
       <c r="I32" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D33">
         <v>0.9162303664921466</v>
@@ -2843,18 +3323,18 @@
         <v>263</v>
       </c>
       <c r="I33" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D34">
         <v>0.837696335078534</v>
@@ -2872,18 +3352,18 @@
         <v>263</v>
       </c>
       <c r="I34" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D35">
         <v>0.8821292775665399</v>
@@ -2901,18 +3381,18 @@
         <v>263</v>
       </c>
       <c r="I35" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D36">
         <v>0.8859315589353612</v>
@@ -2930,18 +3410,18 @@
         <v>263</v>
       </c>
       <c r="I36" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D37">
         <v>0.8212927756653993</v>
@@ -2959,18 +3439,18 @@
         <v>263</v>
       </c>
       <c r="I37" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D38">
         <v>0.9407308377896613</v>
@@ -2988,18 +3468,18 @@
         <v>253</v>
       </c>
       <c r="I38" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D39">
         <v>0.9163830821584832</v>
@@ -3017,18 +3497,18 @@
         <v>253</v>
       </c>
       <c r="I39" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D40">
         <v>0.8704423918327662</v>
@@ -3046,18 +3526,18 @@
         <v>253</v>
       </c>
       <c r="I40" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D41">
         <v>0.09695071675889329</v>
@@ -3075,18 +3555,18 @@
         <v>253</v>
       </c>
       <c r="I41" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D42">
         <v>0.1118212812648221</v>
@@ -3104,18 +3584,18 @@
         <v>253</v>
       </c>
       <c r="I42" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D43">
         <v>0.130031515256917</v>
@@ -3133,18 +3613,18 @@
         <v>253</v>
       </c>
       <c r="I43" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D44">
         <v>0.317057059877445</v>
@@ -3162,18 +3642,18 @@
         <v>253</v>
       </c>
       <c r="I44" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D45">
         <v>0.3563365536576291</v>
@@ -3191,18 +3671,18 @@
         <v>253</v>
       </c>
       <c r="I45" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D46">
         <v>0.4037824584524792</v>
@@ -3220,18 +3700,18 @@
         <v>253</v>
       </c>
       <c r="I46" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D47">
         <v>0.8484848484848485</v>
@@ -3249,18 +3729,18 @@
         <v>253</v>
       </c>
       <c r="I47" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D48">
         <v>0.803030303030303</v>
@@ -3278,18 +3758,18 @@
         <v>253</v>
       </c>
       <c r="I48" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D49">
         <v>0.7424242424242424</v>
@@ -3307,18 +3787,18 @@
         <v>253</v>
       </c>
       <c r="I49" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D50">
         <v>0.8663101604278075</v>
@@ -3336,18 +3816,18 @@
         <v>253</v>
       </c>
       <c r="I50" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D51">
         <v>0.8823529411764706</v>
@@ -3365,18 +3845,18 @@
         <v>253</v>
       </c>
       <c r="I51" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D52">
         <v>0.8556149732620321</v>
@@ -3394,18 +3874,18 @@
         <v>253</v>
       </c>
       <c r="I52" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D53">
         <v>0.8616600790513834</v>
@@ -3423,18 +3903,18 @@
         <v>253</v>
       </c>
       <c r="I53" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D54">
         <v>0.8616600790513834</v>
@@ -3452,18 +3932,18 @@
         <v>253</v>
       </c>
       <c r="I54" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D55">
         <v>0.8260869565217391</v>
@@ -3481,7 +3961,7 @@
         <v>253</v>
       </c>
       <c r="I55" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3491,68 +3971,85 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="12" width="18.7109375" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
+    <col min="15" max="15" width="36.7109375" customWidth="1"/>
+    <col min="16" max="17" width="18.7109375" customWidth="1"/>
+    <col min="18" max="18" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K1" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="L1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="M1" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>106</v>
+      </c>
+      <c r="O1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P1" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>109</v>
+      </c>
+      <c r="R1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2">
         <v>0.9497450348899624</v>
@@ -3573,24 +4070,36 @@
         <v>0.1585783521869673</v>
       </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N2">
         <v>0.1585783521869673</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2">
+        <v>-0.009547469685576918</v>
+      </c>
+      <c r="Q2">
+        <v>0.03690350066479627</v>
+      </c>
+      <c r="R2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>0.09039919269379848</v>
@@ -3617,24 +4126,36 @@
         <v>1.637225445824592</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N3">
         <v>0.349</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3">
+        <v>-0.01950821088880687</v>
+      </c>
+      <c r="Q3">
+        <v>0.008164866857799255</v>
+      </c>
+      <c r="R3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E4">
         <v>0.3017094343669052</v>
@@ -3661,24 +4182,36 @@
         <v>1.658750048532445</v>
       </c>
       <c r="M4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N4">
         <v>0.3366</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>114</v>
+      </c>
+      <c r="P4">
+        <v>-0.04655890094471718</v>
+      </c>
+      <c r="Q4">
+        <v>0.01912009232937731</v>
+      </c>
+      <c r="R4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>0.8333333333333334</v>
@@ -3705,24 +4238,36 @@
         <v>1.1714295204668</v>
       </c>
       <c r="M5" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N5">
         <v>0.4938941871029767</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5">
+        <v>-0.07142857142857142</v>
+      </c>
+      <c r="Q5">
+        <v>0.130241215008934</v>
+      </c>
+      <c r="R5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>0.8862433862433863</v>
@@ -3749,24 +4294,36 @@
         <v>1.400632776710893</v>
       </c>
       <c r="M6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N6">
         <v>0.4462239688329609</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P6">
+        <v>-0.05426356589147287</v>
+      </c>
+      <c r="Q6">
+        <v>0.02761214074670986</v>
+      </c>
+      <c r="R6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>0.8720930232558139</v>
@@ -3793,24 +4350,36 @@
         <v>1.586004072823823</v>
       </c>
       <c r="M7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N7">
         <v>0.9094173748556938</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>113</v>
+      </c>
+      <c r="P7">
+        <v>-0.04177596020833175</v>
+      </c>
+      <c r="Q7">
+        <v>0.03788432607331588</v>
+      </c>
+      <c r="R7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E8">
         <v>0.9497450348899624</v>
@@ -3831,24 +4400,36 @@
         <v>1.448835277480167E-05</v>
       </c>
       <c r="M8" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N8">
         <v>4.346505832440501E-05</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>113</v>
+      </c>
+      <c r="P8">
+        <v>0.02725895814217121</v>
+      </c>
+      <c r="Q8">
+        <v>0.09445333385997573</v>
+      </c>
+      <c r="R8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E9">
         <v>0.09039919269379848</v>
@@ -3875,24 +4456,36 @@
         <v>1.72</v>
       </c>
       <c r="M9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N9">
         <v>0.0004</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>114</v>
+      </c>
+      <c r="P9">
+        <v>-0.05126736698243801</v>
+      </c>
+      <c r="Q9">
+        <v>-0.01508697321136034</v>
+      </c>
+      <c r="R9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E10">
         <v>0.3017094343669052</v>
@@ -3919,24 +4512,36 @@
         <v>1.72</v>
       </c>
       <c r="M10" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N10">
         <v>0.0004</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>114</v>
+      </c>
+      <c r="P10">
+        <v>-0.1256862042172851</v>
+      </c>
+      <c r="Q10">
+        <v>-0.03537531056256221</v>
+      </c>
+      <c r="R10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>0.8333333333333334</v>
@@ -3963,24 +4568,36 @@
         <v>1.188514823808941</v>
       </c>
       <c r="M11" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N11">
         <v>0.3434504000213381</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>113</v>
+      </c>
+      <c r="P11">
+        <v>-0.03651368760064402</v>
+      </c>
+      <c r="Q11">
+        <v>0.1830387554082666</v>
+      </c>
+      <c r="R11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>0.8862433862433863</v>
@@ -4007,24 +4624,36 @@
         <v>1.542857142857143</v>
       </c>
       <c r="M12" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N12">
         <v>0.09291134403762413</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12">
+        <v>-0.005588512241054602</v>
+      </c>
+      <c r="Q12">
+        <v>0.08740359897172237</v>
+      </c>
+      <c r="R12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>0.8720930232558139</v>
@@ -4051,24 +4680,36 @@
         <v>1.702106891515892</v>
       </c>
       <c r="M13" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N13">
         <v>0.02189684689784475</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>113</v>
+      </c>
+      <c r="P13">
+        <v>0.003838771593090211</v>
+      </c>
+      <c r="Q13">
+        <v>0.09452543094275381</v>
+      </c>
+      <c r="R13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>0.9360670194003528</v>
@@ -4089,24 +4730,36 @@
         <v>0.0008712249487968415</v>
       </c>
       <c r="M14" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N14">
         <v>0.001742449897593683</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P14">
+        <v>0.0132521474128741</v>
+      </c>
+      <c r="Q14">
+        <v>0.0811041136100535</v>
+      </c>
+      <c r="R14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>0.09607086470930229</v>
@@ -4133,24 +4786,36 @@
         <v>1.72</v>
       </c>
       <c r="M15" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N15">
         <v>0.0018</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>114</v>
+      </c>
+      <c r="P15">
+        <v>-0.04617217904084742</v>
+      </c>
+      <c r="Q15">
+        <v>-0.008838817121943308</v>
+      </c>
+      <c r="R15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E16">
         <v>0.3154288386745751</v>
@@ -4177,24 +4842,36 @@
         <v>1.72</v>
       </c>
       <c r="M16" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N16">
         <v>0.0022</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>114</v>
+      </c>
+      <c r="P16">
+        <v>-0.1131438348997234</v>
+      </c>
+      <c r="Q16">
+        <v>-0.0204788712647841</v>
+      </c>
+      <c r="R16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E17">
         <v>0.8043478260869565</v>
@@ -4221,24 +4898,36 @@
         <v>1.243243243243243</v>
       </c>
       <c r="M17" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N17">
         <v>0.4938941871029767</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>113</v>
+      </c>
+      <c r="P17">
+        <v>-0.05569153069153064</v>
+      </c>
+      <c r="Q17">
+        <v>0.1481537875904076</v>
+      </c>
+      <c r="R17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>0.8994708994708994</v>
@@ -4265,24 +4954,36 @@
         <v>1.511717281558992</v>
       </c>
       <c r="M18" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N18">
         <v>0.03574193652474216</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>113</v>
+      </c>
+      <c r="P18">
+        <v>0.002741720565337171</v>
+      </c>
+      <c r="Q18">
+        <v>0.1029690177624242</v>
+      </c>
+      <c r="R18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>0.874031007751938</v>
@@ -4309,24 +5010,36 @@
         <v>1.72</v>
       </c>
       <c r="M19" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N19">
         <v>0.01642263517338357</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>113</v>
+      </c>
+      <c r="P19">
+        <v>0.005802707930367505</v>
+      </c>
+      <c r="Q19">
+        <v>0.09554657303978027</v>
+      </c>
+      <c r="R19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E20">
         <v>0.9572425828970333</v>
@@ -4347,24 +5060,36 @@
         <v>0.7589783551323271</v>
       </c>
       <c r="M20" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N20">
         <v>0.7589783551323271</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>113</v>
+      </c>
+      <c r="P20">
+        <v>-0.02028082889276633</v>
+      </c>
+      <c r="Q20">
+        <v>0.02624359794454106</v>
+      </c>
+      <c r="R20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E21">
         <v>0.08409677600760461</v>
@@ -4385,24 +5110,36 @@
         <v>0.6637999999999999</v>
       </c>
       <c r="M21" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N21">
         <v>0.6637999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>114</v>
+      </c>
+      <c r="P21">
+        <v>-0.0142294328360232</v>
+      </c>
+      <c r="Q21">
+        <v>0.02058433823526295</v>
+      </c>
+      <c r="R21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E22">
         <v>0.2869453687617096</v>
@@ -4423,24 +5160,36 @@
         <v>0.516</v>
       </c>
       <c r="M22" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N22">
         <v>0.516</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>114</v>
+      </c>
+      <c r="P22">
+        <v>-0.02924065294566617</v>
+      </c>
+      <c r="Q22">
+        <v>0.05097829023562198</v>
+      </c>
+      <c r="R22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <v>0.8194444444444444</v>
@@ -4461,24 +5210,36 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>113</v>
+      </c>
+      <c r="P23">
+        <v>-0.1084520884520883</v>
+      </c>
+      <c r="Q23">
+        <v>0.1354452054794529</v>
+      </c>
+      <c r="R23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E24">
         <v>0.9057591623036649</v>
@@ -4499,24 +5260,36 @@
         <v>0.8311704095417624</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N24">
         <v>0.8311704095417624</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>113</v>
+      </c>
+      <c r="P24">
+        <v>-0.06964953136679887</v>
+      </c>
+      <c r="Q24">
+        <v>0.04973337731233337</v>
+      </c>
+      <c r="R24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E25">
         <v>0.8821292775665399</v>
@@ -4537,24 +5310,36 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>113</v>
+      </c>
+      <c r="P25">
+        <v>-0.05703422053231939</v>
+      </c>
+      <c r="Q25">
+        <v>0.04942965779467681</v>
+      </c>
+      <c r="R25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E26">
         <v>0.9572425828970333</v>
@@ -4575,24 +5360,36 @@
         <v>0.003869222643548615</v>
       </c>
       <c r="M26" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N26">
         <v>0.01160766793064584</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>113</v>
+      </c>
+      <c r="P26">
+        <v>0.00859192659616724</v>
+      </c>
+      <c r="Q26">
+        <v>0.09175711354344908</v>
+      </c>
+      <c r="R26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E27">
         <v>0.08409677600760461</v>
@@ -4613,24 +5410,36 @@
         <v>0.0032</v>
       </c>
       <c r="M27" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N27">
         <v>0.006</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>114</v>
+      </c>
+      <c r="P27">
+        <v>-0.05724448040629365</v>
+      </c>
+      <c r="Q27">
+        <v>-0.009295274346557969</v>
+      </c>
+      <c r="R27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E28">
         <v>0.2869453687617096</v>
@@ -4651,24 +5460,36 @@
         <v>0.0056</v>
       </c>
       <c r="M28" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N28">
         <v>0.0108</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>114</v>
+      </c>
+      <c r="P28">
+        <v>-0.1321164458071846</v>
+      </c>
+      <c r="Q28">
+        <v>-0.01702686197773369</v>
+      </c>
+      <c r="R28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E29">
         <v>0.8194444444444444</v>
@@ -4689,24 +5510,36 @@
         <v>0.6055766163353462</v>
       </c>
       <c r="M29" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>113</v>
+      </c>
+      <c r="P29">
+        <v>-0.08893822029095019</v>
+      </c>
+      <c r="Q29">
+        <v>0.171875</v>
+      </c>
+      <c r="R29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E30">
         <v>0.9057591623036649</v>
@@ -4727,24 +5560,36 @@
         <v>0.02585758046344289</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N30">
         <v>0.05171516092688578</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>113</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0.1371632174931668</v>
+      </c>
+      <c r="R30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>0.8821292775665399</v>
@@ -4765,24 +5610,36 @@
         <v>0.02373851525005458</v>
       </c>
       <c r="M31" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N31">
         <v>0.04747703050010915</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>113</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0.1216730038022814</v>
+      </c>
+      <c r="R31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E32">
         <v>0.954261198371146</v>
@@ -4803,24 +5660,36 @@
         <v>0.009812492570670151</v>
       </c>
       <c r="M32" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N32">
         <v>0.0196249851413403</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>113</v>
+      </c>
+      <c r="P32">
+        <v>0.003442818587617621</v>
+      </c>
+      <c r="Q32">
+        <v>0.09094345250022397</v>
+      </c>
+      <c r="R32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E33">
         <v>0.08091932330798474</v>
@@ -4841,24 +5710,36 @@
         <v>0.0016</v>
       </c>
       <c r="M33" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N33">
         <v>0.006</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P33">
+        <v>-0.063099354823316</v>
+      </c>
+      <c r="Q33">
+        <v>-0.009795305328775369</v>
+      </c>
+      <c r="R33" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E34">
         <v>0.2760765501167317</v>
@@ -4879,24 +5760,36 @@
         <v>0.002</v>
       </c>
       <c r="M34" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N34">
         <v>0.008399999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>114</v>
+      </c>
+      <c r="P34">
+        <v>-0.1494866851663962</v>
+      </c>
+      <c r="Q34">
+        <v>-0.02139425990847783</v>
+      </c>
+      <c r="R34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E35">
         <v>0.8055555555555556</v>
@@ -4917,24 +5810,36 @@
         <v>0.8025873486341526</v>
       </c>
       <c r="M35" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>113</v>
+      </c>
+      <c r="P35">
+        <v>-0.1036050156739811</v>
+      </c>
+      <c r="Q35">
+        <v>0.1643835616438356</v>
+      </c>
+      <c r="R35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E36">
         <v>0.9162303664921466</v>
@@ -4955,24 +5860,36 @@
         <v>0.01480610912734845</v>
       </c>
       <c r="M36" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N36">
         <v>0.03878637069516434</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>113</v>
+      </c>
+      <c r="P36">
+        <v>0.01025641025641026</v>
+      </c>
+      <c r="Q36">
+        <v>0.1530566801619438</v>
+      </c>
+      <c r="R36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E37">
         <v>0.8859315589353612</v>
@@ -4993,24 +5910,36 @@
         <v>0.02227097895923274</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N37">
         <v>0.04454195791846547</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>113</v>
+      </c>
+      <c r="P37">
+        <v>0.003802281368821293</v>
+      </c>
+      <c r="Q37">
+        <v>0.1254752851711027</v>
+      </c>
+      <c r="R37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E38">
         <v>0.9407308377896613</v>
@@ -5031,24 +5960,36 @@
         <v>0.1467487068347569</v>
       </c>
       <c r="M38" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N38">
         <v>0.1467487068347569</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>113</v>
+      </c>
+      <c r="P38">
+        <v>-0.01582008783175719</v>
+      </c>
+      <c r="Q38">
+        <v>0.06451559909411336</v>
+      </c>
+      <c r="R38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E39">
         <v>0.09695071675889327</v>
@@ -5069,24 +6010,36 @@
         <v>0.1052</v>
       </c>
       <c r="M39" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N39">
         <v>0.1868</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>114</v>
+      </c>
+      <c r="P39">
+        <v>-0.03571830630142864</v>
+      </c>
+      <c r="Q39">
+        <v>0.005977177289570985</v>
+      </c>
+      <c r="R39" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E40">
         <v>0.3170570598774448</v>
@@ -5107,24 +6060,36 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="M40" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N40">
         <v>0.1416</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>114</v>
+      </c>
+      <c r="P40">
+        <v>-0.08982206866643555</v>
+      </c>
+      <c r="Q40">
+        <v>0.01126308110606705</v>
+      </c>
+      <c r="R40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E41">
         <v>0.8484848484848485</v>
@@ -5145,24 +6110,36 @@
         <v>0.6463551955394902</v>
       </c>
       <c r="M41" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N41">
         <v>0.6463551955394902</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>113</v>
+      </c>
+      <c r="P41">
+        <v>-0.1131249999999998</v>
+      </c>
+      <c r="Q41">
+        <v>0.2034996861268049</v>
+      </c>
+      <c r="R41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E42">
         <v>0.8663101604278075</v>
@@ -5183,24 +6160,36 @@
         <v>0.6276258050283593</v>
       </c>
       <c r="M42" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N42">
         <v>0.8501067391385259</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>113</v>
+      </c>
+      <c r="P42">
+        <v>-0.07119289340101519</v>
+      </c>
+      <c r="Q42">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="R42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E43">
         <v>0.8616600790513834</v>
@@ -5221,24 +6210,36 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>113</v>
+      </c>
+      <c r="P43">
+        <v>-0.05533596837944664</v>
+      </c>
+      <c r="Q43">
+        <v>0.05533596837944664</v>
+      </c>
+      <c r="R43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>0.9407308377896613</v>
@@ -5259,24 +6260,36 @@
         <v>0.003403025345125086</v>
       </c>
       <c r="M44" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N44">
         <v>0.01020907603537526</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>113</v>
+      </c>
+      <c r="P44">
+        <v>0.01283465784607815</v>
+      </c>
+      <c r="Q44">
+        <v>0.127742234067712</v>
+      </c>
+      <c r="R44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>0.09695071675889327</v>
@@ -5297,24 +6310,36 @@
         <v>0.007</v>
       </c>
       <c r="M45" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N45">
         <v>0.0166</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>114</v>
+      </c>
+      <c r="P45">
+        <v>-0.06143081418824267</v>
+      </c>
+      <c r="Q45">
+        <v>-0.004730782807804843</v>
+      </c>
+      <c r="R45" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>0.3170570598774448</v>
@@ -5335,24 +6360,36 @@
         <v>0.007</v>
       </c>
       <c r="M46" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N46">
         <v>0.0138</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>114</v>
+      </c>
+      <c r="P46">
+        <v>-0.1592997954158392</v>
+      </c>
+      <c r="Q46">
+        <v>-0.01415100173422988</v>
+      </c>
+      <c r="R46" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>0.8484848484848485</v>
@@ -5373,24 +6410,36 @@
         <v>0.2109029260566068</v>
       </c>
       <c r="M47" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N47">
         <v>0.6327087781698203</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>113</v>
+      </c>
+      <c r="P47">
+        <v>-0.07352941176470588</v>
+      </c>
+      <c r="Q47">
+        <v>0.2711864406779661</v>
+      </c>
+      <c r="R47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>0.8663101604278075</v>
@@ -5411,24 +6460,36 @@
         <v>0.8501067391385259</v>
       </c>
       <c r="M48" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N48">
         <v>0.8501067391385259</v>
       </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>113</v>
+      </c>
+      <c r="P48">
+        <v>-0.05615820998675333</v>
+      </c>
+      <c r="Q48">
+        <v>0.07951283350219536</v>
+      </c>
+      <c r="R48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E49">
         <v>0.8616600790513834</v>
@@ -5449,24 +6510,36 @@
         <v>0.2626182904425174</v>
       </c>
       <c r="M49" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N49">
         <v>0.5252365808850348</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>113</v>
+      </c>
+      <c r="P49">
+        <v>-0.03162055335968379</v>
+      </c>
+      <c r="Q49">
+        <v>0.1001976284584995</v>
+      </c>
+      <c r="R49" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E50">
         <v>0.9163830821584832</v>
@@ -5487,24 +6560,36 @@
         <v>0.04866005335540764</v>
       </c>
       <c r="M50" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="N50">
         <v>0.09732010671081527</v>
       </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>113</v>
+      </c>
+      <c r="P50">
+        <v>-0.009843146013245659</v>
+      </c>
+      <c r="Q50">
+        <v>0.1017245266646797</v>
+      </c>
+      <c r="R50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E51">
         <v>0.1118212812648221</v>
@@ -5525,24 +6610,36 @@
         <v>0.1366</v>
       </c>
       <c r="M51" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N51">
         <v>0.1868</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>114</v>
+      </c>
+      <c r="P51">
+        <v>-0.0459950736638484</v>
+      </c>
+      <c r="Q51">
+        <v>0.009574605679658545</v>
+      </c>
+      <c r="R51" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E52">
         <v>0.3563365536576291</v>
@@ -5563,24 +6660,36 @@
         <v>0.1234</v>
       </c>
       <c r="M52" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N52">
         <v>0.1416</v>
       </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>114</v>
+      </c>
+      <c r="P52">
+        <v>-0.1179283647360767</v>
+      </c>
+      <c r="Q52">
+        <v>0.02303655514637615</v>
+      </c>
+      <c r="R52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E53">
         <v>0.803030303030303</v>
@@ -5601,24 +6710,36 @@
         <v>0.4795001221869534</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N53">
         <v>0.6463551955394902</v>
       </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>113</v>
+      </c>
+      <c r="P53">
+        <v>-0.09015151515151501</v>
+      </c>
+      <c r="Q53">
+        <v>0.213666666666667</v>
+      </c>
+      <c r="R53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E54">
         <v>0.8823529411764706</v>
@@ -5639,24 +6760,36 @@
         <v>0.4576140668763148</v>
       </c>
       <c r="M54" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N54">
         <v>0.8501067391385259</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>113</v>
+      </c>
+      <c r="P54">
+        <v>-0.04218323586744636</v>
+      </c>
+      <c r="Q54">
+        <v>0.09913967059336842</v>
+      </c>
+      <c r="R54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E55">
         <v>0.8616600790513834</v>
@@ -5677,10 +6810,22 @@
         <v>0.2432427057426535</v>
       </c>
       <c r="M55" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N55">
         <v>0.486485411485307</v>
+      </c>
+      <c r="O55" t="s">
+        <v>113</v>
+      </c>
+      <c r="P55">
+        <v>-0.02766798418972332</v>
+      </c>
+      <c r="Q55">
+        <v>0.1001976284584995</v>
+      </c>
+      <c r="R55" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -5690,207 +6835,224 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
+    <col min="3" max="17" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+        <v>131</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2">
         <v>516</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>300</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>216</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.72</v>
       </c>
-      <c r="J2" t="b">
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>4999</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>42</v>
       </c>
-      <c r="M2" t="s">
-        <v>107</v>
-      </c>
       <c r="N2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O2" t="b">
+        <v>139</v>
+      </c>
+      <c r="O2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3">
-        <v>263</v>
+        <v>138</v>
+      </c>
+      <c r="F3" t="s">
+        <v>123</v>
       </c>
       <c r="G3">
         <v>263</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" t="b">
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>4999</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>42</v>
       </c>
-      <c r="M3" t="s">
-        <v>107</v>
-      </c>
       <c r="N3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" t="b">
+        <v>139</v>
+      </c>
+      <c r="O3" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4">
-        <v>253</v>
+        <v>138</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
       </c>
       <c r="G4">
         <v>253</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" t="b">
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>4999</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>42</v>
       </c>
-      <c r="M4" t="s">
-        <v>107</v>
-      </c>
       <c r="N4" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" t="b">
+        <v>139</v>
+      </c>
+      <c r="O4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
-        <v>109</v>
+      <c r="Q4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_classifier_results.xlsx
+++ b/examples/example_classifier_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="145">
   <si>
     <t>Group</t>
   </si>
@@ -194,10 +194,10 @@
     <t>AUC Test</t>
   </si>
   <si>
-    <t>Brier Score Test</t>
-  </si>
-  <si>
-    <t>Log-Loss Test</t>
+    <t>Brier score Test</t>
+  </si>
+  <si>
+    <t>Log-loss Test</t>
   </si>
   <si>
     <t>Sensitivity Test</t>
@@ -227,6 +227,9 @@
     <t>Subgroups</t>
   </si>
   <si>
+    <t>Subgroup adjustment</t>
+  </si>
+  <si>
     <t>Patient as the unit (cluster bootstrap / cluster-robust tests)</t>
   </si>
   <si>
@@ -248,21 +251,27 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Hommel: AUC, Sensitivity, Specificity, Accuracy; Romano-Wolf step-down: Brier Score, Log-Loss</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Bonferroni (normal theory, Obuchowski SE): AUC; Romano-Wolf simultaneous (max-|t|): Brier Score, Log-Loss; Bonferroni (percentile bootstrap): Sensitivity, Specificity, Accuracy. Brier score and log-loss: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). AUC: difference ± z × SE, z the normal quantile for coverage 1 - 0.05/m (Bonferroni). Sensitivity, specificity and accuracy: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Hommel: AUC, Sensitivity, Specificity, Accuracy; Romano-Wolf step-down: Brier score, Log-loss</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Bonferroni (normal theory, Obuchowski SE): AUC; Romano-Wolf simultaneous (max-|t|): Brier score, Log-loss; Bonferroni (percentile bootstrap): Sensitivity, Specificity, Accuracy. Brier score and log-loss: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). AUC: difference ± z × SE, z the normal quantile for coverage 1 - 0.05/m (Bonferroni). Sensitivity, specificity and accuracy: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
-    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings; p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
+    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings</t>
+  </si>
+  <si>
+    <t>Subgroup results are exploratory: p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
+    <t>grouping</t>
+  </si>
+  <si>
     <t>model</t>
   </si>
   <si>
@@ -287,6 +296,9 @@
     <t>method</t>
   </si>
   <si>
+    <t>eye</t>
+  </si>
+  <si>
     <t>auc</t>
   </si>
   <si>
@@ -435,9 +447,6 @@
   </si>
   <si>
     <t>patient_id</t>
-  </si>
-  <si>
-    <t>eye</t>
   </si>
   <si>
     <t>patient</t>
@@ -2229,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -2249,7 +2258,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2257,7 +2266,7 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2265,7 +2274,7 @@
         <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2273,7 +2282,7 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2281,7 +2290,7 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2289,7 +2298,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2297,7 +2306,7 @@
         <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2305,7 +2314,7 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2313,7 +2322,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2321,7 +2330,7 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2329,7 +2338,7 @@
         <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2337,7 +2346,7 @@
         <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2345,7 +2354,7 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2353,7 +2362,15 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2363,1605 +2380,1770 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+    <col min="1" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>90</v>
+      </c>
+      <c r="J1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2">
         <v>0.9497450348899624</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.9320893216905599</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.9658422111533366</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>516</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>300</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3">
+        <v>0.9360670194003528</v>
+      </c>
+      <c r="F3">
+        <v>0.9132995820124723</v>
+      </c>
+      <c r="G3">
+        <v>0.9561922327746769</v>
+      </c>
+      <c r="H3">
+        <v>516</v>
+      </c>
+      <c r="I3">
+        <v>300</v>
+      </c>
+      <c r="J3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="F4">
+        <v>0.8573046968123558</v>
+      </c>
+      <c r="G4">
+        <v>0.9177145234366175</v>
+      </c>
+      <c r="H4">
+        <v>516</v>
+      </c>
+      <c r="I4">
+        <v>300</v>
+      </c>
+      <c r="J4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5">
+        <v>0.09039919269379845</v>
+      </c>
+      <c r="F5">
+        <v>0.07832652244405816</v>
+      </c>
+      <c r="G5">
+        <v>0.1022662245047647</v>
+      </c>
+      <c r="H5">
+        <v>516</v>
+      </c>
+      <c r="I5">
+        <v>300</v>
+      </c>
+      <c r="J5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6">
+        <v>0.09607086470930232</v>
+      </c>
+      <c r="F6">
+        <v>0.08251477675096154</v>
+      </c>
+      <c r="G6">
+        <v>0.1101717326762754</v>
+      </c>
+      <c r="H6">
+        <v>516</v>
+      </c>
+      <c r="I6">
+        <v>300</v>
+      </c>
+      <c r="J6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7">
+        <v>0.1235763627906977</v>
+      </c>
+      <c r="F7">
+        <v>0.1064186137780775</v>
+      </c>
+      <c r="G7">
+        <v>0.1410180048162069</v>
+      </c>
+      <c r="H7">
+        <v>516</v>
+      </c>
+      <c r="I7">
+        <v>300</v>
+      </c>
+      <c r="J7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E8">
+        <v>0.3017094343669053</v>
+      </c>
+      <c r="F8">
+        <v>0.2707681375493131</v>
+      </c>
+      <c r="G8">
+        <v>0.3317168115905306</v>
+      </c>
+      <c r="H8">
+        <v>516</v>
+      </c>
+      <c r="I8">
+        <v>300</v>
+      </c>
+      <c r="J8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3">
-        <v>0.9360670194003528</v>
-      </c>
-      <c r="E3">
-        <v>0.9132995820124723</v>
-      </c>
-      <c r="F3">
-        <v>0.9561922327746769</v>
-      </c>
-      <c r="G3">
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9">
+        <v>0.3154288386745746</v>
+      </c>
+      <c r="F9">
+        <v>0.2813931137035998</v>
+      </c>
+      <c r="G9">
+        <v>0.3510561699111525</v>
+      </c>
+      <c r="H9">
         <v>516</v>
       </c>
-      <c r="H3">
+      <c r="I9">
         <v>300</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E10">
+        <v>0.3822401917568288</v>
+      </c>
+      <c r="F10">
+        <v>0.3387446684060572</v>
+      </c>
+      <c r="G10">
+        <v>0.4265781353425924</v>
+      </c>
+      <c r="H10">
+        <v>516</v>
+      </c>
+      <c r="I10">
+        <v>300</v>
+      </c>
+      <c r="J10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F11">
+        <v>0.7656013257575758</v>
+      </c>
+      <c r="G11">
+        <v>0.8960148148148149</v>
+      </c>
+      <c r="H11">
+        <v>516</v>
+      </c>
+      <c r="I11">
+        <v>300</v>
+      </c>
+      <c r="J11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="F12">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="G12">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="H12">
+        <v>516</v>
+      </c>
+      <c r="I12">
+        <v>300</v>
+      </c>
+      <c r="J12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4">
-        <v>0.888888888888889</v>
-      </c>
-      <c r="E4">
-        <v>0.8573046968123558</v>
-      </c>
-      <c r="F4">
-        <v>0.9177145234366175</v>
-      </c>
-      <c r="G4">
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="F13">
+        <v>0.6846128033040785</v>
+      </c>
+      <c r="G13">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H13">
         <v>516</v>
       </c>
-      <c r="H4">
+      <c r="I13">
         <v>300</v>
       </c>
-      <c r="I4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="J13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5">
-        <v>0.09039919269379845</v>
-      </c>
-      <c r="E5">
-        <v>0.07832652244405816</v>
-      </c>
-      <c r="F5">
-        <v>0.1022662245047647</v>
-      </c>
-      <c r="G5">
+      <c r="D14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14">
+        <v>0.8862433862433863</v>
+      </c>
+      <c r="F14">
+        <v>0.852937169418176</v>
+      </c>
+      <c r="G14">
+        <v>0.9182058047493403</v>
+      </c>
+      <c r="H14">
         <v>516</v>
       </c>
-      <c r="H5">
+      <c r="I14">
         <v>300</v>
       </c>
-      <c r="I5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6">
-        <v>0.09607086470930232</v>
-      </c>
-      <c r="E6">
-        <v>0.08251477675096154</v>
-      </c>
-      <c r="F6">
-        <v>0.1101717326762754</v>
-      </c>
-      <c r="G6">
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15">
+        <v>0.8994708994708994</v>
+      </c>
+      <c r="F15">
+        <v>0.8660881121774977</v>
+      </c>
+      <c r="G15">
+        <v>0.9300518134715026</v>
+      </c>
+      <c r="H15">
         <v>516</v>
       </c>
-      <c r="H6">
+      <c r="I15">
         <v>300</v>
       </c>
-      <c r="I6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="J15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7">
-        <v>0.1235763627906977</v>
-      </c>
-      <c r="E7">
-        <v>0.1064186137780775</v>
-      </c>
-      <c r="F7">
-        <v>0.1410180048162069</v>
-      </c>
-      <c r="G7">
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="F16">
+        <v>0.8077940861367046</v>
+      </c>
+      <c r="G16">
+        <v>0.8837240729101195</v>
+      </c>
+      <c r="H16">
         <v>516</v>
       </c>
-      <c r="H7">
+      <c r="I16">
         <v>300</v>
       </c>
-      <c r="I7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="J16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8">
-        <v>0.3017094343669053</v>
-      </c>
-      <c r="E8">
-        <v>0.2707681375493131</v>
-      </c>
-      <c r="F8">
-        <v>0.3317168115905306</v>
-      </c>
-      <c r="G8">
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17">
+        <v>0.8720930232558139</v>
+      </c>
+      <c r="F17">
+        <v>0.8428290766208252</v>
+      </c>
+      <c r="G17">
+        <v>0.9011928958756779</v>
+      </c>
+      <c r="H17">
         <v>516</v>
       </c>
-      <c r="H8">
+      <c r="I17">
         <v>300</v>
       </c>
-      <c r="I8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9">
-        <v>0.3154288386745746</v>
-      </c>
-      <c r="E9">
-        <v>0.2813931137035998</v>
-      </c>
-      <c r="F9">
-        <v>0.3510561699111525</v>
-      </c>
-      <c r="G9">
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18">
+        <v>0.874031007751938</v>
+      </c>
+      <c r="F18">
+        <v>0.8448275862068966</v>
+      </c>
+      <c r="G18">
+        <v>0.9020735511528966</v>
+      </c>
+      <c r="H18">
         <v>516</v>
       </c>
-      <c r="H9">
+      <c r="I18">
         <v>300</v>
       </c>
-      <c r="I9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10">
-        <v>0.3822401917568288</v>
-      </c>
-      <c r="E10">
-        <v>0.3387446684060572</v>
-      </c>
-      <c r="F10">
-        <v>0.4265781353425924</v>
-      </c>
-      <c r="G10">
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19">
+        <v>0.8236434108527132</v>
+      </c>
+      <c r="F19">
+        <v>0.7895702093070514</v>
+      </c>
+      <c r="G19">
+        <v>0.8568627450980392</v>
+      </c>
+      <c r="H19">
         <v>516</v>
       </c>
-      <c r="H10">
+      <c r="I19">
         <v>300</v>
       </c>
-      <c r="I10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E11">
-        <v>0.7656013257575758</v>
-      </c>
-      <c r="F11">
-        <v>0.8960148148148149</v>
-      </c>
-      <c r="G11">
-        <v>516</v>
-      </c>
-      <c r="H11">
-        <v>300</v>
-      </c>
-      <c r="I11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12">
-        <v>0.8043478260869565</v>
-      </c>
-      <c r="E12">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="F12">
-        <v>0.8695652173913043</v>
-      </c>
-      <c r="G12">
-        <v>516</v>
-      </c>
-      <c r="H12">
-        <v>300</v>
-      </c>
-      <c r="I12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="E13">
-        <v>0.6846128033040785</v>
-      </c>
-      <c r="F13">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G13">
-        <v>516</v>
-      </c>
-      <c r="H13">
-        <v>300</v>
-      </c>
-      <c r="I13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14">
-        <v>0.8862433862433863</v>
-      </c>
-      <c r="E14">
-        <v>0.852937169418176</v>
-      </c>
-      <c r="F14">
-        <v>0.9182058047493403</v>
-      </c>
-      <c r="G14">
-        <v>516</v>
-      </c>
-      <c r="H14">
-        <v>300</v>
-      </c>
-      <c r="I14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15">
-        <v>0.8994708994708994</v>
-      </c>
-      <c r="E15">
-        <v>0.8660881121774977</v>
-      </c>
-      <c r="F15">
-        <v>0.9300518134715026</v>
-      </c>
-      <c r="G15">
-        <v>516</v>
-      </c>
-      <c r="H15">
-        <v>300</v>
-      </c>
-      <c r="I15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16">
-        <v>0.8465608465608465</v>
-      </c>
-      <c r="E16">
-        <v>0.8077940861367046</v>
-      </c>
-      <c r="F16">
-        <v>0.8837240729101195</v>
-      </c>
-      <c r="G16">
-        <v>516</v>
-      </c>
-      <c r="H16">
-        <v>300</v>
-      </c>
-      <c r="I16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17">
-        <v>0.8720930232558139</v>
-      </c>
-      <c r="E17">
-        <v>0.8428290766208252</v>
-      </c>
-      <c r="F17">
-        <v>0.9011928958756779</v>
-      </c>
-      <c r="G17">
-        <v>516</v>
-      </c>
-      <c r="H17">
-        <v>300</v>
-      </c>
-      <c r="I17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18">
-        <v>0.874031007751938</v>
-      </c>
-      <c r="E18">
-        <v>0.8448275862068966</v>
-      </c>
-      <c r="F18">
-        <v>0.9020735511528966</v>
-      </c>
-      <c r="G18">
-        <v>516</v>
-      </c>
-      <c r="H18">
-        <v>300</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19">
-        <v>0.8236434108527132</v>
-      </c>
-      <c r="E19">
-        <v>0.7895702093070514</v>
-      </c>
-      <c r="F19">
-        <v>0.8568627450980392</v>
-      </c>
-      <c r="G19">
-        <v>516</v>
-      </c>
-      <c r="H19">
-        <v>300</v>
-      </c>
-      <c r="I19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20">
         <v>0.9572425828970333</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.9314174085184896</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.9779403804253587</v>
-      </c>
-      <c r="G20">
-        <v>263</v>
       </c>
       <c r="H20">
         <v>263</v>
       </c>
-      <c r="I20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="I20">
+        <v>263</v>
+      </c>
+      <c r="J20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21">
         <v>0.954261198371146</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.9278557781439901</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.9757148084114029</v>
-      </c>
-      <c r="G21">
-        <v>263</v>
       </c>
       <c r="H21">
         <v>263</v>
       </c>
-      <c r="I21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="I21">
+        <v>263</v>
+      </c>
+      <c r="J21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
         <v>52</v>
       </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22">
         <v>0.9070680628272252</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.8680864992881939</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.9400875480541542</v>
-      </c>
-      <c r="G22">
-        <v>263</v>
       </c>
       <c r="H22">
         <v>263</v>
       </c>
-      <c r="I22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="I22">
+        <v>263</v>
+      </c>
+      <c r="J22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
         <v>50</v>
       </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23">
         <v>0.08409677600760457</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.06911136540874524</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.1009847289695818</v>
-      </c>
-      <c r="G23">
-        <v>263</v>
       </c>
       <c r="H23">
         <v>263</v>
       </c>
-      <c r="I23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="I23">
+        <v>263</v>
+      </c>
+      <c r="J23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24">
+      <c r="D24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24">
         <v>0.08091932330798481</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.06420706836501901</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.09966024858365012</v>
-      </c>
-      <c r="G24">
-        <v>263</v>
       </c>
       <c r="H24">
         <v>263</v>
       </c>
-      <c r="I24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="I24">
+        <v>263</v>
+      </c>
+      <c r="J24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
         <v>52</v>
       </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25">
         <v>0.1173666533840304</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.0959141370114068</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.1397679711159696</v>
-      </c>
-      <c r="G25">
-        <v>263</v>
       </c>
       <c r="H25">
         <v>263</v>
       </c>
-      <c r="I25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="I25">
+        <v>263</v>
+      </c>
+      <c r="J25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26">
         <v>0.2869453687617093</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.2491849800219261</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.3292138341683321</v>
-      </c>
-      <c r="G26">
-        <v>263</v>
       </c>
       <c r="H26">
         <v>263</v>
       </c>
-      <c r="I26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="I26">
+        <v>263</v>
+      </c>
+      <c r="J26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27">
         <v>0.2760765501167315</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.2337866905120009</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.3225826966370221</v>
-      </c>
-      <c r="G27">
-        <v>263</v>
       </c>
       <c r="H27">
         <v>263</v>
       </c>
-      <c r="I27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="I27">
+        <v>263</v>
+      </c>
+      <c r="J27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
         <v>52</v>
       </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28">
         <v>0.3615170226541689</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.3096911889090577</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.4159065315200386</v>
-      </c>
-      <c r="G28">
-        <v>263</v>
       </c>
       <c r="H28">
         <v>263</v>
       </c>
-      <c r="I28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="I28">
+        <v>263</v>
+      </c>
+      <c r="J28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s">
         <v>50</v>
       </c>
-      <c r="C29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29">
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29">
         <v>0.8194444444444444</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.7241379310344828</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.9058823529411765</v>
-      </c>
-      <c r="G29">
-        <v>263</v>
       </c>
       <c r="H29">
         <v>263</v>
       </c>
-      <c r="I29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="I29">
+        <v>263</v>
+      </c>
+      <c r="J29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
         <v>51</v>
       </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30">
         <v>0.8055555555555556</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.7083333333333334</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.8889649923896501</v>
-      </c>
-      <c r="G30">
-        <v>263</v>
       </c>
       <c r="H30">
         <v>263</v>
       </c>
-      <c r="I30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="I30">
+        <v>263</v>
+      </c>
+      <c r="J30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
         <v>52</v>
       </c>
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31">
         <v>0.7777777777777778</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.676056338028169</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.8676470588235294</v>
-      </c>
-      <c r="G31">
-        <v>263</v>
       </c>
       <c r="H31">
         <v>263</v>
       </c>
-      <c r="I31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="I31">
+        <v>263</v>
+      </c>
+      <c r="J31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
         <v>50</v>
       </c>
-      <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32">
         <v>0.9057591623036649</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.8628515406162466</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.945273631840796</v>
-      </c>
-      <c r="G32">
-        <v>263</v>
       </c>
       <c r="H32">
         <v>263</v>
       </c>
-      <c r="I32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="I32">
+        <v>263</v>
+      </c>
+      <c r="J32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
         <v>51</v>
       </c>
-      <c r="C33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33">
         <v>0.9162303664921466</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.8743455497382199</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.953223949337939</v>
-      </c>
-      <c r="G33">
-        <v>263</v>
       </c>
       <c r="H33">
         <v>263</v>
       </c>
-      <c r="I33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="I33">
+        <v>263</v>
+      </c>
+      <c r="J33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34">
         <v>0.837696335078534</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.7857142857142857</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.8888888888888888</v>
-      </c>
-      <c r="G34">
-        <v>263</v>
       </c>
       <c r="H34">
         <v>263</v>
       </c>
-      <c r="I34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="I34">
+        <v>263</v>
+      </c>
+      <c r="J34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>48</v>
       </c>
       <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
         <v>50</v>
       </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35">
         <v>0.8821292775665399</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.8403041825095057</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.9201520912547528</v>
-      </c>
-      <c r="G35">
-        <v>263</v>
       </c>
       <c r="H35">
         <v>263</v>
       </c>
-      <c r="I35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="I35">
+        <v>263</v>
+      </c>
+      <c r="J35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s">
         <v>51</v>
       </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36">
         <v>0.8859315589353612</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.844106463878327</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.9201520912547528</v>
-      </c>
-      <c r="G36">
-        <v>263</v>
       </c>
       <c r="H36">
         <v>263</v>
       </c>
-      <c r="I36" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="I36">
+        <v>263</v>
+      </c>
+      <c r="J36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37">
         <v>0.8212927756653993</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.7756653992395437</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.8669201520912547</v>
-      </c>
-      <c r="G37">
-        <v>263</v>
       </c>
       <c r="H37">
         <v>263</v>
       </c>
-      <c r="I37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="I37">
+        <v>263</v>
+      </c>
+      <c r="J37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s">
         <v>50</v>
       </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38">
         <v>0.9407308377896613</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.911409306760217</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.9649602719005704</v>
-      </c>
-      <c r="G38">
-        <v>253</v>
       </c>
       <c r="H38">
         <v>253</v>
       </c>
-      <c r="I38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="I38">
+        <v>253</v>
+      </c>
+      <c r="J38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39">
+      <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39">
         <v>0.9163830821584832</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.8794413082083586</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.9491267011035582</v>
-      </c>
-      <c r="G39">
-        <v>253</v>
       </c>
       <c r="H39">
         <v>253</v>
       </c>
-      <c r="I39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="I39">
+        <v>253</v>
+      </c>
+      <c r="J39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40">
         <v>0.8704423918327662</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.8206890454828421</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.9151523253929671</v>
-      </c>
-      <c r="G40">
-        <v>253</v>
       </c>
       <c r="H40">
         <v>253</v>
       </c>
-      <c r="I40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="I40">
+        <v>253</v>
+      </c>
+      <c r="J40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>49</v>
       </c>
       <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
         <v>50</v>
       </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41">
         <v>0.09695071675889329</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.08017872622529643</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.1154392034308301</v>
-      </c>
-      <c r="G41">
-        <v>253</v>
       </c>
       <c r="H41">
         <v>253</v>
       </c>
-      <c r="I41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="I41">
+        <v>253</v>
+      </c>
+      <c r="J41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
         <v>51</v>
       </c>
-      <c r="C42" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42">
+      <c r="D42" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42">
         <v>0.1118212812648221</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.0916886461521739</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.1326395123577075</v>
-      </c>
-      <c r="G42">
-        <v>253</v>
       </c>
       <c r="H42">
         <v>253</v>
       </c>
-      <c r="I42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="I42">
+        <v>253</v>
+      </c>
+      <c r="J42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
         <v>52</v>
       </c>
-      <c r="C43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43">
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43">
         <v>0.130031515256917</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.1057446896225297</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0.1559957030592885</v>
-      </c>
-      <c r="G43">
-        <v>253</v>
       </c>
       <c r="H43">
         <v>253</v>
       </c>
-      <c r="I43" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="I43">
+        <v>253</v>
+      </c>
+      <c r="J43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
         <v>50</v>
       </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44">
+      <c r="D44" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44">
         <v>0.317057059877445</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.2758562403397774</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.3622894928340787</v>
-      </c>
-      <c r="G44">
-        <v>253</v>
       </c>
       <c r="H44">
         <v>253</v>
       </c>
-      <c r="I44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="I44">
+        <v>253</v>
+      </c>
+      <c r="J44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
         <v>51</v>
       </c>
-      <c r="C45" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45">
         <v>0.3563365536576291</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.3056173165279735</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.4092161441083348</v>
-      </c>
-      <c r="G45">
-        <v>253</v>
       </c>
       <c r="H45">
         <v>253</v>
       </c>
-      <c r="I45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="I45">
+        <v>253</v>
+      </c>
+      <c r="J45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
         <v>52</v>
       </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46">
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46">
         <v>0.4037824584524792</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.3398855733723783</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.4722873582532369</v>
-      </c>
-      <c r="G46">
-        <v>253</v>
       </c>
       <c r="H46">
         <v>253</v>
       </c>
-      <c r="I46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="I46">
+        <v>253</v>
+      </c>
+      <c r="J46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47">
+      <c r="D47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47">
         <v>0.8484848484848485</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.7534246575342466</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.9305555555555556</v>
-      </c>
-      <c r="G47">
-        <v>253</v>
       </c>
       <c r="H47">
         <v>253</v>
       </c>
-      <c r="I47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="I47">
+        <v>253</v>
+      </c>
+      <c r="J47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" t="s">
-        <v>92</v>
-      </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48">
         <v>0.803030303030303</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.7017543859649122</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.8947368421052632</v>
-      </c>
-      <c r="G48">
-        <v>253</v>
       </c>
       <c r="H48">
         <v>253</v>
       </c>
-      <c r="I48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="I48">
+        <v>253</v>
+      </c>
+      <c r="J48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" t="s">
         <v>52</v>
       </c>
-      <c r="C49" t="s">
-        <v>92</v>
-      </c>
-      <c r="D49">
+      <c r="D49" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49">
         <v>0.7424242424242424</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.6323529411764706</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.8450704225352113</v>
-      </c>
-      <c r="G49">
-        <v>253</v>
       </c>
       <c r="H49">
         <v>253</v>
       </c>
-      <c r="I49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="I49">
+        <v>253</v>
+      </c>
+      <c r="J49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
-        <v>93</v>
-      </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50">
         <v>0.8663101604278075</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.8148044111527257</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.9135135135135135</v>
-      </c>
-      <c r="G50">
-        <v>253</v>
       </c>
       <c r="H50">
         <v>253</v>
       </c>
-      <c r="I50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="I50">
+        <v>253</v>
+      </c>
+      <c r="J50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
-        <v>93</v>
-      </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51">
         <v>0.8823529411764706</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.835046541887699</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.9259259259259259</v>
-      </c>
-      <c r="G51">
-        <v>253</v>
       </c>
       <c r="H51">
         <v>253</v>
       </c>
-      <c r="I51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="I51">
+        <v>253</v>
+      </c>
+      <c r="J51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52">
         <v>0.8556149732620321</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.8011363636363636</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.9039590823489129</v>
-      </c>
-      <c r="G52">
-        <v>253</v>
       </c>
       <c r="H52">
         <v>253</v>
       </c>
-      <c r="I52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="I52">
+        <v>253</v>
+      </c>
+      <c r="J52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s">
         <v>50</v>
       </c>
-      <c r="C53" t="s">
-        <v>94</v>
-      </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53">
         <v>0.8616600790513834</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.8181818181818182</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.9011857707509882</v>
-      </c>
-      <c r="G53">
-        <v>253</v>
       </c>
       <c r="H53">
         <v>253</v>
       </c>
-      <c r="I53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="I53">
+        <v>253</v>
+      </c>
+      <c r="J53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" t="s">
         <v>51</v>
       </c>
-      <c r="C54" t="s">
-        <v>94</v>
-      </c>
-      <c r="D54">
+      <c r="D54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E54">
         <v>0.8616600790513834</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.8181818181818182</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.9011857707509882</v>
-      </c>
-      <c r="G54">
-        <v>253</v>
       </c>
       <c r="H54">
         <v>253</v>
       </c>
-      <c r="I54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="I54">
+        <v>253</v>
+      </c>
+      <c r="J54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s">
         <v>52</v>
       </c>
-      <c r="C55" t="s">
-        <v>94</v>
-      </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55">
         <v>0.8260869565217391</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.7786561264822134</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.8735177865612648</v>
-      </c>
-      <c r="G55">
-        <v>253</v>
       </c>
       <c r="H55">
         <v>253</v>
       </c>
-      <c r="I55" t="s">
-        <v>96</v>
+      <c r="I55">
+        <v>253</v>
+      </c>
+      <c r="J55" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3971,1214 +4153,1280 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="12" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="36.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="36.7109375" customWidth="1"/>
-    <col min="16" max="17" width="18.7109375" customWidth="1"/>
-    <col min="18" max="18" width="36.7109375" customWidth="1"/>
+    <col min="1" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="36.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="36.7109375" customWidth="1"/>
+    <col min="17" max="18" width="18.7109375" customWidth="1"/>
+    <col min="19" max="19" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O1" t="s">
+        <v>110</v>
+      </c>
+      <c r="P1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2">
+        <v>0.9497450348899624</v>
+      </c>
+      <c r="G2">
+        <v>0.9360670194003528</v>
+      </c>
+      <c r="H2">
+        <v>0.01367801548960967</v>
+      </c>
+      <c r="I2">
+        <v>-0.005336812651498976</v>
+      </c>
+      <c r="J2">
+        <v>0.03269284363071832</v>
+      </c>
+      <c r="K2">
+        <v>0.1585783521869673</v>
+      </c>
+      <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2">
+        <v>0.1585783521869673</v>
+      </c>
+      <c r="P2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q2">
+        <v>-0.009547469685576918</v>
+      </c>
+      <c r="R2">
+        <v>0.03690350066479627</v>
+      </c>
+      <c r="S2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3">
+        <v>0.09039919269379848</v>
+      </c>
+      <c r="G3">
+        <v>0.09607086470930229</v>
+      </c>
+      <c r="H3">
+        <v>-0.005671672015503809</v>
+      </c>
+      <c r="I3">
+        <v>-0.01696010224074354</v>
+      </c>
+      <c r="J3">
+        <v>0.006063415874129986</v>
+      </c>
+      <c r="K3">
+        <v>0.349</v>
+      </c>
+      <c r="L3">
+        <v>0.06038851071385942</v>
+      </c>
+      <c r="M3">
+        <v>1.637225445824592</v>
+      </c>
+      <c r="N3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3">
+        <v>0.349</v>
+      </c>
+      <c r="P3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q3">
+        <v>-0.01950821088880687</v>
+      </c>
+      <c r="R3">
+        <v>0.008164866857799255</v>
+      </c>
+      <c r="S3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>0.3017094343669052</v>
+      </c>
+      <c r="G4">
+        <v>0.3154288386745751</v>
+      </c>
+      <c r="H4">
+        <v>-0.01371940430766994</v>
+      </c>
+      <c r="I4">
+        <v>-0.04096857231250371</v>
+      </c>
+      <c r="J4">
+        <v>0.01379438013133473</v>
+      </c>
+      <c r="K4">
+        <v>0.3366</v>
+      </c>
+      <c r="L4">
+        <v>0.04410529743021843</v>
+      </c>
+      <c r="M4">
+        <v>1.658750048532445</v>
+      </c>
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4">
+        <v>0.3366</v>
+      </c>
+      <c r="P4" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q4">
+        <v>-0.04655890094471718</v>
+      </c>
+      <c r="R4">
+        <v>0.01912009232937731</v>
+      </c>
+      <c r="S4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G5">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="H5">
+        <v>0.02898550724637683</v>
+      </c>
+      <c r="I5">
+        <v>-0.05263157894736842</v>
+      </c>
+      <c r="J5">
+        <v>0.1134832366215345</v>
+      </c>
+      <c r="K5">
+        <v>0.4938941871029767</v>
+      </c>
+      <c r="L5">
+        <v>0.1566666666666667</v>
+      </c>
+      <c r="M5">
+        <v>1.1714295204668</v>
+      </c>
+      <c r="N5" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5">
+        <v>0.4938941871029767</v>
+      </c>
+      <c r="P5" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q5">
+        <v>-0.07142857142857142</v>
+      </c>
+      <c r="R5">
+        <v>0.130241215008934</v>
+      </c>
+      <c r="S5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
         <v>97</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>0.8862433862433863</v>
+      </c>
+      <c r="G6">
+        <v>0.8994708994708994</v>
+      </c>
+      <c r="H6">
+        <v>-0.01322751322751314</v>
+      </c>
+      <c r="I6">
+        <v>-0.04639490333476167</v>
+      </c>
+      <c r="J6">
+        <v>0.02026352423192726</v>
+      </c>
+      <c r="K6">
+        <v>0.4462239688329609</v>
+      </c>
+      <c r="L6">
+        <v>0.1442978581876312</v>
+      </c>
+      <c r="M6">
+        <v>1.400632776710893</v>
+      </c>
+      <c r="N6" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6">
+        <v>0.4462239688329609</v>
+      </c>
+      <c r="P6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q6">
+        <v>-0.05426356589147287</v>
+      </c>
+      <c r="R6">
+        <v>0.02761214074670986</v>
+      </c>
+      <c r="S6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>98</v>
       </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M1" t="s">
-        <v>105</v>
-      </c>
-      <c r="N1" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" t="s">
-        <v>107</v>
-      </c>
-      <c r="P1" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>109</v>
-      </c>
-      <c r="R1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E7" t="s">
         <v>51</v>
       </c>
-      <c r="E2">
+      <c r="F7">
+        <v>0.8720930232558139</v>
+      </c>
+      <c r="G7">
+        <v>0.874031007751938</v>
+      </c>
+      <c r="H7">
+        <v>-0.001937984496124034</v>
+      </c>
+      <c r="I7">
+        <v>-0.03475239539069325</v>
+      </c>
+      <c r="J7">
+        <v>0.03125</v>
+      </c>
+      <c r="K7">
+        <v>0.9094173748556938</v>
+      </c>
+      <c r="L7">
+        <v>0.1009144260952641</v>
+      </c>
+      <c r="M7">
+        <v>1.586004072823823</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7">
+        <v>0.9094173748556938</v>
+      </c>
+      <c r="P7" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7">
+        <v>-0.04177596020833175</v>
+      </c>
+      <c r="R7">
+        <v>0.03788432607331588</v>
+      </c>
+      <c r="S7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8">
         <v>0.9497450348899624</v>
       </c>
-      <c r="F2">
+      <c r="G8">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="H8">
+        <v>0.06085614600107347</v>
+      </c>
+      <c r="I8">
+        <v>0.03334994975402623</v>
+      </c>
+      <c r="J8">
+        <v>0.08836234224812071</v>
+      </c>
+      <c r="K8">
+        <v>1.448835277480167E-05</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8">
+        <v>4.346505832440501E-05</v>
+      </c>
+      <c r="P8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q8">
+        <v>0.02725895814217121</v>
+      </c>
+      <c r="R8">
+        <v>0.09445333385997573</v>
+      </c>
+      <c r="S8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>0.09039919269379848</v>
+      </c>
+      <c r="G9">
+        <v>0.1235763627906977</v>
+      </c>
+      <c r="H9">
+        <v>-0.03317717009689918</v>
+      </c>
+      <c r="I9">
+        <v>-0.0483943797631313</v>
+      </c>
+      <c r="J9">
+        <v>-0.01828621828652867</v>
+      </c>
+      <c r="K9">
+        <v>0.0004</v>
+      </c>
+      <c r="L9">
+        <v>-0.04746069207779437</v>
+      </c>
+      <c r="M9">
+        <v>1.72</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9">
+        <v>0.0004</v>
+      </c>
+      <c r="P9" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q9">
+        <v>-0.05126736698243801</v>
+      </c>
+      <c r="R9">
+        <v>-0.01508697321136034</v>
+      </c>
+      <c r="S9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10">
+        <v>0.3017094343669052</v>
+      </c>
+      <c r="G10">
+        <v>0.3822401917568288</v>
+      </c>
+      <c r="H10">
+        <v>-0.08053075738992366</v>
+      </c>
+      <c r="I10">
+        <v>-0.1192318182347926</v>
+      </c>
+      <c r="J10">
+        <v>-0.04360054027952263</v>
+      </c>
+      <c r="K10">
+        <v>0.0004</v>
+      </c>
+      <c r="L10">
+        <v>-0.05550309531095601</v>
+      </c>
+      <c r="M10">
+        <v>1.72</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10">
+        <v>0.0004</v>
+      </c>
+      <c r="P10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q10">
+        <v>-0.1256862042172851</v>
+      </c>
+      <c r="R10">
+        <v>-0.03537531056256221</v>
+      </c>
+      <c r="S10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G11">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="H11">
+        <v>0.07246376811594202</v>
+      </c>
+      <c r="I11">
+        <v>-0.01563115157480314</v>
+      </c>
+      <c r="J11">
+        <v>0.1677441004546439</v>
+      </c>
+      <c r="K11">
+        <v>0.1144834666737794</v>
+      </c>
+      <c r="L11">
+        <v>0.11767755313634</v>
+      </c>
+      <c r="M11">
+        <v>1.188514823808941</v>
+      </c>
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11">
+        <v>0.3434504000213381</v>
+      </c>
+      <c r="P11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q11">
+        <v>-0.03651368760064402</v>
+      </c>
+      <c r="R11">
+        <v>0.1830387554082666</v>
+      </c>
+      <c r="S11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12">
+        <v>0.8862433862433863</v>
+      </c>
+      <c r="G12">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="H12">
+        <v>0.03968253968253976</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.07859078590785908</v>
+      </c>
+      <c r="K12">
+        <v>0.04645567201881207</v>
+      </c>
+      <c r="L12">
+        <v>-0.01055297593921486</v>
+      </c>
+      <c r="M12">
+        <v>1.542857142857143</v>
+      </c>
+      <c r="N12" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12">
+        <v>0.09291134403762413</v>
+      </c>
+      <c r="P12" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q12">
+        <v>-0.005588512241054602</v>
+      </c>
+      <c r="R12">
+        <v>0.08740359897172237</v>
+      </c>
+      <c r="S12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>0.8720930232558139</v>
+      </c>
+      <c r="G13">
+        <v>0.8236434108527132</v>
+      </c>
+      <c r="H13">
+        <v>0.04844961240310075</v>
+      </c>
+      <c r="I13">
+        <v>0.01167201843526879</v>
+      </c>
+      <c r="J13">
+        <v>0.08577835648148151</v>
+      </c>
+      <c r="K13">
+        <v>0.01094842344892238</v>
+      </c>
+      <c r="L13">
+        <v>0.01255639356682853</v>
+      </c>
+      <c r="M13">
+        <v>1.702106891515892</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13">
+        <v>0.02189684689784475</v>
+      </c>
+      <c r="P13" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13">
+        <v>0.003838771593090211</v>
+      </c>
+      <c r="R13">
+        <v>0.09452543094275381</v>
+      </c>
+      <c r="S13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14">
         <v>0.9360670194003528</v>
       </c>
-      <c r="G2">
-        <v>0.01367801548960967</v>
-      </c>
-      <c r="H2">
-        <v>-0.005336812651498976</v>
-      </c>
-      <c r="I2">
-        <v>0.03269284363071832</v>
-      </c>
-      <c r="J2">
-        <v>0.1585783521869673</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2">
-        <v>0.1585783521869673</v>
-      </c>
-      <c r="O2" t="s">
-        <v>113</v>
-      </c>
-      <c r="P2">
-        <v>-0.009547469685576918</v>
-      </c>
-      <c r="Q2">
-        <v>0.03690350066479627</v>
-      </c>
-      <c r="R2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G14">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="H14">
+        <v>0.0471781305114638</v>
+      </c>
+      <c r="I14">
+        <v>0.01940274785435394</v>
+      </c>
+      <c r="J14">
+        <v>0.07495351316857367</v>
+      </c>
+      <c r="K14">
+        <v>0.0008712249487968415</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14">
+        <v>0.001742449897593683</v>
+      </c>
+      <c r="P14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q14">
+        <v>0.0132521474128741</v>
+      </c>
+      <c r="R14">
+        <v>0.0811041136100535</v>
+      </c>
+      <c r="S14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
-        <v>0.09039919269379848</v>
-      </c>
-      <c r="F3">
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15">
         <v>0.09607086470930229</v>
       </c>
-      <c r="G3">
-        <v>-0.005671672015503809</v>
-      </c>
-      <c r="H3">
-        <v>-0.01696010224074354</v>
-      </c>
-      <c r="I3">
-        <v>0.006063415874129986</v>
-      </c>
-      <c r="J3">
-        <v>0.349</v>
-      </c>
-      <c r="K3">
-        <v>0.06038851071385942</v>
-      </c>
-      <c r="L3">
-        <v>1.637225445824592</v>
-      </c>
-      <c r="M3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N3">
-        <v>0.349</v>
-      </c>
-      <c r="O3" t="s">
-        <v>114</v>
-      </c>
-      <c r="P3">
-        <v>-0.01950821088880687</v>
-      </c>
-      <c r="Q3">
-        <v>0.008164866857799255</v>
-      </c>
-      <c r="R3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G15">
+        <v>0.1235763627906977</v>
+      </c>
+      <c r="H15">
+        <v>-0.02750549808139537</v>
+      </c>
+      <c r="I15">
+        <v>-0.04313435688609747</v>
+      </c>
+      <c r="J15">
+        <v>-0.01196780749470757</v>
+      </c>
+      <c r="K15">
+        <v>0.0014</v>
+      </c>
+      <c r="L15">
+        <v>-0.06036792806785095</v>
+      </c>
+      <c r="M15">
+        <v>1.72</v>
+      </c>
+      <c r="N15" t="s">
+        <v>73</v>
+      </c>
+      <c r="O15">
+        <v>0.0018</v>
+      </c>
+      <c r="P15" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q15">
+        <v>-0.04617217904084742</v>
+      </c>
+      <c r="R15">
+        <v>-0.008838817121943308</v>
+      </c>
+      <c r="S15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
       </c>
-      <c r="E4">
-        <v>0.3017094343669052</v>
-      </c>
-      <c r="F4">
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
         <v>0.3154288386745751</v>
       </c>
-      <c r="G4">
-        <v>-0.01371940430766994</v>
-      </c>
-      <c r="H4">
-        <v>-0.04096857231250371</v>
-      </c>
-      <c r="I4">
-        <v>0.01379438013133473</v>
-      </c>
-      <c r="J4">
-        <v>0.3366</v>
-      </c>
-      <c r="K4">
-        <v>0.04410529743021843</v>
-      </c>
-      <c r="L4">
-        <v>1.658750048532445</v>
-      </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="N4">
-        <v>0.3366</v>
-      </c>
-      <c r="O4" t="s">
-        <v>114</v>
-      </c>
-      <c r="P4">
-        <v>-0.04655890094471718</v>
-      </c>
-      <c r="Q4">
-        <v>0.01912009232937731</v>
-      </c>
-      <c r="R4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G16">
+        <v>0.3822401917568288</v>
+      </c>
+      <c r="H16">
+        <v>-0.06681135308225372</v>
+      </c>
+      <c r="I16">
+        <v>-0.1061917788999018</v>
+      </c>
+      <c r="J16">
+        <v>-0.02801716367843521</v>
+      </c>
+      <c r="K16">
+        <v>0.0016</v>
+      </c>
+      <c r="L16">
+        <v>-0.06287739108654766</v>
+      </c>
+      <c r="M16">
+        <v>1.72</v>
+      </c>
+      <c r="N16" t="s">
+        <v>73</v>
+      </c>
+      <c r="O16">
+        <v>0.0022</v>
+      </c>
+      <c r="P16" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q16">
+        <v>-0.1131438348997234</v>
+      </c>
+      <c r="R16">
+        <v>-0.0204788712647841</v>
+      </c>
+      <c r="S16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="E5">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F5">
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17">
         <v>0.8043478260869565</v>
       </c>
-      <c r="G5">
-        <v>0.02898550724637683</v>
-      </c>
-      <c r="H5">
-        <v>-0.05263157894736842</v>
-      </c>
-      <c r="I5">
-        <v>0.1134832366215345</v>
-      </c>
-      <c r="J5">
+      <c r="G17">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="H17">
+        <v>0.04347826086956519</v>
+      </c>
+      <c r="I17">
+        <v>-0.03821656050955414</v>
+      </c>
+      <c r="J17">
+        <v>0.1268715944089079</v>
+      </c>
+      <c r="K17">
+        <v>0.3060346718543977</v>
+      </c>
+      <c r="L17">
+        <v>-0.007731958762886596</v>
+      </c>
+      <c r="M17">
+        <v>1.243243243243243</v>
+      </c>
+      <c r="N17" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17">
         <v>0.4938941871029767</v>
       </c>
-      <c r="K5">
-        <v>0.1566666666666667</v>
-      </c>
-      <c r="L5">
-        <v>1.1714295204668</v>
-      </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5">
-        <v>0.4938941871029767</v>
-      </c>
-      <c r="O5" t="s">
-        <v>113</v>
-      </c>
-      <c r="P5">
-        <v>-0.07142857142857142</v>
-      </c>
-      <c r="Q5">
-        <v>0.130241215008934</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="P17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="Q17">
+        <v>-0.05569153069153064</v>
+      </c>
+      <c r="R17">
+        <v>0.1481537875904076</v>
+      </c>
+      <c r="S17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="E6">
-        <v>0.8862433862433863</v>
-      </c>
-      <c r="F6">
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
         <v>0.8994708994708994</v>
       </c>
-      <c r="G6">
-        <v>-0.01322751322751314</v>
-      </c>
-      <c r="H6">
-        <v>-0.04639490333476167</v>
-      </c>
-      <c r="I6">
-        <v>0.02026352423192726</v>
-      </c>
-      <c r="J6">
-        <v>0.4462239688329609</v>
-      </c>
-      <c r="K6">
-        <v>0.1442978581876312</v>
-      </c>
-      <c r="L6">
-        <v>1.400632776710893</v>
-      </c>
-      <c r="M6" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6">
-        <v>0.4462239688329609</v>
-      </c>
-      <c r="O6" t="s">
-        <v>113</v>
-      </c>
-      <c r="P6">
-        <v>-0.05426356589147287</v>
-      </c>
-      <c r="Q6">
-        <v>0.02761214074670986</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="G18">
+        <v>0.8465608465608465</v>
+      </c>
+      <c r="H18">
+        <v>0.05291005291005291</v>
+      </c>
+      <c r="I18">
+        <v>0.01312335958005249</v>
+      </c>
+      <c r="J18">
+        <v>0.09230972194032881</v>
+      </c>
+      <c r="K18">
+        <v>0.01191397884158072</v>
+      </c>
+      <c r="L18">
+        <v>0.02927226035221758</v>
+      </c>
+      <c r="M18">
+        <v>1.511717281558992</v>
+      </c>
+      <c r="N18" t="s">
+        <v>74</v>
+      </c>
+      <c r="O18">
+        <v>0.03574193652474216</v>
+      </c>
+      <c r="P18" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="Q18">
+        <v>0.002741720565337171</v>
+      </c>
+      <c r="R18">
+        <v>0.1029690177624242</v>
+      </c>
+      <c r="S18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
         <v>51</v>
       </c>
-      <c r="E7">
-        <v>0.8720930232558139</v>
-      </c>
-      <c r="F7">
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
         <v>0.874031007751938</v>
       </c>
-      <c r="G7">
-        <v>-0.001937984496124034</v>
-      </c>
-      <c r="H7">
-        <v>-0.03475239539069325</v>
-      </c>
-      <c r="I7">
-        <v>0.03125</v>
-      </c>
-      <c r="J7">
-        <v>0.9094173748556938</v>
-      </c>
-      <c r="K7">
-        <v>0.1009144260952641</v>
-      </c>
-      <c r="L7">
-        <v>1.586004072823823</v>
-      </c>
-      <c r="M7" t="s">
-        <v>73</v>
-      </c>
-      <c r="N7">
-        <v>0.9094173748556938</v>
-      </c>
-      <c r="O7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P7">
-        <v>-0.04177596020833175</v>
-      </c>
-      <c r="Q7">
-        <v>0.03788432607331588</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="G19">
+        <v>0.8236434108527132</v>
+      </c>
+      <c r="H19">
+        <v>0.05038759689922478</v>
+      </c>
+      <c r="I19">
+        <v>0.013670542458577</v>
+      </c>
+      <c r="J19">
+        <v>0.08663281190468416</v>
+      </c>
+      <c r="K19">
+        <v>0.007770714070688979</v>
+      </c>
+      <c r="L19">
+        <v>-0.01383544821940237</v>
+      </c>
+      <c r="M19">
+        <v>1.72</v>
+      </c>
+      <c r="N19" t="s">
+        <v>74</v>
+      </c>
+      <c r="O19">
+        <v>0.01642263517338357</v>
+      </c>
+      <c r="P19" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8">
-        <v>0.9497450348899624</v>
-      </c>
-      <c r="F8">
-        <v>0.888888888888889</v>
-      </c>
-      <c r="G8">
-        <v>0.06085614600107347</v>
-      </c>
-      <c r="H8">
-        <v>0.03334994975402623</v>
-      </c>
-      <c r="I8">
-        <v>0.08836234224812071</v>
-      </c>
-      <c r="J8">
-        <v>1.448835277480167E-05</v>
-      </c>
-      <c r="M8" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8">
-        <v>4.346505832440501E-05</v>
-      </c>
-      <c r="O8" t="s">
-        <v>113</v>
-      </c>
-      <c r="P8">
-        <v>0.02725895814217121</v>
-      </c>
-      <c r="Q8">
-        <v>0.09445333385997573</v>
-      </c>
-      <c r="R8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9">
-        <v>0.09039919269379848</v>
-      </c>
-      <c r="F9">
-        <v>0.1235763627906977</v>
-      </c>
-      <c r="G9">
-        <v>-0.03317717009689918</v>
-      </c>
-      <c r="H9">
-        <v>-0.0483943797631313</v>
-      </c>
-      <c r="I9">
-        <v>-0.01828621828652867</v>
-      </c>
-      <c r="J9">
-        <v>0.0004</v>
-      </c>
-      <c r="K9">
-        <v>-0.04746069207779437</v>
-      </c>
-      <c r="L9">
-        <v>1.72</v>
-      </c>
-      <c r="M9" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9">
-        <v>0.0004</v>
-      </c>
-      <c r="O9" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9">
-        <v>-0.05126736698243801</v>
-      </c>
-      <c r="Q9">
-        <v>-0.01508697321136034</v>
-      </c>
-      <c r="R9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10">
-        <v>0.3017094343669052</v>
-      </c>
-      <c r="F10">
-        <v>0.3822401917568288</v>
-      </c>
-      <c r="G10">
-        <v>-0.08053075738992366</v>
-      </c>
-      <c r="H10">
-        <v>-0.1192318182347926</v>
-      </c>
-      <c r="I10">
-        <v>-0.04360054027952263</v>
-      </c>
-      <c r="J10">
-        <v>0.0004</v>
-      </c>
-      <c r="K10">
-        <v>-0.05550309531095601</v>
-      </c>
-      <c r="L10">
-        <v>1.72</v>
-      </c>
-      <c r="M10" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10">
-        <v>0.0004</v>
-      </c>
-      <c r="O10" t="s">
-        <v>114</v>
-      </c>
-      <c r="P10">
-        <v>-0.1256862042172851</v>
-      </c>
-      <c r="Q10">
-        <v>-0.03537531056256221</v>
-      </c>
-      <c r="R10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="F11">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="G11">
-        <v>0.07246376811594202</v>
-      </c>
-      <c r="H11">
-        <v>-0.01563115157480314</v>
-      </c>
-      <c r="I11">
-        <v>0.1677441004546439</v>
-      </c>
-      <c r="J11">
-        <v>0.1144834666737794</v>
-      </c>
-      <c r="K11">
-        <v>0.11767755313634</v>
-      </c>
-      <c r="L11">
-        <v>1.188514823808941</v>
-      </c>
-      <c r="M11" t="s">
-        <v>73</v>
-      </c>
-      <c r="N11">
-        <v>0.3434504000213381</v>
-      </c>
-      <c r="O11" t="s">
-        <v>113</v>
-      </c>
-      <c r="P11">
-        <v>-0.03651368760064402</v>
-      </c>
-      <c r="Q11">
-        <v>0.1830387554082666</v>
-      </c>
-      <c r="R11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12">
-        <v>0.8862433862433863</v>
-      </c>
-      <c r="F12">
-        <v>0.8465608465608465</v>
-      </c>
-      <c r="G12">
-        <v>0.03968253968253976</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0.07859078590785908</v>
-      </c>
-      <c r="J12">
-        <v>0.04645567201881207</v>
-      </c>
-      <c r="K12">
-        <v>-0.01055297593921486</v>
-      </c>
-      <c r="L12">
-        <v>1.542857142857143</v>
-      </c>
-      <c r="M12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12">
-        <v>0.09291134403762413</v>
-      </c>
-      <c r="O12" t="s">
-        <v>113</v>
-      </c>
-      <c r="P12">
-        <v>-0.005588512241054602</v>
-      </c>
-      <c r="Q12">
-        <v>0.08740359897172237</v>
-      </c>
-      <c r="R12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13">
-        <v>0.8720930232558139</v>
-      </c>
-      <c r="F13">
-        <v>0.8236434108527132</v>
-      </c>
-      <c r="G13">
-        <v>0.04844961240310075</v>
-      </c>
-      <c r="H13">
-        <v>0.01167201843526879</v>
-      </c>
-      <c r="I13">
-        <v>0.08577835648148151</v>
-      </c>
-      <c r="J13">
-        <v>0.01094842344892238</v>
-      </c>
-      <c r="K13">
-        <v>0.01255639356682853</v>
-      </c>
-      <c r="L13">
-        <v>1.702106891515892</v>
-      </c>
-      <c r="M13" t="s">
-        <v>73</v>
-      </c>
-      <c r="N13">
-        <v>0.02189684689784475</v>
-      </c>
-      <c r="O13" t="s">
-        <v>113</v>
-      </c>
-      <c r="P13">
-        <v>0.003838771593090211</v>
-      </c>
-      <c r="Q13">
-        <v>0.09452543094275381</v>
-      </c>
-      <c r="R13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14">
-        <v>0.9360670194003528</v>
-      </c>
-      <c r="F14">
-        <v>0.888888888888889</v>
-      </c>
-      <c r="G14">
-        <v>0.0471781305114638</v>
-      </c>
-      <c r="H14">
-        <v>0.01940274785435394</v>
-      </c>
-      <c r="I14">
-        <v>0.07495351316857367</v>
-      </c>
-      <c r="J14">
-        <v>0.0008712249487968415</v>
-      </c>
-      <c r="M14" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14">
-        <v>0.001742449897593683</v>
-      </c>
-      <c r="O14" t="s">
-        <v>113</v>
-      </c>
-      <c r="P14">
-        <v>0.0132521474128741</v>
-      </c>
-      <c r="Q14">
-        <v>0.0811041136100535</v>
-      </c>
-      <c r="R14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15">
-        <v>0.09607086470930229</v>
-      </c>
-      <c r="F15">
-        <v>0.1235763627906977</v>
-      </c>
-      <c r="G15">
-        <v>-0.02750549808139537</v>
-      </c>
-      <c r="H15">
-        <v>-0.04313435688609747</v>
-      </c>
-      <c r="I15">
-        <v>-0.01196780749470757</v>
-      </c>
-      <c r="J15">
-        <v>0.0014</v>
-      </c>
-      <c r="K15">
-        <v>-0.06036792806785095</v>
-      </c>
-      <c r="L15">
-        <v>1.72</v>
-      </c>
-      <c r="M15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15">
-        <v>0.0018</v>
-      </c>
-      <c r="O15" t="s">
-        <v>114</v>
-      </c>
-      <c r="P15">
-        <v>-0.04617217904084742</v>
-      </c>
-      <c r="Q15">
-        <v>-0.008838817121943308</v>
-      </c>
-      <c r="R15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16">
-        <v>0.3154288386745751</v>
-      </c>
-      <c r="F16">
-        <v>0.3822401917568288</v>
-      </c>
-      <c r="G16">
-        <v>-0.06681135308225372</v>
-      </c>
-      <c r="H16">
-        <v>-0.1061917788999018</v>
-      </c>
-      <c r="I16">
-        <v>-0.02801716367843521</v>
-      </c>
-      <c r="J16">
-        <v>0.0016</v>
-      </c>
-      <c r="K16">
-        <v>-0.06287739108654766</v>
-      </c>
-      <c r="L16">
-        <v>1.72</v>
-      </c>
-      <c r="M16" t="s">
-        <v>72</v>
-      </c>
-      <c r="N16">
-        <v>0.0022</v>
-      </c>
-      <c r="O16" t="s">
-        <v>114</v>
-      </c>
-      <c r="P16">
-        <v>-0.1131438348997234</v>
-      </c>
-      <c r="Q16">
-        <v>-0.0204788712647841</v>
-      </c>
-      <c r="R16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17">
-        <v>0.8043478260869565</v>
-      </c>
-      <c r="F17">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="G17">
-        <v>0.04347826086956519</v>
-      </c>
-      <c r="H17">
-        <v>-0.03821656050955414</v>
-      </c>
-      <c r="I17">
-        <v>0.1268715944089079</v>
-      </c>
-      <c r="J17">
-        <v>0.3060346718543977</v>
-      </c>
-      <c r="K17">
-        <v>-0.007731958762886596</v>
-      </c>
-      <c r="L17">
-        <v>1.243243243243243</v>
-      </c>
-      <c r="M17" t="s">
-        <v>73</v>
-      </c>
-      <c r="N17">
-        <v>0.4938941871029767</v>
-      </c>
-      <c r="O17" t="s">
-        <v>113</v>
-      </c>
-      <c r="P17">
-        <v>-0.05569153069153064</v>
-      </c>
-      <c r="Q17">
-        <v>0.1481537875904076</v>
-      </c>
-      <c r="R17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18">
-        <v>0.8994708994708994</v>
-      </c>
-      <c r="F18">
-        <v>0.8465608465608465</v>
-      </c>
-      <c r="G18">
-        <v>0.05291005291005291</v>
-      </c>
-      <c r="H18">
-        <v>0.01312335958005249</v>
-      </c>
-      <c r="I18">
-        <v>0.09230972194032881</v>
-      </c>
-      <c r="J18">
-        <v>0.01191397884158072</v>
-      </c>
-      <c r="K18">
-        <v>0.02927226035221758</v>
-      </c>
-      <c r="L18">
-        <v>1.511717281558992</v>
-      </c>
-      <c r="M18" t="s">
-        <v>73</v>
-      </c>
-      <c r="N18">
-        <v>0.03574193652474216</v>
-      </c>
-      <c r="O18" t="s">
-        <v>113</v>
-      </c>
-      <c r="P18">
-        <v>0.002741720565337171</v>
-      </c>
-      <c r="Q18">
-        <v>0.1029690177624242</v>
-      </c>
-      <c r="R18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19">
-        <v>0.874031007751938</v>
-      </c>
-      <c r="F19">
-        <v>0.8236434108527132</v>
-      </c>
-      <c r="G19">
-        <v>0.05038759689922478</v>
-      </c>
-      <c r="H19">
-        <v>0.013670542458577</v>
-      </c>
-      <c r="I19">
-        <v>0.08663281190468416</v>
-      </c>
-      <c r="J19">
-        <v>0.007770714070688979</v>
-      </c>
-      <c r="K19">
-        <v>-0.01383544821940237</v>
-      </c>
-      <c r="L19">
-        <v>1.72</v>
-      </c>
-      <c r="M19" t="s">
-        <v>73</v>
-      </c>
-      <c r="N19">
-        <v>0.01642263517338357</v>
-      </c>
-      <c r="O19" t="s">
-        <v>113</v>
-      </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.005802707930367505</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>0.09554657303978027</v>
       </c>
-      <c r="R19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.9572425828970333</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.954261198371146</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.002981384525887365</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>-0.01606351322333427</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.022026282275109</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7589783551323271</v>
       </c>
-      <c r="M20" t="s">
-        <v>111</v>
-      </c>
-      <c r="N20">
+      <c r="N20" t="s">
+        <v>115</v>
+      </c>
+      <c r="O20">
         <v>0.7589783551323271</v>
       </c>
-      <c r="O20" t="s">
-        <v>113</v>
-      </c>
-      <c r="P20">
+      <c r="P20" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20">
         <v>-0.02028082889276633</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>0.02624359794454106</v>
       </c>
-      <c r="R20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>51</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.08409677600760461</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.08091932330798474</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.003177452699619873</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>-0.01107254006932483</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.01767353194661654</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.6637999999999999</v>
       </c>
-      <c r="M21" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21">
+      <c r="N21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O21">
         <v>0.6637999999999999</v>
       </c>
-      <c r="O21" t="s">
-        <v>114</v>
-      </c>
-      <c r="P21">
+      <c r="P21" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q21">
         <v>-0.0142294328360232</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>0.02058433823526295</v>
       </c>
-      <c r="R21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>51</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.2869453687617096</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.2760765501167317</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.01086881864497791</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-0.02212520523906435</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.04443815211367416</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.516</v>
       </c>
-      <c r="M22" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22">
+      <c r="N22" t="s">
+        <v>73</v>
+      </c>
+      <c r="O22">
         <v>0.516</v>
       </c>
-      <c r="O22" t="s">
-        <v>114</v>
-      </c>
-      <c r="P22">
+      <c r="P22" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q22">
         <v>-0.02924065294566617</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>0.05097829023562198</v>
       </c>
-      <c r="R22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -5186,299 +5434,317 @@
         <v>92</v>
       </c>
       <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" t="s">
         <v>50</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>51</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.8194444444444444</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.8055555555555556</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.01388888888888884</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-0.08571428571428572</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.1143091334894614</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>1</v>
       </c>
-      <c r="M23" t="s">
-        <v>112</v>
-      </c>
-      <c r="N23">
+      <c r="N23" t="s">
+        <v>116</v>
+      </c>
+      <c r="O23">
         <v>1</v>
       </c>
-      <c r="O23" t="s">
-        <v>113</v>
-      </c>
-      <c r="P23">
+      <c r="P23" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q23">
         <v>-0.1084520884520883</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>0.1354452054794529</v>
       </c>
-      <c r="R23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
         <v>50</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>51</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.9057591623036649</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.9162303664921466</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-0.01047120418848169</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>-0.05913978494623656</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.03685185185185189</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.8311704095417624</v>
       </c>
-      <c r="M24" t="s">
-        <v>112</v>
-      </c>
-      <c r="N24">
+      <c r="N24" t="s">
+        <v>116</v>
+      </c>
+      <c r="O24">
         <v>0.8311704095417624</v>
       </c>
-      <c r="O24" t="s">
-        <v>113</v>
-      </c>
-      <c r="P24">
+      <c r="P24" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q24">
         <v>-0.06964953136679887</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>0.04973337731233337</v>
       </c>
-      <c r="R24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.8821292775665399</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.8859315589353612</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>-0.003802281368821325</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>-0.04562737642585551</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.04182509505703422</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1</v>
       </c>
-      <c r="M25" t="s">
-        <v>112</v>
-      </c>
-      <c r="N25">
+      <c r="N25" t="s">
+        <v>116</v>
+      </c>
+      <c r="O25">
         <v>1</v>
       </c>
-      <c r="O25" t="s">
-        <v>113</v>
-      </c>
-      <c r="P25">
+      <c r="P25" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q25">
         <v>-0.05703422053231939</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>0.04942965779467681</v>
       </c>
-      <c r="R25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
         <v>50</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>52</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.9572425828970333</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.9070680628272252</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.05017452006980816</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0.0161306298087938</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>0.08421841033082253</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>0.003869222643548615</v>
       </c>
-      <c r="M26" t="s">
-        <v>111</v>
-      </c>
-      <c r="N26">
+      <c r="N26" t="s">
+        <v>115</v>
+      </c>
+      <c r="O26">
         <v>0.01160766793064584</v>
       </c>
-      <c r="O26" t="s">
-        <v>113</v>
-      </c>
-      <c r="P26">
+      <c r="P26" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q26">
         <v>0.00859192659616724</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>0.09175711354344908</v>
       </c>
-      <c r="R26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
         <v>50</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>52</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.08409677600760461</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.1173666533840304</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>-0.03326987737642581</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>-0.05333303837337318</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>-0.01403268008184253</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>0.0032</v>
       </c>
-      <c r="M27" t="s">
-        <v>72</v>
-      </c>
-      <c r="N27">
+      <c r="N27" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27">
         <v>0.006</v>
       </c>
-      <c r="O27" t="s">
-        <v>114</v>
-      </c>
-      <c r="P27">
+      <c r="P27" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q27">
         <v>-0.05724448040629365</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>-0.009295274346557969</v>
       </c>
-      <c r="R27" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="S27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
         <v>50</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>52</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.2869453687617096</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.3615170226541687</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>-0.07457165389245912</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-0.1233238778955756</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>-0.02701278723372434</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>0.0056</v>
       </c>
-      <c r="M28" t="s">
-        <v>72</v>
-      </c>
-      <c r="N28">
+      <c r="N28" t="s">
+        <v>73</v>
+      </c>
+      <c r="O28">
         <v>0.0108</v>
       </c>
-      <c r="O28" t="s">
-        <v>114</v>
-      </c>
-      <c r="P28">
+      <c r="P28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q28">
         <v>-0.1321164458071846</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>-0.01702686197773369</v>
       </c>
-      <c r="R28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="S28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -5486,299 +5752,317 @@
         <v>92</v>
       </c>
       <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s">
         <v>50</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>52</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.8194444444444444</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.04166666666666663</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>-0.06451612903225806</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>0.1470588235294118</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0.6055766163353462</v>
       </c>
-      <c r="M29" t="s">
-        <v>112</v>
-      </c>
-      <c r="N29">
+      <c r="N29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O29">
         <v>1</v>
       </c>
-      <c r="O29" t="s">
-        <v>113</v>
-      </c>
-      <c r="P29">
+      <c r="P29" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q29">
         <v>-0.08893822029095019</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>0.171875</v>
       </c>
-      <c r="R29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
         <v>50</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>52</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.9057591623036649</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.837696335078534</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.06806282722513091</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0.0154639175257732</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>0.1237113402061856</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>0.02585758046344289</v>
       </c>
-      <c r="M30" t="s">
-        <v>112</v>
-      </c>
-      <c r="N30">
+      <c r="N30" t="s">
+        <v>116</v>
+      </c>
+      <c r="O30">
         <v>0.05171516092688578</v>
       </c>
-      <c r="O30" t="s">
-        <v>113</v>
-      </c>
-      <c r="P30">
+      <c r="P30" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q30">
         <v>0</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0.1371632174931668</v>
       </c>
-      <c r="R30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" t="s">
         <v>50</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>52</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.8821292775665399</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.8212927756653993</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.06083650190114065</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0.01140684410646388</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>0.1102661596958175</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>0.02373851525005458</v>
       </c>
-      <c r="M31" t="s">
-        <v>112</v>
-      </c>
-      <c r="N31">
+      <c r="N31" t="s">
+        <v>116</v>
+      </c>
+      <c r="O31">
         <v>0.04747703050010915</v>
       </c>
-      <c r="O31" t="s">
-        <v>113</v>
-      </c>
-      <c r="P31">
+      <c r="P31" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q31">
         <v>0</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.1216730038022814</v>
       </c>
-      <c r="R31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>52</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.954261198371146</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.9070680628272252</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.04719313554392079</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>0.01137451854762576</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0.08301175254021582</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>0.009812492570670151</v>
       </c>
-      <c r="M32" t="s">
-        <v>111</v>
-      </c>
-      <c r="N32">
+      <c r="N32" t="s">
+        <v>115</v>
+      </c>
+      <c r="O32">
         <v>0.0196249851413403</v>
       </c>
-      <c r="O32" t="s">
-        <v>113</v>
-      </c>
-      <c r="P32">
+      <c r="P32" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q32">
         <v>0.003442818587617621</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.09094345250022397</v>
       </c>
-      <c r="R32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>52</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.08091932330798474</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.1173666533840304</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>-0.03644733007604568</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>-0.05932266260572364</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>-0.01460453971831455</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>0.0016</v>
       </c>
-      <c r="M33" t="s">
-        <v>72</v>
-      </c>
-      <c r="N33">
+      <c r="N33" t="s">
+        <v>73</v>
+      </c>
+      <c r="O33">
         <v>0.006</v>
       </c>
-      <c r="O33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P33">
+      <c r="P33" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q33">
         <v>-0.063099354823316</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>-0.009795305328775369</v>
       </c>
-      <c r="R33" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" t="s">
         <v>51</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>52</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.2760765501167317</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.3615170226541687</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>-0.08544047253743703</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>-0.1406807097413394</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>-0.03111577025431145</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>0.002</v>
       </c>
-      <c r="M34" t="s">
-        <v>72</v>
-      </c>
-      <c r="N34">
+      <c r="N34" t="s">
+        <v>73</v>
+      </c>
+      <c r="O34">
         <v>0.008399999999999999</v>
       </c>
-      <c r="O34" t="s">
-        <v>114</v>
-      </c>
-      <c r="P34">
+      <c r="P34" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q34">
         <v>-0.1494866851663962</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>-0.02139425990847783</v>
       </c>
-      <c r="R34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -5786,299 +6070,317 @@
         <v>92</v>
       </c>
       <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
         <v>51</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>52</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.8055555555555556</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.7777777777777778</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>0.02777777777777779</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>-0.07692307692307693</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>0.1375</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>0.8025873486341526</v>
       </c>
-      <c r="M35" t="s">
-        <v>112</v>
-      </c>
-      <c r="N35">
+      <c r="N35" t="s">
+        <v>116</v>
+      </c>
+      <c r="O35">
         <v>1</v>
       </c>
-      <c r="O35" t="s">
-        <v>113</v>
-      </c>
-      <c r="P35">
+      <c r="P35" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q35">
         <v>-0.1036050156739811</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.1643835616438356</v>
       </c>
-      <c r="R35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
         <v>51</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>52</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.9162303664921466</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.837696335078534</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>0.07853403141361259</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>0.02093695462478186</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>0.1358722034613761</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>0.01480610912734845</v>
       </c>
-      <c r="M36" t="s">
-        <v>112</v>
-      </c>
-      <c r="N36">
+      <c r="N36" t="s">
+        <v>116</v>
+      </c>
+      <c r="O36">
         <v>0.03878637069516434</v>
       </c>
-      <c r="O36" t="s">
-        <v>113</v>
-      </c>
-      <c r="P36">
+      <c r="P36" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q36">
         <v>0.01025641025641026</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>0.1530566801619438</v>
       </c>
-      <c r="R36" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" t="s">
         <v>51</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>52</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.8859315589353612</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.8212927756653993</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.06463878326996197</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>0.01140684410646388</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>0.1178707224334601</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>0.02227097895923274</v>
       </c>
-      <c r="M37" t="s">
-        <v>112</v>
-      </c>
-      <c r="N37">
+      <c r="N37" t="s">
+        <v>116</v>
+      </c>
+      <c r="O37">
         <v>0.04454195791846547</v>
       </c>
-      <c r="O37" t="s">
-        <v>113</v>
-      </c>
-      <c r="P37">
+      <c r="P37" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q37">
         <v>0.003802281368821293</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>0.1254752851711027</v>
       </c>
-      <c r="R37" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s">
         <v>50</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>51</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.9407308377896613</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.9163830821584832</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>0.02434775563117808</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>-0.008537871277605434</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>0.0572333825399616</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>0.1467487068347569</v>
       </c>
-      <c r="M38" t="s">
-        <v>111</v>
-      </c>
-      <c r="N38">
+      <c r="N38" t="s">
+        <v>115</v>
+      </c>
+      <c r="O38">
         <v>0.1467487068347569</v>
       </c>
-      <c r="O38" t="s">
-        <v>113</v>
-      </c>
-      <c r="P38">
+      <c r="P38" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q38">
         <v>-0.01582008783175719</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>0.06451559909411336</v>
       </c>
-      <c r="R38" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="S38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
         <v>50</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>51</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.09695071675889327</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.1118212812648221</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-0.01487056450592883</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>-0.03288227345609322</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>0.003186446569978699</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>0.1052</v>
       </c>
-      <c r="M39" t="s">
-        <v>72</v>
-      </c>
-      <c r="N39">
+      <c r="N39" t="s">
+        <v>73</v>
+      </c>
+      <c r="O39">
         <v>0.1868</v>
       </c>
-      <c r="O39" t="s">
-        <v>114</v>
-      </c>
-      <c r="P39">
+      <c r="P39" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q39">
         <v>-0.03571830630142864</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>0.005977177289570985</v>
       </c>
-      <c r="R39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="S39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
         <v>50</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>51</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.3170570598774448</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.3563365536576291</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>-0.03927949378018425</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>-0.08396634944318943</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.003910375492078746</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>0.07779999999999999</v>
       </c>
-      <c r="M40" t="s">
-        <v>72</v>
-      </c>
-      <c r="N40">
+      <c r="N40" t="s">
+        <v>73</v>
+      </c>
+      <c r="O40">
         <v>0.1416</v>
       </c>
-      <c r="O40" t="s">
-        <v>114</v>
-      </c>
-      <c r="P40">
+      <c r="P40" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q40">
         <v>-0.08982206866643555</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>0.01126308110606705</v>
       </c>
-      <c r="R40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -6086,299 +6388,317 @@
         <v>92</v>
       </c>
       <c r="C41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
         <v>50</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>51</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.8484848484848485</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.803030303030303</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>0.04545454545454553</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>-0.0847457627118644</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>0.1739130434782609</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>0.6463551955394902</v>
       </c>
-      <c r="M41" t="s">
-        <v>112</v>
-      </c>
-      <c r="N41">
+      <c r="N41" t="s">
+        <v>116</v>
+      </c>
+      <c r="O41">
         <v>0.6463551955394902</v>
       </c>
-      <c r="O41" t="s">
-        <v>113</v>
-      </c>
-      <c r="P41">
+      <c r="P41" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q41">
         <v>-0.1131249999999998</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>0.2034996861268049</v>
       </c>
-      <c r="R41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" t="s">
         <v>50</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>51</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.8663101604278075</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.8823529411764706</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>-0.01604278074866305</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>-0.05945945945945946</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0.02660285584253046</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>0.6276258050283593</v>
       </c>
-      <c r="M42" t="s">
-        <v>112</v>
-      </c>
-      <c r="N42">
+      <c r="N42" t="s">
+        <v>116</v>
+      </c>
+      <c r="O42">
         <v>0.8501067391385259</v>
       </c>
-      <c r="O42" t="s">
-        <v>113</v>
-      </c>
-      <c r="P42">
+      <c r="P42" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q42">
         <v>-0.07119289340101519</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>0.03333333333333333</v>
       </c>
-      <c r="R42" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
         <v>50</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>51</v>
-      </c>
-      <c r="E43">
-        <v>0.8616600790513834</v>
       </c>
       <c r="F43">
         <v>0.8616600790513834</v>
       </c>
       <c r="G43">
+        <v>0.8616600790513834</v>
+      </c>
+      <c r="H43">
         <v>0</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>-0.04743083003952569</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0.04743083003952569</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" t="s">
-        <v>112</v>
-      </c>
-      <c r="N43">
+      <c r="N43" t="s">
+        <v>116</v>
+      </c>
+      <c r="O43">
         <v>1</v>
       </c>
-      <c r="O43" t="s">
-        <v>113</v>
-      </c>
-      <c r="P43">
+      <c r="P43" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q43">
         <v>-0.05533596837944664</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>0.05533596837944664</v>
       </c>
-      <c r="R43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
         <v>50</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>52</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.9407308377896613</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.8704423918327662</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>0.0702884459568951</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>0.02325072430146023</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>0.11732616761233</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>0.003403025345125086</v>
       </c>
-      <c r="M44" t="s">
-        <v>111</v>
-      </c>
-      <c r="N44">
+      <c r="N44" t="s">
+        <v>115</v>
+      </c>
+      <c r="O44">
         <v>0.01020907603537526</v>
       </c>
-      <c r="O44" t="s">
-        <v>113</v>
-      </c>
-      <c r="P44">
+      <c r="P44" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q44">
         <v>0.01283465784607815</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>0.127742234067712</v>
       </c>
-      <c r="R44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="S44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
         <v>50</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>52</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.09695071675889327</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.130031515256917</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>-0.03308079849802376</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>-0.05855212414881788</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>-0.01034818093491874</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>0.007</v>
       </c>
-      <c r="M45" t="s">
-        <v>72</v>
-      </c>
-      <c r="N45">
+      <c r="N45" t="s">
+        <v>73</v>
+      </c>
+      <c r="O45">
         <v>0.0166</v>
       </c>
-      <c r="O45" t="s">
-        <v>114</v>
-      </c>
-      <c r="P45">
+      <c r="P45" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q45">
         <v>-0.06143081418824267</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>-0.004730782807804843</v>
       </c>
-      <c r="R45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="S45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" t="s">
         <v>50</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>52</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.3170570598774448</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.4037824584524793</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>-0.08672539857503453</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>-0.1531605520737868</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>-0.03011349316215359</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>0.007</v>
       </c>
-      <c r="M46" t="s">
-        <v>72</v>
-      </c>
-      <c r="N46">
+      <c r="N46" t="s">
+        <v>73</v>
+      </c>
+      <c r="O46">
         <v>0.0138</v>
       </c>
-      <c r="O46" t="s">
-        <v>114</v>
-      </c>
-      <c r="P46">
+      <c r="P46" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q46">
         <v>-0.1592997954158392</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>-0.01415100173422988</v>
       </c>
-      <c r="R46" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -6386,299 +6706,317 @@
         <v>92</v>
       </c>
       <c r="C47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
         <v>50</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>52</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.8484848484848485</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.7424242424242424</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>0.1060606060606061</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-0.03947368421052631</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>0.2424242424242424</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>0.2109029260566068</v>
       </c>
-      <c r="M47" t="s">
-        <v>112</v>
-      </c>
-      <c r="N47">
+      <c r="N47" t="s">
+        <v>116</v>
+      </c>
+      <c r="O47">
         <v>0.6327087781698203</v>
       </c>
-      <c r="O47" t="s">
-        <v>113</v>
-      </c>
-      <c r="P47">
+      <c r="P47" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q47">
         <v>-0.07352941176470588</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>0.2711864406779661</v>
       </c>
-      <c r="R47" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="S47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" t="s">
         <v>50</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>52</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.8663101604278075</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.8556149732620321</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>0.01069518716577544</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>-0.04591836734693878</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>0.06595227976443453</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>0.8501067391385259</v>
       </c>
-      <c r="M48" t="s">
-        <v>112</v>
-      </c>
-      <c r="N48">
+      <c r="N48" t="s">
+        <v>116</v>
+      </c>
+      <c r="O48">
         <v>0.8501067391385259</v>
       </c>
-      <c r="O48" t="s">
-        <v>113</v>
-      </c>
-      <c r="P48">
+      <c r="P48" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q48">
         <v>-0.05615820998675333</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>0.07951283350219536</v>
       </c>
-      <c r="R48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="S48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" t="s">
         <v>50</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>52</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.8616600790513834</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.8260869565217391</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>0.03557312252964429</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>-0.01976284584980237</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>0.09090909090909091</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>0.2626182904425174</v>
       </c>
-      <c r="M49" t="s">
-        <v>112</v>
-      </c>
-      <c r="N49">
+      <c r="N49" t="s">
+        <v>116</v>
+      </c>
+      <c r="O49">
         <v>0.5252365808850348</v>
       </c>
-      <c r="O49" t="s">
-        <v>113</v>
-      </c>
-      <c r="P49">
+      <c r="P49" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q49">
         <v>-0.03162055335968379</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>0.1001976284584995</v>
       </c>
-      <c r="R49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="S49" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s">
         <v>51</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>52</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.9163830821584832</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.8704423918327662</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>0.04594069032571702</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>0.0002701670605949474</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>0.09161121359083908</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>0.04866005335540764</v>
       </c>
-      <c r="M50" t="s">
-        <v>111</v>
-      </c>
-      <c r="N50">
+      <c r="N50" t="s">
+        <v>115</v>
+      </c>
+      <c r="O50">
         <v>0.09732010671081527</v>
       </c>
-      <c r="O50" t="s">
-        <v>113</v>
-      </c>
-      <c r="P50">
+      <c r="P50" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q50">
         <v>-0.009843146013245659</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>0.1017245266646797</v>
       </c>
-      <c r="R50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="S50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" t="s">
         <v>51</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>52</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.1118212812648221</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.130031515256917</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>-0.01821023399209493</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>-0.04208292671189801</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>0.00481220577491211</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>0.1366</v>
       </c>
-      <c r="M51" t="s">
-        <v>72</v>
-      </c>
-      <c r="N51">
+      <c r="N51" t="s">
+        <v>73</v>
+      </c>
+      <c r="O51">
         <v>0.1868</v>
       </c>
-      <c r="O51" t="s">
-        <v>114</v>
-      </c>
-      <c r="P51">
+      <c r="P51" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q51">
         <v>-0.0459950736638484</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>0.009574605679658545</v>
       </c>
-      <c r="R51" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" t="s">
         <v>51</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>52</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.3563365536576291</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.4037824584524793</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>-0.04744590479485028</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>-0.1062323134937177</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>0.01013852501960102</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>0.1234</v>
       </c>
-      <c r="M52" t="s">
-        <v>72</v>
-      </c>
-      <c r="N52">
+      <c r="N52" t="s">
+        <v>73</v>
+      </c>
+      <c r="O52">
         <v>0.1416</v>
       </c>
-      <c r="O52" t="s">
-        <v>114</v>
-      </c>
-      <c r="P52">
+      <c r="P52" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q52">
         <v>-0.1179283647360767</v>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <v>0.02303655514637615</v>
       </c>
-      <c r="R52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -6686,146 +7024,155 @@
         <v>92</v>
       </c>
       <c r="C53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" t="s">
         <v>51</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>52</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.803030303030303</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.7424242424242424</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>0.06060606060606055</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>-0.0625</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>0.1864406779661017</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>0.4795001221869534</v>
       </c>
-      <c r="M53" t="s">
-        <v>112</v>
-      </c>
-      <c r="N53">
+      <c r="N53" t="s">
+        <v>116</v>
+      </c>
+      <c r="O53">
         <v>0.6463551955394902</v>
       </c>
-      <c r="O53" t="s">
-        <v>113</v>
-      </c>
-      <c r="P53">
+      <c r="P53" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q53">
         <v>-0.09015151515151501</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>0.213666666666667</v>
       </c>
-      <c r="R53" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" t="s">
         <v>51</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>52</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.8823529411764706</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.8556149732620321</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>0.0267379679144385</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>-0.02748011656851434</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>0.0855763517528224</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>0.4576140668763148</v>
       </c>
-      <c r="M54" t="s">
-        <v>112</v>
-      </c>
-      <c r="N54">
+      <c r="N54" t="s">
+        <v>116</v>
+      </c>
+      <c r="O54">
         <v>0.8501067391385259</v>
       </c>
-      <c r="O54" t="s">
-        <v>113</v>
-      </c>
-      <c r="P54">
+      <c r="P54" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q54">
         <v>-0.04218323586744636</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>0.09913967059336842</v>
       </c>
-      <c r="R54" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" t="s">
         <v>51</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>52</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.8616600790513834</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.8260869565217391</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>0.03557312252964429</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>-0.0158102766798419</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>0.09090909090909091</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>0.2432427057426535</v>
       </c>
-      <c r="M55" t="s">
-        <v>112</v>
-      </c>
-      <c r="N55">
+      <c r="N55" t="s">
+        <v>116</v>
+      </c>
+      <c r="O55">
         <v>0.486485411485307</v>
       </c>
-      <c r="O55" t="s">
-        <v>113</v>
-      </c>
-      <c r="P55">
+      <c r="P55" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q55">
         <v>-0.02766798418972332</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>0.1001976284584995</v>
       </c>
-      <c r="R55" t="s">
-        <v>117</v>
+      <c r="S55" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6835,224 +7182,237 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
-    <col min="3" max="17" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="18" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="M1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>516</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>300</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>216</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.72</v>
       </c>
-      <c r="K2" t="b">
+      <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>4999</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>42</v>
       </c>
-      <c r="N2" t="s">
-        <v>139</v>
-      </c>
       <c r="O2" t="s">
-        <v>140</v>
-      </c>
-      <c r="P2" t="b">
+        <v>92</v>
+      </c>
+      <c r="P2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3">
-        <v>263</v>
+        <v>142</v>
+      </c>
+      <c r="G3" t="s">
+        <v>127</v>
       </c>
       <c r="H3">
         <v>263</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" t="b">
+      <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>4999</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
-        <v>139</v>
-      </c>
       <c r="O3" t="s">
-        <v>140</v>
-      </c>
-      <c r="P3" t="b">
+        <v>92</v>
+      </c>
+      <c r="P3" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4">
-        <v>253</v>
+        <v>142</v>
+      </c>
+      <c r="G4" t="s">
+        <v>127</v>
       </c>
       <c r="H4">
         <v>253</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" t="b">
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>4999</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>139</v>
-      </c>
       <c r="O4" t="s">
-        <v>140</v>
-      </c>
-      <c r="P4" t="b">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>141</v>
+      <c r="R4" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_classifier_results.xlsx
+++ b/examples/example_classifier_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="135">
   <si>
     <t>Group</t>
   </si>
@@ -44,12 +44,6 @@
     <t>AUC Diff 95% CI high</t>
   </si>
   <si>
-    <t>AUC Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>AUC Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Obuchowski (AUC) p</t>
   </si>
   <si>
@@ -107,12 +101,6 @@
     <t>Sensitivity Diff 95% CI high</t>
   </si>
   <si>
-    <t>Sensitivity Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>Sensitivity Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Sensitivity p</t>
   </si>
   <si>
@@ -128,12 +116,6 @@
     <t>Specificity Diff 95% CI high</t>
   </si>
   <si>
-    <t>Specificity Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>Specificity Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Specificity p</t>
   </si>
   <si>
@@ -149,12 +131,6 @@
     <t>Accuracy Diff 95% CI high</t>
   </si>
   <si>
-    <t>Accuracy Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>Accuracy Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Accuracy p</t>
   </si>
   <si>
@@ -194,10 +170,10 @@
     <t>AUC Test</t>
   </si>
   <si>
-    <t>Brier score Test</t>
-  </si>
-  <si>
-    <t>Log-loss Test</t>
+    <t>Brier Score Test</t>
+  </si>
+  <si>
+    <t>Log-Loss Test</t>
   </si>
   <si>
     <t>Sensitivity Test</t>
@@ -251,10 +227,10 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Hommel: AUC, Sensitivity, Specificity, Accuracy; Romano-Wolf step-down: Brier score, Log-loss</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Bonferroni (normal theory, Obuchowski SE): AUC; Romano-Wolf simultaneous (max-|t|): Brier score, Log-loss; Bonferroni (percentile bootstrap): Sensitivity, Specificity, Accuracy. Brier score and log-loss: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). AUC: difference ± z × SE, z the normal quantile for coverage 1 - 0.05/m (Bonferroni). Sensitivity, specificity and accuracy: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Hommel: AUC, Sensitivity, Specificity, Accuracy; Romano-Wolf step-down: Brier Score, Log-Loss</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group, for the Brier score and log-loss only: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). The AUC, sensitivity, specificity and accuracy have no adjusted interval: their adjusted p-values (Romano-Wolf from a different statistic, or Hommel) have no matching interval, so their CIs are unadjusted. fwer_method='bonferroni' gives Bonferroni p-values with matching intervals for every metric</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
@@ -377,16 +353,10 @@
     <t>Romano-Wolf step-down</t>
   </si>
   <si>
-    <t>Bonferroni (normal theory, Obuchowski SE)</t>
+    <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
   </si>
   <si>
     <t>Romano-Wolf simultaneous (max-|t|)</t>
-  </si>
-  <si>
-    <t>Bonferroni (percentile bootstrap)</t>
-  </si>
-  <si>
-    <t>Bonferroni (normal theory, DeLong SE)</t>
   </si>
   <si>
     <t>definition</t>
@@ -784,24 +754,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="22.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" customWidth="1"/>
-    <col min="13" max="17" width="22.7109375" customWidth="1"/>
-    <col min="18" max="19" width="15.7109375" customWidth="1"/>
-    <col min="20" max="24" width="22.7109375" customWidth="1"/>
-    <col min="25" max="26" width="15.7109375" customWidth="1"/>
-    <col min="27" max="31" width="22.7109375" customWidth="1"/>
-    <col min="32" max="33" width="15.7109375" customWidth="1"/>
-    <col min="34" max="38" width="22.7109375" customWidth="1"/>
-    <col min="39" max="40" width="15.7109375" customWidth="1"/>
-    <col min="41" max="45" width="22.7109375" customWidth="1"/>
-    <col min="46" max="47" width="15.7109375" customWidth="1"/>
+    <col min="1" max="8" width="22.7109375" customWidth="1"/>
+    <col min="9" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="15" width="22.7109375" customWidth="1"/>
+    <col min="16" max="17" width="15.7109375" customWidth="1"/>
+    <col min="18" max="22" width="22.7109375" customWidth="1"/>
+    <col min="23" max="24" width="15.7109375" customWidth="1"/>
+    <col min="25" max="27" width="22.7109375" customWidth="1"/>
+    <col min="28" max="29" width="15.7109375" customWidth="1"/>
+    <col min="30" max="32" width="22.7109375" customWidth="1"/>
+    <col min="33" max="34" width="15.7109375" customWidth="1"/>
+    <col min="35" max="37" width="22.7109375" customWidth="1"/>
+    <col min="38" max="39" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:39">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -919,40 +889,16 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
+    </row>
+    <row r="2" spans="1:39">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="C2" t="s">
         <v>43</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
       <c r="D2">
         <v>516</v>
@@ -970,132 +916,108 @@
         <v>0.03269284363071832</v>
       </c>
       <c r="I2">
-        <v>-0.009547469685576918</v>
+        <v>0.1585783521869673</v>
       </c>
       <c r="J2">
-        <v>0.03690350066479627</v>
+        <v>0.1585783521869673</v>
       </c>
       <c r="K2">
-        <v>0.1585783521869673</v>
+        <v>-0.005671672015503809</v>
       </c>
       <c r="L2">
-        <v>0.1585783521869673</v>
+        <v>-0.01696010224074354</v>
       </c>
       <c r="M2">
-        <v>-0.005671672015503809</v>
+        <v>0.006063415874129986</v>
       </c>
       <c r="N2">
-        <v>-0.01696010224074354</v>
+        <v>-0.01950821088880687</v>
       </c>
       <c r="O2">
-        <v>0.006063415874129986</v>
+        <v>0.008164866857799255</v>
       </c>
       <c r="P2">
-        <v>-0.01950821088880687</v>
+        <v>0.349</v>
       </c>
       <c r="Q2">
-        <v>0.008164866857799255</v>
+        <v>0.349</v>
       </c>
       <c r="R2">
-        <v>0.349</v>
+        <v>-0.01371940430766994</v>
       </c>
       <c r="S2">
-        <v>0.349</v>
+        <v>-0.04096857231250371</v>
       </c>
       <c r="T2">
-        <v>-0.01371940430766994</v>
+        <v>0.01379438013133473</v>
       </c>
       <c r="U2">
-        <v>-0.04096857231250371</v>
+        <v>-0.04655890094471718</v>
       </c>
       <c r="V2">
-        <v>0.01379438013133473</v>
+        <v>0.01912009232937731</v>
       </c>
       <c r="W2">
-        <v>-0.04655890094471718</v>
+        <v>0.3366</v>
       </c>
       <c r="X2">
-        <v>0.01912009232937731</v>
+        <v>0.3366</v>
       </c>
       <c r="Y2">
-        <v>0.3366</v>
+        <v>0.02898550724637683</v>
       </c>
       <c r="Z2">
-        <v>0.3366</v>
+        <v>-0.05263157894736842</v>
       </c>
       <c r="AA2">
-        <v>0.02898550724637683</v>
+        <v>0.1134832366215345</v>
       </c>
       <c r="AB2">
-        <v>-0.05263157894736842</v>
+        <v>0.4938941871029767</v>
       </c>
       <c r="AC2">
-        <v>0.1134832366215345</v>
+        <v>0.4938941871029767</v>
       </c>
       <c r="AD2">
-        <v>-0.07142857142857142</v>
+        <v>-0.01322751322751314</v>
       </c>
       <c r="AE2">
-        <v>0.130241215008934</v>
+        <v>-0.04639490333476167</v>
       </c>
       <c r="AF2">
-        <v>0.4938941871029767</v>
+        <v>0.02026352423192726</v>
       </c>
       <c r="AG2">
-        <v>0.4938941871029767</v>
+        <v>0.4462239688329609</v>
       </c>
       <c r="AH2">
-        <v>-0.01322751322751314</v>
+        <v>0.4462239688329609</v>
       </c>
       <c r="AI2">
-        <v>-0.04639490333476167</v>
+        <v>-0.001937984496124034</v>
       </c>
       <c r="AJ2">
-        <v>0.02026352423192726</v>
+        <v>-0.03475239539069325</v>
       </c>
       <c r="AK2">
-        <v>-0.05426356589147287</v>
+        <v>0.03125</v>
       </c>
       <c r="AL2">
-        <v>0.02761214074670986</v>
+        <v>0.9094173748556938</v>
       </c>
       <c r="AM2">
-        <v>0.4462239688329609</v>
-      </c>
-      <c r="AN2">
-        <v>0.4462239688329609</v>
-      </c>
-      <c r="AO2">
-        <v>-0.001937984496124034</v>
-      </c>
-      <c r="AP2">
-        <v>-0.03475239539069325</v>
-      </c>
-      <c r="AQ2">
-        <v>0.03125</v>
-      </c>
-      <c r="AR2">
-        <v>-0.04177596020833175</v>
-      </c>
-      <c r="AS2">
-        <v>0.03788432607331588</v>
-      </c>
-      <c r="AT2">
         <v>0.9094173748556938</v>
       </c>
-      <c r="AU2">
-        <v>0.9094173748556938</v>
-      </c>
-    </row>
-    <row r="3" spans="1:47">
+    </row>
+    <row r="3" spans="1:39">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>516</v>
@@ -1113,132 +1035,108 @@
         <v>0.08836234224812071</v>
       </c>
       <c r="I3">
-        <v>0.02725895814217121</v>
+        <v>1.448835277480167E-05</v>
       </c>
       <c r="J3">
-        <v>0.09445333385997573</v>
+        <v>4.346505832440501E-05</v>
       </c>
       <c r="K3">
-        <v>1.448835277480167E-05</v>
+        <v>-0.03317717009689918</v>
       </c>
       <c r="L3">
-        <v>4.346505832440501E-05</v>
+        <v>-0.0483943797631313</v>
       </c>
       <c r="M3">
-        <v>-0.03317717009689918</v>
+        <v>-0.01828621828652867</v>
       </c>
       <c r="N3">
-        <v>-0.0483943797631313</v>
+        <v>-0.05126736698243801</v>
       </c>
       <c r="O3">
-        <v>-0.01828621828652867</v>
+        <v>-0.01508697321136034</v>
       </c>
       <c r="P3">
-        <v>-0.05126736698243801</v>
+        <v>0.0004</v>
       </c>
       <c r="Q3">
-        <v>-0.01508697321136034</v>
+        <v>0.0004</v>
       </c>
       <c r="R3">
+        <v>-0.08053075738992366</v>
+      </c>
+      <c r="S3">
+        <v>-0.1192318182347926</v>
+      </c>
+      <c r="T3">
+        <v>-0.04360054027952263</v>
+      </c>
+      <c r="U3">
+        <v>-0.1256862042172851</v>
+      </c>
+      <c r="V3">
+        <v>-0.03537531056256221</v>
+      </c>
+      <c r="W3">
         <v>0.0004</v>
       </c>
-      <c r="S3">
+      <c r="X3">
         <v>0.0004</v>
       </c>
-      <c r="T3">
-        <v>-0.08053075738992366</v>
-      </c>
-      <c r="U3">
-        <v>-0.1192318182347926</v>
-      </c>
-      <c r="V3">
-        <v>-0.04360054027952263</v>
-      </c>
-      <c r="W3">
-        <v>-0.1256862042172851</v>
-      </c>
-      <c r="X3">
-        <v>-0.03537531056256221</v>
-      </c>
       <c r="Y3">
-        <v>0.0004</v>
+        <v>0.07246376811594202</v>
       </c>
       <c r="Z3">
-        <v>0.0004</v>
+        <v>-0.01563115157480314</v>
       </c>
       <c r="AA3">
-        <v>0.07246376811594202</v>
+        <v>0.1677441004546439</v>
       </c>
       <c r="AB3">
-        <v>-0.01563115157480314</v>
+        <v>0.1144834666737794</v>
       </c>
       <c r="AC3">
-        <v>0.1677441004546439</v>
+        <v>0.3434504000213381</v>
       </c>
       <c r="AD3">
-        <v>-0.03651368760064402</v>
+        <v>0.03968253968253976</v>
       </c>
       <c r="AE3">
-        <v>0.1830387554082666</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.1144834666737794</v>
+        <v>0.07859078590785908</v>
       </c>
       <c r="AG3">
-        <v>0.3434504000213381</v>
+        <v>0.04645567201881207</v>
       </c>
       <c r="AH3">
-        <v>0.03968253968253976</v>
+        <v>0.09291134403762413</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.04844961240310075</v>
       </c>
       <c r="AJ3">
-        <v>0.07859078590785908</v>
+        <v>0.01167201843526879</v>
       </c>
       <c r="AK3">
-        <v>-0.005588512241054602</v>
+        <v>0.08577835648148151</v>
       </c>
       <c r="AL3">
-        <v>0.08740359897172237</v>
+        <v>0.01094842344892238</v>
       </c>
       <c r="AM3">
-        <v>0.04645567201881207</v>
-      </c>
-      <c r="AN3">
-        <v>0.09291134403762413</v>
-      </c>
-      <c r="AO3">
-        <v>0.04844961240310075</v>
-      </c>
-      <c r="AP3">
-        <v>0.01167201843526879</v>
-      </c>
-      <c r="AQ3">
-        <v>0.08577835648148151</v>
-      </c>
-      <c r="AR3">
-        <v>0.003838771593090211</v>
-      </c>
-      <c r="AS3">
-        <v>0.09452543094275381</v>
-      </c>
-      <c r="AT3">
-        <v>0.01094842344892238</v>
-      </c>
-      <c r="AU3">
         <v>0.02189684689784475</v>
       </c>
     </row>
-    <row r="4" spans="1:47">
+    <row r="4" spans="1:39">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>516</v>
@@ -1256,132 +1154,108 @@
         <v>0.07495351316857367</v>
       </c>
       <c r="I4">
-        <v>0.0132521474128741</v>
+        <v>0.0008712249487968415</v>
       </c>
       <c r="J4">
-        <v>0.0811041136100535</v>
+        <v>0.001742449897593683</v>
       </c>
       <c r="K4">
-        <v>0.0008712249487968415</v>
+        <v>-0.02750549808139537</v>
       </c>
       <c r="L4">
-        <v>0.001742449897593683</v>
+        <v>-0.04313435688609747</v>
       </c>
       <c r="M4">
-        <v>-0.02750549808139537</v>
+        <v>-0.01196780749470757</v>
       </c>
       <c r="N4">
-        <v>-0.04313435688609747</v>
+        <v>-0.04617217904084742</v>
       </c>
       <c r="O4">
-        <v>-0.01196780749470757</v>
+        <v>-0.008838817121943308</v>
       </c>
       <c r="P4">
-        <v>-0.04617217904084742</v>
+        <v>0.0014</v>
       </c>
       <c r="Q4">
-        <v>-0.008838817121943308</v>
+        <v>0.0018</v>
       </c>
       <c r="R4">
-        <v>0.0014</v>
+        <v>-0.06681135308225372</v>
       </c>
       <c r="S4">
-        <v>0.0018</v>
+        <v>-0.1061917788999018</v>
       </c>
       <c r="T4">
-        <v>-0.06681135308225372</v>
+        <v>-0.02801716367843521</v>
       </c>
       <c r="U4">
-        <v>-0.1061917788999018</v>
+        <v>-0.1131438348997234</v>
       </c>
       <c r="V4">
-        <v>-0.02801716367843521</v>
+        <v>-0.0204788712647841</v>
       </c>
       <c r="W4">
-        <v>-0.1131438348997234</v>
+        <v>0.0016</v>
       </c>
       <c r="X4">
-        <v>-0.0204788712647841</v>
+        <v>0.0022</v>
       </c>
       <c r="Y4">
-        <v>0.0016</v>
+        <v>0.04347826086956519</v>
       </c>
       <c r="Z4">
-        <v>0.0022</v>
+        <v>-0.03821656050955414</v>
       </c>
       <c r="AA4">
-        <v>0.04347826086956519</v>
+        <v>0.1268715944089079</v>
       </c>
       <c r="AB4">
-        <v>-0.03821656050955414</v>
+        <v>0.3060346718543977</v>
       </c>
       <c r="AC4">
-        <v>0.1268715944089079</v>
+        <v>0.4938941871029767</v>
       </c>
       <c r="AD4">
-        <v>-0.05569153069153064</v>
+        <v>0.05291005291005291</v>
       </c>
       <c r="AE4">
-        <v>0.1481537875904076</v>
+        <v>0.01312335958005249</v>
       </c>
       <c r="AF4">
-        <v>0.3060346718543977</v>
+        <v>0.09230972194032881</v>
       </c>
       <c r="AG4">
-        <v>0.4938941871029767</v>
+        <v>0.01191397884158072</v>
       </c>
       <c r="AH4">
-        <v>0.05291005291005291</v>
+        <v>0.03574193652474216</v>
       </c>
       <c r="AI4">
-        <v>0.01312335958005249</v>
+        <v>0.05038759689922478</v>
       </c>
       <c r="AJ4">
-        <v>0.09230972194032881</v>
+        <v>0.013670542458577</v>
       </c>
       <c r="AK4">
-        <v>0.002741720565337171</v>
+        <v>0.08663281190468416</v>
       </c>
       <c r="AL4">
-        <v>0.1029690177624242</v>
+        <v>0.007770714070688979</v>
       </c>
       <c r="AM4">
-        <v>0.01191397884158072</v>
-      </c>
-      <c r="AN4">
-        <v>0.03574193652474216</v>
-      </c>
-      <c r="AO4">
-        <v>0.05038759689922478</v>
-      </c>
-      <c r="AP4">
-        <v>0.013670542458577</v>
-      </c>
-      <c r="AQ4">
-        <v>0.08663281190468416</v>
-      </c>
-      <c r="AR4">
-        <v>0.005802707930367505</v>
-      </c>
-      <c r="AS4">
-        <v>0.09554657303978027</v>
-      </c>
-      <c r="AT4">
-        <v>0.007770714070688979</v>
-      </c>
-      <c r="AU4">
         <v>0.01642263517338357</v>
       </c>
     </row>
-    <row r="5" spans="1:47">
+    <row r="5" spans="1:39">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D5">
         <v>263</v>
@@ -1399,132 +1273,108 @@
         <v>0.022026282275109</v>
       </c>
       <c r="I5">
-        <v>-0.02028082889276633</v>
+        <v>0.7589783551323271</v>
       </c>
       <c r="J5">
-        <v>0.02624359794454106</v>
+        <v>0.7589783551323271</v>
       </c>
       <c r="K5">
-        <v>0.7589783551323271</v>
+        <v>0.003177452699619873</v>
       </c>
       <c r="L5">
-        <v>0.7589783551323271</v>
+        <v>-0.01107254006932483</v>
       </c>
       <c r="M5">
-        <v>0.003177452699619873</v>
+        <v>0.01767353194661654</v>
       </c>
       <c r="N5">
-        <v>-0.01107254006932483</v>
+        <v>-0.0142294328360232</v>
       </c>
       <c r="O5">
-        <v>0.01767353194661654</v>
+        <v>0.02058433823526295</v>
       </c>
       <c r="P5">
-        <v>-0.0142294328360232</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.02058433823526295</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="R5">
-        <v>0.6637999999999999</v>
+        <v>0.01086881864497791</v>
       </c>
       <c r="S5">
-        <v>0.6637999999999999</v>
+        <v>-0.02212520523906435</v>
       </c>
       <c r="T5">
-        <v>0.01086881864497791</v>
+        <v>0.04443815211367416</v>
       </c>
       <c r="U5">
-        <v>-0.02212520523906435</v>
+        <v>-0.02924065294566617</v>
       </c>
       <c r="V5">
-        <v>0.04443815211367416</v>
+        <v>0.05097829023562198</v>
       </c>
       <c r="W5">
-        <v>-0.02924065294566617</v>
+        <v>0.516</v>
       </c>
       <c r="X5">
-        <v>0.05097829023562198</v>
+        <v>0.516</v>
       </c>
       <c r="Y5">
-        <v>0.516</v>
+        <v>0.01388888888888884</v>
       </c>
       <c r="Z5">
-        <v>0.516</v>
+        <v>-0.08571428571428572</v>
       </c>
       <c r="AA5">
-        <v>0.01388888888888884</v>
+        <v>0.1143091334894614</v>
       </c>
       <c r="AB5">
-        <v>-0.08571428571428572</v>
+        <v>1</v>
       </c>
       <c r="AC5">
-        <v>0.1143091334894614</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>-0.1084520884520883</v>
+        <v>-0.01047120418848169</v>
       </c>
       <c r="AE5">
-        <v>0.1354452054794529</v>
+        <v>-0.05913978494623656</v>
       </c>
       <c r="AF5">
+        <v>0.03685185185185189</v>
+      </c>
+      <c r="AG5">
+        <v>0.8311704095417624</v>
+      </c>
+      <c r="AH5">
+        <v>0.8311704095417624</v>
+      </c>
+      <c r="AI5">
+        <v>-0.003802281368821325</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.04562737642585551</v>
+      </c>
+      <c r="AK5">
+        <v>0.04182509505703422</v>
+      </c>
+      <c r="AL5">
         <v>1</v>
       </c>
-      <c r="AG5">
+      <c r="AM5">
         <v>1</v>
       </c>
-      <c r="AH5">
-        <v>-0.01047120418848169</v>
-      </c>
-      <c r="AI5">
-        <v>-0.05913978494623656</v>
-      </c>
-      <c r="AJ5">
-        <v>0.03685185185185189</v>
-      </c>
-      <c r="AK5">
-        <v>-0.06964953136679887</v>
-      </c>
-      <c r="AL5">
-        <v>0.04973337731233337</v>
-      </c>
-      <c r="AM5">
-        <v>0.8311704095417624</v>
-      </c>
-      <c r="AN5">
-        <v>0.8311704095417624</v>
-      </c>
-      <c r="AO5">
-        <v>-0.003802281368821325</v>
-      </c>
-      <c r="AP5">
-        <v>-0.04562737642585551</v>
-      </c>
-      <c r="AQ5">
-        <v>0.04182509505703422</v>
-      </c>
-      <c r="AR5">
-        <v>-0.05703422053231939</v>
-      </c>
-      <c r="AS5">
-        <v>0.04942965779467681</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:47">
+    </row>
+    <row r="6" spans="1:39">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D6">
         <v>263</v>
@@ -1542,132 +1392,108 @@
         <v>0.08421841033082253</v>
       </c>
       <c r="I6">
-        <v>0.00859192659616724</v>
+        <v>0.003869222643548615</v>
       </c>
       <c r="J6">
-        <v>0.09175711354344908</v>
+        <v>0.01160766793064584</v>
       </c>
       <c r="K6">
-        <v>0.003869222643548615</v>
+        <v>-0.03326987737642581</v>
       </c>
       <c r="L6">
-        <v>0.01160766793064584</v>
+        <v>-0.05333303837337318</v>
       </c>
       <c r="M6">
-        <v>-0.03326987737642581</v>
+        <v>-0.01403268008184253</v>
       </c>
       <c r="N6">
-        <v>-0.05333303837337318</v>
+        <v>-0.05724448040629365</v>
       </c>
       <c r="O6">
-        <v>-0.01403268008184253</v>
+        <v>-0.009295274346557969</v>
       </c>
       <c r="P6">
-        <v>-0.05724448040629365</v>
+        <v>0.0032</v>
       </c>
       <c r="Q6">
-        <v>-0.009295274346557969</v>
+        <v>0.006</v>
       </c>
       <c r="R6">
-        <v>0.0032</v>
+        <v>-0.07457165389245912</v>
       </c>
       <c r="S6">
-        <v>0.006</v>
+        <v>-0.1233238778955756</v>
       </c>
       <c r="T6">
-        <v>-0.07457165389245912</v>
+        <v>-0.02701278723372434</v>
       </c>
       <c r="U6">
-        <v>-0.1233238778955756</v>
+        <v>-0.1321164458071846</v>
       </c>
       <c r="V6">
-        <v>-0.02701278723372434</v>
+        <v>-0.01702686197773369</v>
       </c>
       <c r="W6">
-        <v>-0.1321164458071846</v>
+        <v>0.0056</v>
       </c>
       <c r="X6">
-        <v>-0.01702686197773369</v>
+        <v>0.0108</v>
       </c>
       <c r="Y6">
-        <v>0.0056</v>
+        <v>0.04166666666666663</v>
       </c>
       <c r="Z6">
-        <v>0.0108</v>
+        <v>-0.06451612903225806</v>
       </c>
       <c r="AA6">
-        <v>0.04166666666666663</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="AB6">
-        <v>-0.06451612903225806</v>
+        <v>0.6055766163353462</v>
       </c>
       <c r="AC6">
-        <v>0.1470588235294118</v>
+        <v>1</v>
       </c>
       <c r="AD6">
-        <v>-0.08893822029095019</v>
+        <v>0.06806282722513091</v>
       </c>
       <c r="AE6">
-        <v>0.171875</v>
+        <v>0.0154639175257732</v>
       </c>
       <c r="AF6">
-        <v>0.6055766163353462</v>
+        <v>0.1237113402061856</v>
       </c>
       <c r="AG6">
-        <v>1</v>
+        <v>0.02585758046344289</v>
       </c>
       <c r="AH6">
-        <v>0.06806282722513091</v>
+        <v>0.05171516092688578</v>
       </c>
       <c r="AI6">
-        <v>0.0154639175257732</v>
+        <v>0.06083650190114065</v>
       </c>
       <c r="AJ6">
-        <v>0.1237113402061856</v>
+        <v>0.01140684410646388</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>0.1102661596958175</v>
       </c>
       <c r="AL6">
-        <v>0.1371632174931668</v>
+        <v>0.02373851525005458</v>
       </c>
       <c r="AM6">
-        <v>0.02585758046344289</v>
-      </c>
-      <c r="AN6">
-        <v>0.05171516092688578</v>
-      </c>
-      <c r="AO6">
-        <v>0.06083650190114065</v>
-      </c>
-      <c r="AP6">
-        <v>0.01140684410646388</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1102661596958175</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0.1216730038022814</v>
-      </c>
-      <c r="AT6">
-        <v>0.02373851525005458</v>
-      </c>
-      <c r="AU6">
         <v>0.04747703050010915</v>
       </c>
     </row>
-    <row r="7" spans="1:47">
+    <row r="7" spans="1:39">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>263</v>
@@ -1685,132 +1511,108 @@
         <v>0.08301175254021582</v>
       </c>
       <c r="I7">
-        <v>0.003442818587617621</v>
+        <v>0.009812492570670151</v>
       </c>
       <c r="J7">
-        <v>0.09094345250022397</v>
+        <v>0.0196249851413403</v>
       </c>
       <c r="K7">
-        <v>0.009812492570670151</v>
+        <v>-0.03644733007604568</v>
       </c>
       <c r="L7">
-        <v>0.0196249851413403</v>
+        <v>-0.05932266260572364</v>
       </c>
       <c r="M7">
-        <v>-0.03644733007604568</v>
+        <v>-0.01460453971831455</v>
       </c>
       <c r="N7">
-        <v>-0.05932266260572364</v>
+        <v>-0.063099354823316</v>
       </c>
       <c r="O7">
-        <v>-0.01460453971831455</v>
+        <v>-0.009795305328775369</v>
       </c>
       <c r="P7">
-        <v>-0.063099354823316</v>
+        <v>0.0016</v>
       </c>
       <c r="Q7">
-        <v>-0.009795305328775369</v>
+        <v>0.006</v>
       </c>
       <c r="R7">
-        <v>0.0016</v>
+        <v>-0.08544047253743703</v>
       </c>
       <c r="S7">
-        <v>0.006</v>
+        <v>-0.1406807097413394</v>
       </c>
       <c r="T7">
-        <v>-0.08544047253743703</v>
+        <v>-0.03111577025431145</v>
       </c>
       <c r="U7">
-        <v>-0.1406807097413394</v>
+        <v>-0.1494866851663962</v>
       </c>
       <c r="V7">
-        <v>-0.03111577025431145</v>
+        <v>-0.02139425990847783</v>
       </c>
       <c r="W7">
-        <v>-0.1494866851663962</v>
+        <v>0.002</v>
       </c>
       <c r="X7">
-        <v>-0.02139425990847783</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="Y7">
-        <v>0.002</v>
+        <v>0.02777777777777779</v>
       </c>
       <c r="Z7">
-        <v>0.008399999999999999</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="AA7">
-        <v>0.02777777777777779</v>
+        <v>0.1375</v>
       </c>
       <c r="AB7">
-        <v>-0.07692307692307693</v>
+        <v>0.8025873486341526</v>
       </c>
       <c r="AC7">
-        <v>0.1375</v>
+        <v>1</v>
       </c>
       <c r="AD7">
-        <v>-0.1036050156739811</v>
+        <v>0.07853403141361259</v>
       </c>
       <c r="AE7">
-        <v>0.1643835616438356</v>
+        <v>0.02093695462478186</v>
       </c>
       <c r="AF7">
-        <v>0.8025873486341526</v>
+        <v>0.1358722034613761</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>0.01480610912734845</v>
       </c>
       <c r="AH7">
-        <v>0.07853403141361259</v>
+        <v>0.03878637069516434</v>
       </c>
       <c r="AI7">
-        <v>0.02093695462478186</v>
+        <v>0.06463878326996197</v>
       </c>
       <c r="AJ7">
-        <v>0.1358722034613761</v>
+        <v>0.01140684410646388</v>
       </c>
       <c r="AK7">
-        <v>0.01025641025641026</v>
+        <v>0.1178707224334601</v>
       </c>
       <c r="AL7">
-        <v>0.1530566801619438</v>
+        <v>0.02227097895923274</v>
       </c>
       <c r="AM7">
-        <v>0.01480610912734845</v>
-      </c>
-      <c r="AN7">
-        <v>0.03878637069516434</v>
-      </c>
-      <c r="AO7">
-        <v>0.06463878326996197</v>
-      </c>
-      <c r="AP7">
-        <v>0.01140684410646388</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1178707224334601</v>
-      </c>
-      <c r="AR7">
-        <v>0.003802281368821293</v>
-      </c>
-      <c r="AS7">
-        <v>0.1254752851711027</v>
-      </c>
-      <c r="AT7">
-        <v>0.02227097895923274</v>
-      </c>
-      <c r="AU7">
         <v>0.04454195791846547</v>
       </c>
     </row>
-    <row r="8" spans="1:47">
+    <row r="8" spans="1:39">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>253</v>
@@ -1828,132 +1630,108 @@
         <v>0.0572333825399616</v>
       </c>
       <c r="I8">
-        <v>-0.01582008783175719</v>
+        <v>0.1467487068347569</v>
       </c>
       <c r="J8">
-        <v>0.06451559909411336</v>
+        <v>0.1467487068347569</v>
       </c>
       <c r="K8">
-        <v>0.1467487068347569</v>
+        <v>-0.01487056450592883</v>
       </c>
       <c r="L8">
-        <v>0.1467487068347569</v>
+        <v>-0.03288227345609322</v>
       </c>
       <c r="M8">
-        <v>-0.01487056450592883</v>
+        <v>0.003186446569978699</v>
       </c>
       <c r="N8">
-        <v>-0.03288227345609322</v>
+        <v>-0.03571830630142864</v>
       </c>
       <c r="O8">
-        <v>0.003186446569978699</v>
+        <v>0.005977177289570985</v>
       </c>
       <c r="P8">
-        <v>-0.03571830630142864</v>
+        <v>0.1052</v>
       </c>
       <c r="Q8">
-        <v>0.005977177289570985</v>
+        <v>0.1868</v>
       </c>
       <c r="R8">
-        <v>0.1052</v>
+        <v>-0.03927949378018425</v>
       </c>
       <c r="S8">
-        <v>0.1868</v>
+        <v>-0.08396634944318943</v>
       </c>
       <c r="T8">
-        <v>-0.03927949378018425</v>
+        <v>0.003910375492078746</v>
       </c>
       <c r="U8">
-        <v>-0.08396634944318943</v>
+        <v>-0.08982206866643555</v>
       </c>
       <c r="V8">
-        <v>0.003910375492078746</v>
+        <v>0.01126308110606705</v>
       </c>
       <c r="W8">
-        <v>-0.08982206866643555</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="X8">
-        <v>0.01126308110606705</v>
+        <v>0.1416</v>
       </c>
       <c r="Y8">
-        <v>0.07779999999999999</v>
+        <v>0.04545454545454553</v>
       </c>
       <c r="Z8">
-        <v>0.1416</v>
+        <v>-0.0847457627118644</v>
       </c>
       <c r="AA8">
-        <v>0.04545454545454553</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="AB8">
-        <v>-0.0847457627118644</v>
+        <v>0.6463551955394902</v>
       </c>
       <c r="AC8">
-        <v>0.1739130434782609</v>
+        <v>0.6463551955394902</v>
       </c>
       <c r="AD8">
-        <v>-0.1131249999999998</v>
+        <v>-0.01604278074866305</v>
       </c>
       <c r="AE8">
-        <v>0.2034996861268049</v>
+        <v>-0.05945945945945946</v>
       </c>
       <c r="AF8">
-        <v>0.6463551955394902</v>
+        <v>0.02660285584253046</v>
       </c>
       <c r="AG8">
-        <v>0.6463551955394902</v>
+        <v>0.6276258050283593</v>
       </c>
       <c r="AH8">
-        <v>-0.01604278074866305</v>
+        <v>0.8501067391385259</v>
       </c>
       <c r="AI8">
-        <v>-0.05945945945945946</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.02660285584253046</v>
+        <v>-0.04743083003952569</v>
       </c>
       <c r="AK8">
-        <v>-0.07119289340101519</v>
+        <v>0.04743083003952569</v>
       </c>
       <c r="AL8">
-        <v>0.03333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AM8">
-        <v>0.6276258050283593</v>
-      </c>
-      <c r="AN8">
-        <v>0.8501067391385259</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>-0.04743083003952569</v>
-      </c>
-      <c r="AQ8">
-        <v>0.04743083003952569</v>
-      </c>
-      <c r="AR8">
-        <v>-0.05533596837944664</v>
-      </c>
-      <c r="AS8">
-        <v>0.05533596837944664</v>
-      </c>
-      <c r="AT8">
         <v>1</v>
       </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:47">
+    </row>
+    <row r="9" spans="1:39">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D9">
         <v>253</v>
@@ -1971,132 +1749,108 @@
         <v>0.11732616761233</v>
       </c>
       <c r="I9">
-        <v>0.01283465784607815</v>
+        <v>0.003403025345125086</v>
       </c>
       <c r="J9">
-        <v>0.127742234067712</v>
+        <v>0.01020907603537526</v>
       </c>
       <c r="K9">
-        <v>0.003403025345125086</v>
+        <v>-0.03308079849802376</v>
       </c>
       <c r="L9">
-        <v>0.01020907603537526</v>
+        <v>-0.05855212414881788</v>
       </c>
       <c r="M9">
-        <v>-0.03308079849802376</v>
+        <v>-0.01034818093491874</v>
       </c>
       <c r="N9">
-        <v>-0.05855212414881788</v>
+        <v>-0.06143081418824267</v>
       </c>
       <c r="O9">
-        <v>-0.01034818093491874</v>
+        <v>-0.004730782807804843</v>
       </c>
       <c r="P9">
-        <v>-0.06143081418824267</v>
+        <v>0.007</v>
       </c>
       <c r="Q9">
-        <v>-0.004730782807804843</v>
+        <v>0.0166</v>
       </c>
       <c r="R9">
+        <v>-0.08672539857503453</v>
+      </c>
+      <c r="S9">
+        <v>-0.1531605520737868</v>
+      </c>
+      <c r="T9">
+        <v>-0.03011349316215359</v>
+      </c>
+      <c r="U9">
+        <v>-0.1592997954158392</v>
+      </c>
+      <c r="V9">
+        <v>-0.01415100173422988</v>
+      </c>
+      <c r="W9">
         <v>0.007</v>
       </c>
-      <c r="S9">
-        <v>0.0166</v>
-      </c>
-      <c r="T9">
-        <v>-0.08672539857503453</v>
-      </c>
-      <c r="U9">
-        <v>-0.1531605520737868</v>
-      </c>
-      <c r="V9">
-        <v>-0.03011349316215359</v>
-      </c>
-      <c r="W9">
-        <v>-0.1592997954158392</v>
-      </c>
       <c r="X9">
-        <v>-0.01415100173422988</v>
+        <v>0.0138</v>
       </c>
       <c r="Y9">
-        <v>0.007</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="Z9">
-        <v>0.0138</v>
+        <v>-0.03947368421052631</v>
       </c>
       <c r="AA9">
-        <v>0.1060606060606061</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="AB9">
-        <v>-0.03947368421052631</v>
+        <v>0.2109029260566068</v>
       </c>
       <c r="AC9">
-        <v>0.2424242424242424</v>
+        <v>0.6327087781698203</v>
       </c>
       <c r="AD9">
-        <v>-0.07352941176470588</v>
+        <v>0.01069518716577544</v>
       </c>
       <c r="AE9">
-        <v>0.2711864406779661</v>
+        <v>-0.04591836734693878</v>
       </c>
       <c r="AF9">
-        <v>0.2109029260566068</v>
+        <v>0.06595227976443453</v>
       </c>
       <c r="AG9">
-        <v>0.6327087781698203</v>
+        <v>0.8501067391385259</v>
       </c>
       <c r="AH9">
-        <v>0.01069518716577544</v>
+        <v>0.8501067391385259</v>
       </c>
       <c r="AI9">
-        <v>-0.04591836734693878</v>
+        <v>0.03557312252964429</v>
       </c>
       <c r="AJ9">
-        <v>0.06595227976443453</v>
+        <v>-0.01976284584980237</v>
       </c>
       <c r="AK9">
-        <v>-0.05615820998675333</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AL9">
-        <v>0.07951283350219536</v>
+        <v>0.2626182904425174</v>
       </c>
       <c r="AM9">
-        <v>0.8501067391385259</v>
-      </c>
-      <c r="AN9">
-        <v>0.8501067391385259</v>
-      </c>
-      <c r="AO9">
-        <v>0.03557312252964429</v>
-      </c>
-      <c r="AP9">
-        <v>-0.01976284584980237</v>
-      </c>
-      <c r="AQ9">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="AR9">
-        <v>-0.03162055335968379</v>
-      </c>
-      <c r="AS9">
-        <v>0.1001976284584995</v>
-      </c>
-      <c r="AT9">
-        <v>0.2626182904425174</v>
-      </c>
-      <c r="AU9">
         <v>0.5252365808850348</v>
       </c>
     </row>
-    <row r="10" spans="1:47">
+    <row r="10" spans="1:39">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>253</v>
@@ -2114,120 +1868,96 @@
         <v>0.09161121359083908</v>
       </c>
       <c r="I10">
-        <v>-0.009843146013245659</v>
+        <v>0.04866005335540764</v>
       </c>
       <c r="J10">
-        <v>0.1017245266646797</v>
+        <v>0.09732010671081527</v>
       </c>
       <c r="K10">
-        <v>0.04866005335540764</v>
+        <v>-0.01821023399209493</v>
       </c>
       <c r="L10">
-        <v>0.09732010671081527</v>
+        <v>-0.04208292671189801</v>
       </c>
       <c r="M10">
-        <v>-0.01821023399209493</v>
+        <v>0.00481220577491211</v>
       </c>
       <c r="N10">
-        <v>-0.04208292671189801</v>
+        <v>-0.0459950736638484</v>
       </c>
       <c r="O10">
-        <v>0.00481220577491211</v>
+        <v>0.009574605679658545</v>
       </c>
       <c r="P10">
-        <v>-0.0459950736638484</v>
+        <v>0.1366</v>
       </c>
       <c r="Q10">
-        <v>0.009574605679658545</v>
+        <v>0.1868</v>
       </c>
       <c r="R10">
-        <v>0.1366</v>
+        <v>-0.04744590479485028</v>
       </c>
       <c r="S10">
-        <v>0.1868</v>
+        <v>-0.1062323134937177</v>
       </c>
       <c r="T10">
-        <v>-0.04744590479485028</v>
+        <v>0.01013852501960102</v>
       </c>
       <c r="U10">
-        <v>-0.1062323134937177</v>
+        <v>-0.1179283647360767</v>
       </c>
       <c r="V10">
-        <v>0.01013852501960102</v>
+        <v>0.02303655514637615</v>
       </c>
       <c r="W10">
-        <v>-0.1179283647360767</v>
+        <v>0.1234</v>
       </c>
       <c r="X10">
-        <v>0.02303655514637615</v>
+        <v>0.1416</v>
       </c>
       <c r="Y10">
-        <v>0.1234</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="Z10">
-        <v>0.1416</v>
+        <v>-0.0625</v>
       </c>
       <c r="AA10">
-        <v>0.06060606060606055</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="AB10">
-        <v>-0.0625</v>
+        <v>0.4795001221869534</v>
       </c>
       <c r="AC10">
-        <v>0.1864406779661017</v>
+        <v>0.6463551955394902</v>
       </c>
       <c r="AD10">
-        <v>-0.09015151515151501</v>
+        <v>0.0267379679144385</v>
       </c>
       <c r="AE10">
-        <v>0.213666666666667</v>
+        <v>-0.02748011656851434</v>
       </c>
       <c r="AF10">
-        <v>0.4795001221869534</v>
+        <v>0.0855763517528224</v>
       </c>
       <c r="AG10">
-        <v>0.6463551955394902</v>
+        <v>0.4576140668763148</v>
       </c>
       <c r="AH10">
-        <v>0.0267379679144385</v>
+        <v>0.8501067391385259</v>
       </c>
       <c r="AI10">
-        <v>-0.02748011656851434</v>
+        <v>0.03557312252964429</v>
       </c>
       <c r="AJ10">
-        <v>0.0855763517528224</v>
+        <v>-0.0158102766798419</v>
       </c>
       <c r="AK10">
-        <v>-0.04218323586744636</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AL10">
-        <v>0.09913967059336842</v>
+        <v>0.2432427057426535</v>
       </c>
       <c r="AM10">
-        <v>0.4576140668763148</v>
-      </c>
-      <c r="AN10">
-        <v>0.8501067391385259</v>
-      </c>
-      <c r="AO10">
-        <v>0.03557312252964429</v>
-      </c>
-      <c r="AP10">
-        <v>-0.0158102766798419</v>
-      </c>
-      <c r="AQ10">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="AR10">
-        <v>-0.02766798418972332</v>
-      </c>
-      <c r="AS10">
-        <v>0.1001976284584995</v>
-      </c>
-      <c r="AT10">
-        <v>0.2432427057426535</v>
-      </c>
-      <c r="AU10">
         <v>0.486485411485307</v>
       </c>
     </row>
@@ -2247,130 +1977,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2388,48 +2118,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J1" t="s">
         <v>83</v>
-      </c>
-      <c r="C1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E2">
         <v>0.9497450348899624</v>
@@ -2447,21 +2177,21 @@
         <v>300</v>
       </c>
       <c r="J2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>0.9360670194003528</v>
@@ -2479,21 +2209,21 @@
         <v>300</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E4">
         <v>0.888888888888889</v>
@@ -2511,21 +2241,21 @@
         <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E5">
         <v>0.09039919269379845</v>
@@ -2543,21 +2273,21 @@
         <v>300</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>0.09607086470930232</v>
@@ -2575,21 +2305,21 @@
         <v>300</v>
       </c>
       <c r="J6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>0.1235763627906977</v>
@@ -2607,21 +2337,21 @@
         <v>300</v>
       </c>
       <c r="J7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>0.3017094343669053</v>
@@ -2639,21 +2369,21 @@
         <v>300</v>
       </c>
       <c r="J8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <v>0.3154288386745746</v>
@@ -2671,21 +2401,21 @@
         <v>300</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E10">
         <v>0.3822401917568288</v>
@@ -2703,21 +2433,21 @@
         <v>300</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>0.8333333333333334</v>
@@ -2735,21 +2465,21 @@
         <v>300</v>
       </c>
       <c r="J11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E12">
         <v>0.8043478260869565</v>
@@ -2767,21 +2497,21 @@
         <v>300</v>
       </c>
       <c r="J12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E13">
         <v>0.7608695652173914</v>
@@ -2799,21 +2529,21 @@
         <v>300</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E14">
         <v>0.8862433862433863</v>
@@ -2831,21 +2561,21 @@
         <v>300</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>0.8994708994708994</v>
@@ -2863,21 +2593,21 @@
         <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E16">
         <v>0.8465608465608465</v>
@@ -2895,21 +2625,21 @@
         <v>300</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>0.8720930232558139</v>
@@ -2927,21 +2657,21 @@
         <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>0.874031007751938</v>
@@ -2959,21 +2689,21 @@
         <v>300</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>0.8236434108527132</v>
@@ -2991,21 +2721,21 @@
         <v>300</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>0.9572425828970333</v>
@@ -3023,21 +2753,21 @@
         <v>263</v>
       </c>
       <c r="J20" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>0.954261198371146</v>
@@ -3055,21 +2785,21 @@
         <v>263</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>0.9070680628272252</v>
@@ -3087,21 +2817,21 @@
         <v>263</v>
       </c>
       <c r="J22" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E23">
         <v>0.08409677600760457</v>
@@ -3119,21 +2849,21 @@
         <v>263</v>
       </c>
       <c r="J23" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E24">
         <v>0.08091932330798481</v>
@@ -3151,21 +2881,21 @@
         <v>263</v>
       </c>
       <c r="J24" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E25">
         <v>0.1173666533840304</v>
@@ -3183,21 +2913,21 @@
         <v>263</v>
       </c>
       <c r="J25" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>0.2869453687617093</v>
@@ -3215,21 +2945,21 @@
         <v>263</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>0.2760765501167315</v>
@@ -3247,21 +2977,21 @@
         <v>263</v>
       </c>
       <c r="J27" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>0.3615170226541689</v>
@@ -3279,21 +3009,21 @@
         <v>263</v>
       </c>
       <c r="J28" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E29">
         <v>0.8194444444444444</v>
@@ -3311,21 +3041,21 @@
         <v>263</v>
       </c>
       <c r="J29" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E30">
         <v>0.8055555555555556</v>
@@ -3343,21 +3073,21 @@
         <v>263</v>
       </c>
       <c r="J30" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E31">
         <v>0.7777777777777778</v>
@@ -3375,21 +3105,21 @@
         <v>263</v>
       </c>
       <c r="J31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>0.9057591623036649</v>
@@ -3407,21 +3137,21 @@
         <v>263</v>
       </c>
       <c r="J32" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E33">
         <v>0.9162303664921466</v>
@@ -3439,21 +3169,21 @@
         <v>263</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>0.837696335078534</v>
@@ -3471,21 +3201,21 @@
         <v>263</v>
       </c>
       <c r="J34" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>0.8821292775665399</v>
@@ -3503,21 +3233,21 @@
         <v>263</v>
       </c>
       <c r="J35" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E36">
         <v>0.8859315589353612</v>
@@ -3535,21 +3265,21 @@
         <v>263</v>
       </c>
       <c r="J36" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>0.8212927756653993</v>
@@ -3567,21 +3297,21 @@
         <v>263</v>
       </c>
       <c r="J37" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E38">
         <v>0.9407308377896613</v>
@@ -3599,21 +3329,21 @@
         <v>253</v>
       </c>
       <c r="J38" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E39">
         <v>0.9163830821584832</v>
@@ -3631,21 +3361,21 @@
         <v>253</v>
       </c>
       <c r="J39" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E40">
         <v>0.8704423918327662</v>
@@ -3663,21 +3393,21 @@
         <v>253</v>
       </c>
       <c r="J40" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E41">
         <v>0.09695071675889329</v>
@@ -3695,21 +3425,21 @@
         <v>253</v>
       </c>
       <c r="J41" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E42">
         <v>0.1118212812648221</v>
@@ -3727,21 +3457,21 @@
         <v>253</v>
       </c>
       <c r="J42" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E43">
         <v>0.130031515256917</v>
@@ -3759,21 +3489,21 @@
         <v>253</v>
       </c>
       <c r="J43" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E44">
         <v>0.317057059877445</v>
@@ -3791,21 +3521,21 @@
         <v>253</v>
       </c>
       <c r="J44" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E45">
         <v>0.3563365536576291</v>
@@ -3823,21 +3553,21 @@
         <v>253</v>
       </c>
       <c r="J45" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E46">
         <v>0.4037824584524792</v>
@@ -3855,21 +3585,21 @@
         <v>253</v>
       </c>
       <c r="J46" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E47">
         <v>0.8484848484848485</v>
@@ -3887,21 +3617,21 @@
         <v>253</v>
       </c>
       <c r="J47" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E48">
         <v>0.803030303030303</v>
@@ -3919,21 +3649,21 @@
         <v>253</v>
       </c>
       <c r="J48" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E49">
         <v>0.7424242424242424</v>
@@ -3951,21 +3681,21 @@
         <v>253</v>
       </c>
       <c r="J49" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E50">
         <v>0.8663101604278075</v>
@@ -3983,21 +3713,21 @@
         <v>253</v>
       </c>
       <c r="J50" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E51">
         <v>0.8823529411764706</v>
@@ -4015,21 +3745,21 @@
         <v>253</v>
       </c>
       <c r="J51" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E52">
         <v>0.8556149732620321</v>
@@ -4047,21 +3777,21 @@
         <v>253</v>
       </c>
       <c r="J52" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E53">
         <v>0.8616600790513834</v>
@@ -4079,21 +3809,21 @@
         <v>253</v>
       </c>
       <c r="J53" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E54">
         <v>0.8616600790513834</v>
@@ -4111,21 +3841,21 @@
         <v>253</v>
       </c>
       <c r="J54" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E55">
         <v>0.8260869565217391</v>
@@ -4143,7 +3873,7 @@
         <v>253</v>
       </c>
       <c r="J55" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4166,78 +3896,78 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" t="s">
+      <c r="O1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
         <v>103</v>
       </c>
-      <c r="G1" t="s">
+      <c r="Q1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" t="s">
+      <c r="R1" t="s">
         <v>105</v>
       </c>
-      <c r="I1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="S1" t="s">
         <v>106</v>
-      </c>
-      <c r="L1" t="s">
-        <v>107</v>
-      </c>
-      <c r="M1" t="s">
-        <v>108</v>
-      </c>
-      <c r="N1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O1" t="s">
-        <v>110</v>
-      </c>
-      <c r="P1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>112</v>
-      </c>
-      <c r="R1" t="s">
-        <v>113</v>
-      </c>
-      <c r="S1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>0.9497450348899624</v>
@@ -4258,39 +3988,33 @@
         <v>0.1585783521869673</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O2">
         <v>0.1585783521869673</v>
       </c>
       <c r="P2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q2">
-        <v>-0.009547469685576918</v>
-      </c>
-      <c r="R2">
-        <v>0.03690350066479627</v>
+        <v>109</v>
       </c>
       <c r="S2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>0.09039919269379848</v>
@@ -4317,13 +4041,13 @@
         <v>1.637225445824592</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O3">
         <v>0.349</v>
       </c>
       <c r="P3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q3">
         <v>-0.01950821088880687</v>
@@ -4332,24 +4056,24 @@
         <v>0.008164866857799255</v>
       </c>
       <c r="S3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>0.3017094343669052</v>
@@ -4376,13 +4100,13 @@
         <v>1.658750048532445</v>
       </c>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O4">
         <v>0.3366</v>
       </c>
       <c r="P4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q4">
         <v>-0.04655890094471718</v>
@@ -4391,24 +4115,24 @@
         <v>0.01912009232937731</v>
       </c>
       <c r="S4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>0.8333333333333334</v>
@@ -4435,39 +4159,33 @@
         <v>1.1714295204668</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O5">
         <v>0.4938941871029767</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q5">
-        <v>-0.07142857142857142</v>
-      </c>
-      <c r="R5">
-        <v>0.130241215008934</v>
+        <v>109</v>
       </c>
       <c r="S5" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>0.8862433862433863</v>
@@ -4494,39 +4212,33 @@
         <v>1.400632776710893</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O6">
         <v>0.4462239688329609</v>
       </c>
       <c r="P6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q6">
-        <v>-0.05426356589147287</v>
-      </c>
-      <c r="R6">
-        <v>0.02761214074670986</v>
+        <v>109</v>
       </c>
       <c r="S6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>0.8720930232558139</v>
@@ -4553,39 +4265,33 @@
         <v>1.586004072823823</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O7">
         <v>0.9094173748556938</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7">
-        <v>-0.04177596020833175</v>
-      </c>
-      <c r="R7">
-        <v>0.03788432607331588</v>
+        <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F8">
         <v>0.9497450348899624</v>
@@ -4606,39 +4312,33 @@
         <v>1.448835277480167E-05</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O8">
         <v>4.346505832440501E-05</v>
       </c>
       <c r="P8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q8">
-        <v>0.02725895814217121</v>
-      </c>
-      <c r="R8">
-        <v>0.09445333385997573</v>
+        <v>109</v>
       </c>
       <c r="S8" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>0.09039919269379848</v>
@@ -4665,13 +4365,13 @@
         <v>1.72</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O9">
         <v>0.0004</v>
       </c>
       <c r="P9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>-0.05126736698243801</v>
@@ -4680,24 +4380,24 @@
         <v>-0.01508697321136034</v>
       </c>
       <c r="S9" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>0.3017094343669052</v>
@@ -4724,13 +4424,13 @@
         <v>1.72</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O10">
         <v>0.0004</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q10">
         <v>-0.1256862042172851</v>
@@ -4739,24 +4439,24 @@
         <v>-0.03537531056256221</v>
       </c>
       <c r="S10" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>0.8333333333333334</v>
@@ -4783,39 +4483,33 @@
         <v>1.188514823808941</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O11">
         <v>0.3434504000213381</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q11">
-        <v>-0.03651368760064402</v>
-      </c>
-      <c r="R11">
-        <v>0.1830387554082666</v>
+        <v>109</v>
       </c>
       <c r="S11" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>0.8862433862433863</v>
@@ -4842,39 +4536,33 @@
         <v>1.542857142857143</v>
       </c>
       <c r="N12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O12">
         <v>0.09291134403762413</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12">
-        <v>-0.005588512241054602</v>
-      </c>
-      <c r="R12">
-        <v>0.08740359897172237</v>
+        <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F13">
         <v>0.8720930232558139</v>
@@ -4901,39 +4589,33 @@
         <v>1.702106891515892</v>
       </c>
       <c r="N13" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O13">
         <v>0.02189684689784475</v>
       </c>
       <c r="P13" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13">
-        <v>0.003838771593090211</v>
-      </c>
-      <c r="R13">
-        <v>0.09452543094275381</v>
+        <v>109</v>
       </c>
       <c r="S13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>0.9360670194003528</v>
@@ -4954,39 +4636,33 @@
         <v>0.0008712249487968415</v>
       </c>
       <c r="N14" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="O14">
         <v>0.001742449897593683</v>
       </c>
       <c r="P14" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q14">
-        <v>0.0132521474128741</v>
-      </c>
-      <c r="R14">
-        <v>0.0811041136100535</v>
+        <v>109</v>
       </c>
       <c r="S14" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F15">
         <v>0.09607086470930229</v>
@@ -5013,13 +4689,13 @@
         <v>1.72</v>
       </c>
       <c r="N15" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O15">
         <v>0.0018</v>
       </c>
       <c r="P15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q15">
         <v>-0.04617217904084742</v>
@@ -5028,24 +4704,24 @@
         <v>-0.008838817121943308</v>
       </c>
       <c r="S15" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F16">
         <v>0.3154288386745751</v>
@@ -5072,13 +4748,13 @@
         <v>1.72</v>
       </c>
       <c r="N16" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O16">
         <v>0.0022</v>
       </c>
       <c r="P16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>-0.1131438348997234</v>
@@ -5087,24 +4763,24 @@
         <v>-0.0204788712647841</v>
       </c>
       <c r="S16" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F17">
         <v>0.8043478260869565</v>
@@ -5131,39 +4807,33 @@
         <v>1.243243243243243</v>
       </c>
       <c r="N17" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O17">
         <v>0.4938941871029767</v>
       </c>
       <c r="P17" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q17">
-        <v>-0.05569153069153064</v>
-      </c>
-      <c r="R17">
-        <v>0.1481537875904076</v>
+        <v>109</v>
       </c>
       <c r="S17" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F18">
         <v>0.8994708994708994</v>
@@ -5190,39 +4860,33 @@
         <v>1.511717281558992</v>
       </c>
       <c r="N18" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O18">
         <v>0.03574193652474216</v>
       </c>
       <c r="P18" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q18">
-        <v>0.002741720565337171</v>
-      </c>
-      <c r="R18">
-        <v>0.1029690177624242</v>
+        <v>109</v>
       </c>
       <c r="S18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F19">
         <v>0.874031007751938</v>
@@ -5249,39 +4913,33 @@
         <v>1.72</v>
       </c>
       <c r="N19" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O19">
         <v>0.01642263517338357</v>
       </c>
       <c r="P19" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q19">
-        <v>0.005802707930367505</v>
-      </c>
-      <c r="R19">
-        <v>0.09554657303978027</v>
+        <v>109</v>
       </c>
       <c r="S19" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F20">
         <v>0.9572425828970333</v>
@@ -5302,39 +4960,33 @@
         <v>0.7589783551323271</v>
       </c>
       <c r="N20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O20">
         <v>0.7589783551323271</v>
       </c>
       <c r="P20" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q20">
-        <v>-0.02028082889276633</v>
-      </c>
-      <c r="R20">
-        <v>0.02624359794454106</v>
+        <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F21">
         <v>0.08409677600760461</v>
@@ -5355,13 +5007,13 @@
         <v>0.6637999999999999</v>
       </c>
       <c r="N21" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O21">
         <v>0.6637999999999999</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q21">
         <v>-0.0142294328360232</v>
@@ -5370,24 +5022,24 @@
         <v>0.02058433823526295</v>
       </c>
       <c r="S21" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F22">
         <v>0.2869453687617096</v>
@@ -5408,13 +5060,13 @@
         <v>0.516</v>
       </c>
       <c r="N22" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O22">
         <v>0.516</v>
       </c>
       <c r="P22" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q22">
         <v>-0.02924065294566617</v>
@@ -5423,24 +5075,24 @@
         <v>0.05097829023562198</v>
       </c>
       <c r="S22" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <v>0.8194444444444444</v>
@@ -5461,39 +5113,33 @@
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q23">
-        <v>-0.1084520884520883</v>
-      </c>
-      <c r="R23">
-        <v>0.1354452054794529</v>
+        <v>109</v>
       </c>
       <c r="S23" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F24">
         <v>0.9057591623036649</v>
@@ -5514,39 +5160,33 @@
         <v>0.8311704095417624</v>
       </c>
       <c r="N24" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O24">
         <v>0.8311704095417624</v>
       </c>
       <c r="P24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q24">
-        <v>-0.06964953136679887</v>
-      </c>
-      <c r="R24">
-        <v>0.04973337731233337</v>
+        <v>109</v>
       </c>
       <c r="S24" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F25">
         <v>0.8821292775665399</v>
@@ -5567,39 +5207,33 @@
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q25">
-        <v>-0.05703422053231939</v>
-      </c>
-      <c r="R25">
-        <v>0.04942965779467681</v>
+        <v>109</v>
       </c>
       <c r="S25" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F26">
         <v>0.9572425828970333</v>
@@ -5620,39 +5254,33 @@
         <v>0.003869222643548615</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O26">
         <v>0.01160766793064584</v>
       </c>
       <c r="P26" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q26">
-        <v>0.00859192659616724</v>
-      </c>
-      <c r="R26">
-        <v>0.09175711354344908</v>
+        <v>109</v>
       </c>
       <c r="S26" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F27">
         <v>0.08409677600760461</v>
@@ -5673,13 +5301,13 @@
         <v>0.0032</v>
       </c>
       <c r="N27" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O27">
         <v>0.006</v>
       </c>
       <c r="P27" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q27">
         <v>-0.05724448040629365</v>
@@ -5688,24 +5316,24 @@
         <v>-0.009295274346557969</v>
       </c>
       <c r="S27" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F28">
         <v>0.2869453687617096</v>
@@ -5726,13 +5354,13 @@
         <v>0.0056</v>
       </c>
       <c r="N28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O28">
         <v>0.0108</v>
       </c>
       <c r="P28" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q28">
         <v>-0.1321164458071846</v>
@@ -5741,24 +5369,24 @@
         <v>-0.01702686197773369</v>
       </c>
       <c r="S28" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F29">
         <v>0.8194444444444444</v>
@@ -5779,39 +5407,33 @@
         <v>0.6055766163353462</v>
       </c>
       <c r="N29" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O29">
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q29">
-        <v>-0.08893822029095019</v>
-      </c>
-      <c r="R29">
-        <v>0.171875</v>
+        <v>109</v>
       </c>
       <c r="S29" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F30">
         <v>0.9057591623036649</v>
@@ -5832,39 +5454,33 @@
         <v>0.02585758046344289</v>
       </c>
       <c r="N30" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O30">
         <v>0.05171516092688578</v>
       </c>
       <c r="P30" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0.1371632174931668</v>
+        <v>109</v>
       </c>
       <c r="S30" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F31">
         <v>0.8821292775665399</v>
@@ -5885,39 +5501,33 @@
         <v>0.02373851525005458</v>
       </c>
       <c r="N31" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O31">
         <v>0.04747703050010915</v>
       </c>
       <c r="P31" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0.1216730038022814</v>
+        <v>109</v>
       </c>
       <c r="S31" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F32">
         <v>0.954261198371146</v>
@@ -5938,39 +5548,33 @@
         <v>0.009812492570670151</v>
       </c>
       <c r="N32" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O32">
         <v>0.0196249851413403</v>
       </c>
       <c r="P32" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q32">
-        <v>0.003442818587617621</v>
-      </c>
-      <c r="R32">
-        <v>0.09094345250022397</v>
+        <v>109</v>
       </c>
       <c r="S32" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F33">
         <v>0.08091932330798474</v>
@@ -5991,13 +5595,13 @@
         <v>0.0016</v>
       </c>
       <c r="N33" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O33">
         <v>0.006</v>
       </c>
       <c r="P33" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q33">
         <v>-0.063099354823316</v>
@@ -6006,24 +5610,24 @@
         <v>-0.009795305328775369</v>
       </c>
       <c r="S33" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F34">
         <v>0.2760765501167317</v>
@@ -6044,13 +5648,13 @@
         <v>0.002</v>
       </c>
       <c r="N34" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O34">
         <v>0.008399999999999999</v>
       </c>
       <c r="P34" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q34">
         <v>-0.1494866851663962</v>
@@ -6059,24 +5663,24 @@
         <v>-0.02139425990847783</v>
       </c>
       <c r="S34" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F35">
         <v>0.8055555555555556</v>
@@ -6097,39 +5701,33 @@
         <v>0.8025873486341526</v>
       </c>
       <c r="N35" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q35">
-        <v>-0.1036050156739811</v>
-      </c>
-      <c r="R35">
-        <v>0.1643835616438356</v>
+        <v>109</v>
       </c>
       <c r="S35" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F36">
         <v>0.9162303664921466</v>
@@ -6150,39 +5748,33 @@
         <v>0.01480610912734845</v>
       </c>
       <c r="N36" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O36">
         <v>0.03878637069516434</v>
       </c>
       <c r="P36" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q36">
-        <v>0.01025641025641026</v>
-      </c>
-      <c r="R36">
-        <v>0.1530566801619438</v>
+        <v>109</v>
       </c>
       <c r="S36" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F37">
         <v>0.8859315589353612</v>
@@ -6203,39 +5795,33 @@
         <v>0.02227097895923274</v>
       </c>
       <c r="N37" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O37">
         <v>0.04454195791846547</v>
       </c>
       <c r="P37" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q37">
-        <v>0.003802281368821293</v>
-      </c>
-      <c r="R37">
-        <v>0.1254752851711027</v>
+        <v>109</v>
       </c>
       <c r="S37" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F38">
         <v>0.9407308377896613</v>
@@ -6256,39 +5842,33 @@
         <v>0.1467487068347569</v>
       </c>
       <c r="N38" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O38">
         <v>0.1467487068347569</v>
       </c>
       <c r="P38" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q38">
-        <v>-0.01582008783175719</v>
-      </c>
-      <c r="R38">
-        <v>0.06451559909411336</v>
+        <v>109</v>
       </c>
       <c r="S38" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F39">
         <v>0.09695071675889327</v>
@@ -6309,13 +5889,13 @@
         <v>0.1052</v>
       </c>
       <c r="N39" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O39">
         <v>0.1868</v>
       </c>
       <c r="P39" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q39">
         <v>-0.03571830630142864</v>
@@ -6324,24 +5904,24 @@
         <v>0.005977177289570985</v>
       </c>
       <c r="S39" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F40">
         <v>0.3170570598774448</v>
@@ -6362,13 +5942,13 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="N40" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O40">
         <v>0.1416</v>
       </c>
       <c r="P40" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q40">
         <v>-0.08982206866643555</v>
@@ -6377,24 +5957,24 @@
         <v>0.01126308110606705</v>
       </c>
       <c r="S40" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F41">
         <v>0.8484848484848485</v>
@@ -6415,39 +5995,33 @@
         <v>0.6463551955394902</v>
       </c>
       <c r="N41" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O41">
         <v>0.6463551955394902</v>
       </c>
       <c r="P41" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q41">
-        <v>-0.1131249999999998</v>
-      </c>
-      <c r="R41">
-        <v>0.2034996861268049</v>
+        <v>109</v>
       </c>
       <c r="S41" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F42">
         <v>0.8663101604278075</v>
@@ -6468,39 +6042,33 @@
         <v>0.6276258050283593</v>
       </c>
       <c r="N42" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O42">
         <v>0.8501067391385259</v>
       </c>
       <c r="P42" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q42">
-        <v>-0.07119289340101519</v>
-      </c>
-      <c r="R42">
-        <v>0.03333333333333333</v>
+        <v>109</v>
       </c>
       <c r="S42" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F43">
         <v>0.8616600790513834</v>
@@ -6521,39 +6089,33 @@
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q43">
-        <v>-0.05533596837944664</v>
-      </c>
-      <c r="R43">
-        <v>0.05533596837944664</v>
+        <v>109</v>
       </c>
       <c r="S43" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F44">
         <v>0.9407308377896613</v>
@@ -6574,39 +6136,33 @@
         <v>0.003403025345125086</v>
       </c>
       <c r="N44" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O44">
         <v>0.01020907603537526</v>
       </c>
       <c r="P44" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q44">
-        <v>0.01283465784607815</v>
-      </c>
-      <c r="R44">
-        <v>0.127742234067712</v>
+        <v>109</v>
       </c>
       <c r="S44" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F45">
         <v>0.09695071675889327</v>
@@ -6627,13 +6183,13 @@
         <v>0.007</v>
       </c>
       <c r="N45" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O45">
         <v>0.0166</v>
       </c>
       <c r="P45" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q45">
         <v>-0.06143081418824267</v>
@@ -6642,24 +6198,24 @@
         <v>-0.004730782807804843</v>
       </c>
       <c r="S45" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F46">
         <v>0.3170570598774448</v>
@@ -6680,13 +6236,13 @@
         <v>0.007</v>
       </c>
       <c r="N46" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O46">
         <v>0.0138</v>
       </c>
       <c r="P46" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q46">
         <v>-0.1592997954158392</v>
@@ -6695,24 +6251,24 @@
         <v>-0.01415100173422988</v>
       </c>
       <c r="S46" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F47">
         <v>0.8484848484848485</v>
@@ -6733,39 +6289,33 @@
         <v>0.2109029260566068</v>
       </c>
       <c r="N47" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O47">
         <v>0.6327087781698203</v>
       </c>
       <c r="P47" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q47">
-        <v>-0.07352941176470588</v>
-      </c>
-      <c r="R47">
-        <v>0.2711864406779661</v>
+        <v>109</v>
       </c>
       <c r="S47" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F48">
         <v>0.8663101604278075</v>
@@ -6786,39 +6336,33 @@
         <v>0.8501067391385259</v>
       </c>
       <c r="N48" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O48">
         <v>0.8501067391385259</v>
       </c>
       <c r="P48" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q48">
-        <v>-0.05615820998675333</v>
-      </c>
-      <c r="R48">
-        <v>0.07951283350219536</v>
+        <v>109</v>
       </c>
       <c r="S48" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F49">
         <v>0.8616600790513834</v>
@@ -6839,39 +6383,33 @@
         <v>0.2626182904425174</v>
       </c>
       <c r="N49" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O49">
         <v>0.5252365808850348</v>
       </c>
       <c r="P49" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q49">
-        <v>-0.03162055335968379</v>
-      </c>
-      <c r="R49">
-        <v>0.1001976284584995</v>
+        <v>109</v>
       </c>
       <c r="S49" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F50">
         <v>0.9163830821584832</v>
@@ -6892,39 +6430,33 @@
         <v>0.04866005335540764</v>
       </c>
       <c r="N50" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="O50">
         <v>0.09732010671081527</v>
       </c>
       <c r="P50" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q50">
-        <v>-0.009843146013245659</v>
-      </c>
-      <c r="R50">
-        <v>0.1017245266646797</v>
+        <v>109</v>
       </c>
       <c r="S50" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F51">
         <v>0.1118212812648221</v>
@@ -6945,13 +6477,13 @@
         <v>0.1366</v>
       </c>
       <c r="N51" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O51">
         <v>0.1868</v>
       </c>
       <c r="P51" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q51">
         <v>-0.0459950736638484</v>
@@ -6960,24 +6492,24 @@
         <v>0.009574605679658545</v>
       </c>
       <c r="S51" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F52">
         <v>0.3563365536576291</v>
@@ -6998,13 +6530,13 @@
         <v>0.1234</v>
       </c>
       <c r="N52" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="O52">
         <v>0.1416</v>
       </c>
       <c r="P52" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Q52">
         <v>-0.1179283647360767</v>
@@ -7013,24 +6545,24 @@
         <v>0.02303655514637615</v>
       </c>
       <c r="S52" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E53" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F53">
         <v>0.803030303030303</v>
@@ -7051,39 +6583,33 @@
         <v>0.4795001221869534</v>
       </c>
       <c r="N53" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O53">
         <v>0.6463551955394902</v>
       </c>
       <c r="P53" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q53">
-        <v>-0.09015151515151501</v>
-      </c>
-      <c r="R53">
-        <v>0.213666666666667</v>
+        <v>109</v>
       </c>
       <c r="S53" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E54" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F54">
         <v>0.8823529411764706</v>
@@ -7104,39 +6630,33 @@
         <v>0.4576140668763148</v>
       </c>
       <c r="N54" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O54">
         <v>0.8501067391385259</v>
       </c>
       <c r="P54" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q54">
-        <v>-0.04218323586744636</v>
-      </c>
-      <c r="R54">
-        <v>0.09913967059336842</v>
+        <v>109</v>
       </c>
       <c r="S54" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F55">
         <v>0.8616600790513834</v>
@@ -7157,22 +6677,16 @@
         <v>0.2432427057426535</v>
       </c>
       <c r="N55" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="O55">
         <v>0.486485411485307</v>
       </c>
       <c r="P55" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q55">
-        <v>-0.02766798418972332</v>
-      </c>
-      <c r="R55">
-        <v>0.1001976284584995</v>
+        <v>109</v>
       </c>
       <c r="S55" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -7196,78 +6710,78 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" t="s">
+      <c r="P1" t="s">
         <v>124</v>
       </c>
-      <c r="E1" t="s">
+      <c r="Q1" t="s">
         <v>125</v>
       </c>
-      <c r="F1" t="s">
+      <c r="R1" t="s">
         <v>126</v>
-      </c>
-      <c r="G1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K1" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O1" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>135</v>
-      </c>
-      <c r="R1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H2">
         <v>516</v>
@@ -7291,39 +6805,39 @@
         <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H3">
         <v>263</v>
@@ -7347,39 +6861,39 @@
         <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H4">
         <v>253</v>
@@ -7403,16 +6917,16 @@
         <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
